--- a/data/output/workbook/2026-06-28.xlsx
+++ b/data/output/workbook/2026-06-28.xlsx
@@ -461,7 +461,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="8915400"/>
+    <ext cx="10125075" cy="9277350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9277350"/>
+    <ext cx="10125075" cy="9429750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28 03:58</t>
+          <t>2026-06-28 06:29</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2015,807 +2015,807 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="29" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="29" t="inlineStr">
         <is>
           <t>Houston Astros offense vs Detroit Tigers defense</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="30" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B59" s="30" t="inlineStr">
+      <c r="B61" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C59" s="30" t="inlineStr">
+      <c r="C61" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D59" s="30" t="inlineStr">
+      <c r="D61" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E59" s="30" t="inlineStr">
+      <c r="E61" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F59" s="30" t="inlineStr">
+      <c r="F61" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G59" s="30" t="inlineStr">
+      <c r="G61" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H59" s="30" t="inlineStr">
+      <c r="H61" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I59" s="30" t="inlineStr">
+      <c r="I61" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J59" s="30" t="inlineStr">
+      <c r="J61" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K59" s="30" t="inlineStr">
+      <c r="K61" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L59" s="30" t="inlineStr">
+      <c r="L61" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M59" s="30" t="inlineStr">
+      <c r="M61" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N59" s="30" t="inlineStr">
+      <c r="N61" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O59" s="30" t="inlineStr">
+      <c r="O61" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P59" s="30" t="inlineStr">
+      <c r="P61" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q59" s="30" t="inlineStr">
+      <c r="Q61" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B60" s="32" t="n">
-        <v>5.026</v>
-      </c>
-      <c r="C60" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="D60" s="32" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="E60" s="32" t="n">
-        <v>4.533</v>
-      </c>
-      <c r="F60" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G60" s="32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H60" s="34" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I60" s="32" t="inlineStr"/>
-      <c r="J60" s="36" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K60" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L60" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M60" s="32" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="N60" s="32" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="O60" s="32" t="n">
-        <v>4.267</v>
-      </c>
-      <c r="P60" s="32" t="n">
-        <v>4.108</v>
-      </c>
-      <c r="Q60" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B61" s="32" t="n">
-        <v>8.27</v>
-      </c>
-      <c r="C61" s="32" t="n">
-        <v>7.821</v>
-      </c>
-      <c r="D61" s="32" t="n">
-        <v>7.158</v>
-      </c>
-      <c r="E61" s="32" t="n">
-        <v>7.571</v>
-      </c>
-      <c r="F61" s="32" t="n">
-        <v>6.556</v>
-      </c>
-      <c r="G61" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="H61" s="34" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I61" s="32" t="inlineStr"/>
-      <c r="J61" s="36" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="K61" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L61" s="32" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="M61" s="32" t="n">
-        <v>8.532999999999999</v>
-      </c>
-      <c r="N61" s="32" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="O61" s="32" t="n">
-        <v>7.767</v>
-      </c>
-      <c r="P61" s="32" t="n">
-        <v>7.649</v>
-      </c>
-      <c r="Q61" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B62" s="32" t="n">
-        <v>1.378</v>
+        <v>5.026</v>
       </c>
       <c r="C62" s="32" t="n">
-        <v>1.429</v>
+        <v>4.533</v>
       </c>
       <c r="D62" s="32" t="n">
-        <v>1.632</v>
+        <v>4.35</v>
       </c>
       <c r="E62" s="32" t="n">
-        <v>1.714</v>
+        <v>4.533</v>
       </c>
       <c r="F62" s="32" t="n">
-        <v>1.778</v>
+        <v>4.5</v>
       </c>
       <c r="G62" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H62" s="36" t="inlineStr">
-        <is>
-          <t>12th</t>
+        <v>2.4</v>
+      </c>
+      <c r="H62" s="34" t="inlineStr">
+        <is>
+          <t>24th</t>
         </is>
       </c>
       <c r="I62" s="32" t="inlineStr"/>
-      <c r="J62" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P62" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J62" s="36" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K62" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L62" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M62" s="32" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="N62" s="32" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="O62" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="P62" s="32" t="n">
+        <v>4.108</v>
       </c>
       <c r="Q62" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B63" s="32" t="n">
-        <v>7.595</v>
+        <v>8.27</v>
       </c>
       <c r="C63" s="32" t="n">
-        <v>7.429</v>
+        <v>7.821</v>
       </c>
       <c r="D63" s="32" t="n">
-        <v>7.474</v>
+        <v>7.158</v>
       </c>
       <c r="E63" s="32" t="n">
-        <v>7.071</v>
+        <v>7.571</v>
       </c>
       <c r="F63" s="32" t="n">
-        <v>7.111</v>
+        <v>6.556</v>
       </c>
       <c r="G63" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H63" s="36" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I63" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J63" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>6</v>
+      </c>
+      <c r="H63" s="34" t="inlineStr">
+        <is>
+          <t>24th</t>
+        </is>
+      </c>
+      <c r="I63" s="32" t="inlineStr"/>
+      <c r="J63" s="36" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="K63" s="32" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L63" s="32" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M63" s="32" t="n">
-        <v>7.6</v>
+        <v>8.532999999999999</v>
       </c>
       <c r="N63" s="32" t="n">
-        <v>8.050000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="O63" s="32" t="n">
-        <v>7.933</v>
+        <v>7.767</v>
       </c>
       <c r="P63" s="32" t="n">
-        <v>7.838</v>
+        <v>7.649</v>
       </c>
       <c r="Q63" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="n">
+        <v>1.378</v>
+      </c>
+      <c r="C64" s="32" t="n">
+        <v>1.429</v>
+      </c>
+      <c r="D64" s="32" t="n">
+        <v>1.632</v>
+      </c>
+      <c r="E64" s="32" t="n">
+        <v>1.714</v>
+      </c>
+      <c r="F64" s="32" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="G64" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="36" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I64" s="32" t="inlineStr"/>
+      <c r="J64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q64" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B65" s="32" t="n">
+        <v>7.595</v>
+      </c>
+      <c r="C65" s="32" t="n">
+        <v>7.429</v>
+      </c>
+      <c r="D65" s="32" t="n">
+        <v>7.474</v>
+      </c>
+      <c r="E65" s="32" t="n">
+        <v>7.071</v>
+      </c>
+      <c r="F65" s="32" t="n">
+        <v>7.111</v>
+      </c>
+      <c r="G65" s="32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H65" s="36" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J65" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L65" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M65" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N65" s="32" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="O65" s="32" t="n">
+        <v>7.933</v>
+      </c>
+      <c r="P65" s="32" t="n">
+        <v>7.838</v>
+      </c>
+      <c r="Q65" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B64" s="32" t="n">
+      <c r="B66" s="32" t="n">
         <v>0.73</v>
       </c>
-      <c r="C64" s="32" t="n">
+      <c r="C66" s="32" t="n">
         <v>0.714</v>
       </c>
-      <c r="D64" s="32" t="n">
+      <c r="D66" s="32" t="n">
         <v>0.947</v>
       </c>
-      <c r="E64" s="32" t="n">
+      <c r="E66" s="32" t="n">
         <v>0.929</v>
       </c>
-      <c r="F64" s="32" t="n">
+      <c r="F66" s="32" t="n">
         <v>0.889</v>
       </c>
-      <c r="G64" s="32" t="n">
+      <c r="G66" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H64" s="33" t="inlineStr">
+      <c r="H66" s="33" t="inlineStr">
         <is>
           <t>8th</t>
         </is>
       </c>
-      <c r="I64" s="32" t="inlineStr"/>
-      <c r="J64" s="33" t="inlineStr">
+      <c r="I66" s="32" t="inlineStr"/>
+      <c r="J66" s="33" t="inlineStr">
         <is>
           <t>4th</t>
         </is>
       </c>
-      <c r="K64" s="32" t="n">
+      <c r="K66" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L64" s="32" t="n">
+      <c r="L66" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="M64" s="32" t="n">
+      <c r="M66" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="N64" s="32" t="n">
+      <c r="N66" s="32" t="n">
         <v>0.35</v>
       </c>
-      <c r="O64" s="32" t="n">
+      <c r="O66" s="32" t="n">
         <v>0.433</v>
       </c>
-      <c r="P64" s="32" t="n">
+      <c r="P66" s="32" t="n">
         <v>0.432</v>
       </c>
-      <c r="Q64" s="35" t="inlineStr">
+      <c r="Q66" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>Detroit Tigers offense vs Houston Astros defense</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B67" s="30" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C67" s="30" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D67" s="30" t="inlineStr">
+      <c r="D69" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E67" s="30" t="inlineStr">
+      <c r="E69" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F67" s="30" t="inlineStr">
+      <c r="F69" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G67" s="30" t="inlineStr">
+      <c r="G69" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H67" s="30" t="inlineStr">
+      <c r="H69" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I67" s="30" t="inlineStr">
+      <c r="I69" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J67" s="30" t="inlineStr">
+      <c r="J69" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K67" s="30" t="inlineStr">
+      <c r="K69" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L67" s="30" t="inlineStr">
+      <c r="L69" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M67" s="30" t="inlineStr">
+      <c r="M69" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N67" s="30" t="inlineStr">
+      <c r="N69" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O67" s="30" t="inlineStr">
+      <c r="O69" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P67" s="30" t="inlineStr">
+      <c r="P69" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q67" s="30" t="inlineStr">
+      <c r="Q69" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>4.054</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>3.733</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H68" s="34" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>2</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>5.167</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>5.077</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>7.973</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>8.067</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>7.933</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr"/>
-      <c r="J69" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>4.889</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>6.643</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>7.053</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>8.026999999999999</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>0.946</v>
+        <v>4.054</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>1.1</v>
+        <v>4.067</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>1.15</v>
+        <v>3.9</v>
       </c>
       <c r="E70" s="32" t="n">
-        <v>1.2</v>
+        <v>3.733</v>
       </c>
       <c r="F70" s="32" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="G70" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H70" s="36" t="inlineStr">
-        <is>
-          <t>18th</t>
+        <v>2.2</v>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P70" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>5.167</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>5.077</v>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>8.622</v>
+        <v>7.973</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>8.467000000000001</v>
+        <v>8.067</v>
       </c>
       <c r="D71" s="32" t="n">
-        <v>8.85</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E71" s="32" t="n">
-        <v>9.266999999999999</v>
+        <v>7.933</v>
       </c>
       <c r="F71" s="32" t="n">
-        <v>10.3</v>
+        <v>7.3</v>
       </c>
       <c r="G71" s="32" t="n">
-        <v>12.2</v>
+        <v>6.4</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
-          <t>30th</t>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
+      <c r="J71" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
         </is>
       </c>
       <c r="K71" s="32" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="L71" s="32" t="n">
-        <v>7.333</v>
+        <v>4.889</v>
       </c>
       <c r="M71" s="32" t="n">
-        <v>7.214</v>
+        <v>6.643</v>
       </c>
       <c r="N71" s="32" t="n">
-        <v>8.105</v>
+        <v>7.053</v>
       </c>
       <c r="O71" s="32" t="n">
-        <v>7.857</v>
+        <v>8.25</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>8.73</v>
+        <v>8.026999999999999</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>0.946</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H72" s="36" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr"/>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="31" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="n">
+        <v>8.622</v>
+      </c>
+      <c r="C73" s="32" t="n">
+        <v>8.467000000000001</v>
+      </c>
+      <c r="D73" s="32" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="E73" s="32" t="n">
+        <v>9.266999999999999</v>
+      </c>
+      <c r="F73" s="32" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="G73" s="32" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>7.214</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>8.105</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>7.857</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="Q73" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B72" s="32" t="n">
+      <c r="B74" s="32" t="n">
         <v>0.541</v>
       </c>
-      <c r="C72" s="32" t="n">
+      <c r="C74" s="32" t="n">
         <v>0.533</v>
       </c>
-      <c r="D72" s="32" t="n">
+      <c r="D74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="E72" s="32" t="n">
+      <c r="E74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="F72" s="32" t="n">
+      <c r="F74" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="G72" s="32" t="n">
+      <c r="G74" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="H72" s="34" t="inlineStr">
+      <c r="H74" s="34" t="inlineStr">
         <is>
           <t>25th</t>
         </is>
       </c>
-      <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="33" t="inlineStr">
+      <c r="I74" s="32" t="inlineStr"/>
+      <c r="J74" s="33" t="inlineStr">
         <is>
           <t>2nd</t>
         </is>
       </c>
-      <c r="K72" s="32" t="n">
+      <c r="K74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L72" s="32" t="n">
+      <c r="L74" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="M72" s="32" t="n">
+      <c r="M74" s="32" t="n">
         <v>0.357</v>
       </c>
-      <c r="N72" s="32" t="n">
+      <c r="N74" s="32" t="n">
         <v>0.421</v>
       </c>
-      <c r="O72" s="32" t="n">
+      <c r="O74" s="32" t="n">
         <v>0.679</v>
       </c>
-      <c r="P72" s="32" t="n">
+      <c r="P74" s="32" t="n">
         <v>0.5679999999999999</v>
       </c>
-      <c r="Q72" s="35" t="inlineStr">
+      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4518,7 +4518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4535,807 +4535,807 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="29" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr">
         <is>
           <t>Philadelphia Phillies offense vs New York Mets defense</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="30" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B61" s="30" t="inlineStr">
+      <c r="B62" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C61" s="30" t="inlineStr">
+      <c r="C62" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D61" s="30" t="inlineStr">
+      <c r="D62" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E61" s="30" t="inlineStr">
+      <c r="E62" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F61" s="30" t="inlineStr">
+      <c r="F62" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G61" s="30" t="inlineStr">
+      <c r="G62" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H61" s="30" t="inlineStr">
+      <c r="H62" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I61" s="30" t="inlineStr">
+      <c r="I62" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J61" s="30" t="inlineStr">
+      <c r="J62" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K61" s="30" t="inlineStr">
+      <c r="K62" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L61" s="30" t="inlineStr">
+      <c r="L62" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M61" s="30" t="inlineStr">
+      <c r="M62" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N61" s="30" t="inlineStr">
+      <c r="N62" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O61" s="30" t="inlineStr">
+      <c r="O62" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P61" s="30" t="inlineStr">
+      <c r="P62" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q61" s="30" t="inlineStr">
+      <c r="Q62" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B62" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="C62" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="D62" s="32" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="E62" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F62" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="G62" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H62" s="36" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="I62" s="32" t="inlineStr"/>
-      <c r="J62" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K62" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L62" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M62" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="N62" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O62" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P62" s="32" t="n">
-        <v>4.214</v>
-      </c>
-      <c r="Q62" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B63" s="32" t="n">
-        <v>7.568</v>
+        <v>4.1</v>
       </c>
       <c r="C63" s="32" t="n">
-        <v>7.37</v>
+        <v>4.067</v>
       </c>
       <c r="D63" s="32" t="n">
-        <v>7.5</v>
+        <v>3.95</v>
       </c>
       <c r="E63" s="32" t="n">
-        <v>7.923</v>
+        <v>4.6</v>
       </c>
       <c r="F63" s="32" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="G63" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H63" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
+        <v>2.8</v>
+      </c>
+      <c r="H63" s="36" t="inlineStr">
+        <is>
+          <t>20th</t>
         </is>
       </c>
       <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="36" t="inlineStr">
-        <is>
-          <t>12th</t>
+      <c r="J63" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="K63" s="32" t="n">
-        <v>7.4</v>
+        <v>4.8</v>
       </c>
       <c r="L63" s="32" t="n">
-        <v>7.4</v>
+        <v>4.1</v>
       </c>
       <c r="M63" s="32" t="n">
-        <v>7.6</v>
+        <v>4.067</v>
       </c>
       <c r="N63" s="32" t="n">
-        <v>7.9</v>
+        <v>4.6</v>
       </c>
       <c r="O63" s="32" t="n">
-        <v>7.862</v>
+        <v>4.5</v>
       </c>
       <c r="P63" s="32" t="n">
-        <v>7.842</v>
+        <v>4.214</v>
       </c>
       <c r="Q63" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B64" s="32" t="n">
-        <v>1.135</v>
+        <v>7.568</v>
       </c>
       <c r="C64" s="32" t="n">
-        <v>1.148</v>
+        <v>7.37</v>
       </c>
       <c r="D64" s="32" t="n">
-        <v>1.222</v>
+        <v>7.5</v>
       </c>
       <c r="E64" s="32" t="n">
-        <v>1.385</v>
+        <v>7.923</v>
       </c>
       <c r="F64" s="32" t="n">
-        <v>1.333</v>
+        <v>8</v>
       </c>
       <c r="G64" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H64" s="36" t="inlineStr">
-        <is>
-          <t>16th</t>
+        <v>5.8</v>
+      </c>
+      <c r="H64" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="I64" s="32" t="inlineStr"/>
-      <c r="J64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J64" s="36" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K64" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L64" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M64" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N64" s="32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O64" s="32" t="n">
+        <v>7.862</v>
+      </c>
+      <c r="P64" s="32" t="n">
+        <v>7.842</v>
       </c>
       <c r="Q64" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>8.568</v>
+        <v>1.135</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>8.704000000000001</v>
+        <v>1.148</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>8.611000000000001</v>
+        <v>1.222</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>9.077</v>
+        <v>1.385</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>9.555999999999999</v>
+        <v>1.333</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H65" s="34" t="inlineStr">
-        <is>
-          <t>28th</t>
+        <v>0.8</v>
+      </c>
+      <c r="H65" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L65" s="32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M65" s="32" t="n">
-        <v>8.933</v>
-      </c>
-      <c r="N65" s="32" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="O65" s="32" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="P65" s="32" t="n">
-        <v>8.920999999999999</v>
+      <c r="J65" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="n">
+        <v>8.568</v>
+      </c>
+      <c r="C66" s="32" t="n">
+        <v>8.704000000000001</v>
+      </c>
+      <c r="D66" s="32" t="n">
+        <v>8.611000000000001</v>
+      </c>
+      <c r="E66" s="32" t="n">
+        <v>9.077</v>
+      </c>
+      <c r="F66" s="32" t="n">
+        <v>9.555999999999999</v>
+      </c>
+      <c r="G66" s="32" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H66" s="34" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr"/>
+      <c r="J66" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L66" s="32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M66" s="32" t="n">
+        <v>8.933</v>
+      </c>
+      <c r="N66" s="32" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="O66" s="32" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="P66" s="32" t="n">
+        <v>8.920999999999999</v>
+      </c>
+      <c r="Q66" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B66" s="32" t="n">
+      <c r="B67" s="32" t="n">
         <v>0.649</v>
       </c>
-      <c r="C66" s="32" t="n">
+      <c r="C67" s="32" t="n">
         <v>0.481</v>
       </c>
-      <c r="D66" s="32" t="n">
+      <c r="D67" s="32" t="n">
         <v>0.389</v>
       </c>
-      <c r="E66" s="32" t="n">
+      <c r="E67" s="32" t="n">
         <v>0.385</v>
       </c>
-      <c r="F66" s="32" t="n">
+      <c r="F67" s="32" t="n">
         <v>0.444</v>
       </c>
-      <c r="G66" s="32" t="n">
+      <c r="G67" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H66" s="33" t="inlineStr">
+      <c r="H67" s="33" t="inlineStr">
         <is>
           <t>6th</t>
         </is>
       </c>
-      <c r="I66" s="32" t="inlineStr">
+      <c r="I67" s="32" t="inlineStr">
         <is>
           <t>★★★</t>
         </is>
       </c>
-      <c r="J66" s="36" t="inlineStr">
+      <c r="J67" s="36" t="inlineStr">
         <is>
           <t>20th</t>
         </is>
       </c>
-      <c r="K66" s="32" t="n">
+      <c r="K67" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="L66" s="32" t="n">
+      <c r="L67" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="M66" s="32" t="n">
+      <c r="M67" s="32" t="n">
         <v>0.267</v>
       </c>
-      <c r="N66" s="32" t="n">
+      <c r="N67" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="O66" s="32" t="n">
+      <c r="O67" s="32" t="n">
         <v>0.379</v>
       </c>
-      <c r="P66" s="32" t="n">
+      <c r="P67" s="32" t="n">
         <v>0.474</v>
       </c>
-      <c r="Q66" s="35" t="inlineStr">
+      <c r="Q67" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>New York Mets offense vs Philadelphia Phillies defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="30" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="30" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="30" t="inlineStr">
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="30" t="inlineStr">
+      <c r="E70" s="30" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="30" t="inlineStr">
+      <c r="F70" s="30" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="30" t="inlineStr">
+      <c r="G70" s="30" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="30" t="inlineStr">
+      <c r="H70" s="30" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="30" t="inlineStr">
+      <c r="I70" s="30" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="30" t="inlineStr">
+      <c r="J70" s="30" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="30" t="inlineStr">
+      <c r="K70" s="30" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="30" t="inlineStr">
+      <c r="L70" s="30" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="30" t="inlineStr">
+      <c r="M70" s="30" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="30" t="inlineStr">
+      <c r="N70" s="30" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="30" t="inlineStr">
+      <c r="O70" s="30" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="30" t="inlineStr">
+      <c r="P70" s="30" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="30" t="inlineStr">
+      <c r="Q70" s="30" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="31" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="32" t="n">
-        <v>3.357</v>
-      </c>
-      <c r="C70" s="32" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="D70" s="32" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E70" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="F70" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>5.633</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>5.375</v>
-      </c>
-      <c r="Q70" s="35" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.053</v>
+        <v>3.357</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>6.586</v>
+        <v>2.667</v>
       </c>
       <c r="D71" s="32" t="n">
-        <v>6.55</v>
+        <v>2.85</v>
       </c>
       <c r="E71" s="32" t="n">
-        <v>6.333</v>
+        <v>3</v>
       </c>
       <c r="F71" s="32" t="n">
-        <v>5.6</v>
+        <v>2.8</v>
       </c>
       <c r="G71" s="32" t="n">
-        <v>5.8</v>
+        <v>2.8</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
-          <t>26th</t>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
       <c r="J71" s="33" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>8th</t>
         </is>
       </c>
       <c r="K71" s="32" t="n">
-        <v>7.4</v>
+        <v>2.8</v>
       </c>
       <c r="L71" s="32" t="n">
-        <v>8.888999999999999</v>
+        <v>4.7</v>
       </c>
       <c r="M71" s="32" t="n">
-        <v>9.769</v>
+        <v>5.067</v>
       </c>
       <c r="N71" s="32" t="n">
-        <v>9.888999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="O71" s="32" t="n">
-        <v>10.222</v>
+        <v>5.633</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>9.891999999999999</v>
+        <v>5.375</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>0.737</v>
+        <v>7.053</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>0.6899999999999999</v>
+        <v>6.586</v>
       </c>
       <c r="D72" s="32" t="n">
-        <v>0.7</v>
+        <v>6.55</v>
       </c>
       <c r="E72" s="32" t="n">
-        <v>0.733</v>
+        <v>6.333</v>
       </c>
       <c r="F72" s="32" t="n">
-        <v>0.8</v>
+        <v>5.6</v>
       </c>
       <c r="G72" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
+        <v>5.8</v>
+      </c>
+      <c r="H72" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J72" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>8.888999999999999</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>9.769</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>9.888999999999999</v>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>10.222</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>9.891999999999999</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.395</v>
+        <v>0.737</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>8.448</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>8.85</v>
+        <v>0.7</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>8.867000000000001</v>
+        <v>0.733</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>9.5</v>
+        <v>0.8</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>23rd</t>
+        <v>1.2</v>
+      </c>
+      <c r="H73" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>10.444</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>9.154</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>9.055999999999999</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>9.074</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>9.486000000000001</v>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>1st Inn R/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>0.553</v>
+        <v>8.395</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>0.414</v>
+        <v>8.448</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>0.4</v>
+        <v>8.85</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>0.533</v>
+        <v>8.867000000000001</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>0.4</v>
+        <v>9.5</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
+        <v>10</v>
+      </c>
+      <c r="H74" s="34" t="inlineStr">
+        <is>
+          <t>23rd</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
       <c r="J74" s="33" t="inlineStr">
         <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>10.444</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>9.154</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>9.055999999999999</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>9.074</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>9.486000000000001</v>
+      </c>
+      <c r="Q74" s="35" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="C75" s="32" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="D75" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E75" s="32" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="F75" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G75" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H75" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr"/>
+      <c r="J75" s="33" t="inlineStr">
+        <is>
           <t>1st</t>
         </is>
       </c>
-      <c r="K74" s="32" t="n">
+      <c r="K75" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="L74" s="32" t="n">
+      <c r="L75" s="32" t="n">
         <v>0.556</v>
       </c>
-      <c r="M74" s="32" t="n">
+      <c r="M75" s="32" t="n">
         <v>0.615</v>
       </c>
-      <c r="N74" s="32" t="n">
+      <c r="N75" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="O74" s="32" t="n">
+      <c r="O75" s="32" t="n">
         <v>0.519</v>
       </c>
-      <c r="P74" s="32" t="n">
+      <c r="P75" s="32" t="n">
         <v>0.595</v>
       </c>
-      <c r="Q74" s="35" t="inlineStr">
+      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7972,7 +7972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8116,13 +8116,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.5769059405940594</v>
+        <v>0.5769</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-136</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8182,13 +8182,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.628525</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-170</v>
+        <v>-169</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-125</v>
+        <v>-124</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -170). Your call.</t>
+          <t>Model 62.9% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8380,13 +8380,13 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3853846153846154</v>
+        <v>0.3886330935251798</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 38.5% (fair +159). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8422,37 +8422,37 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5841465116279071</v>
+        <v>0.473920704845815</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-140</v>
+        <v>111</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>-115</v>
+        <v>127</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8488,37 +8488,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Texas Rangers @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4562605042016807</v>
+        <v>0.5264705882352941</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>119</v>
+        <v>-111</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8554,37 +8554,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Over 179.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.473920704845815</v>
+        <v>0.5263235294117647</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>111</v>
+        <v>-111</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8625,32 +8625,32 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>Texas Rangers @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5263235294117647</v>
+        <v>0.4877272727272727</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-111</v>
+        <v>105</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8691,12 +8691,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8706,17 +8706,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6421200000000001</v>
+        <v>0.4944700460829493</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-179</v>
+        <v>102</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-150</v>
+        <v>117</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -179). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8752,17 +8752,17 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -8772,17 +8772,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4894009216589862</v>
+        <v>0.6421200000000001</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>104</v>
+        <v>-179</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>117</v>
+        <v>-150</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 64.2% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8818,17 +8818,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8838,17 +8838,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5282587064676618</v>
+        <v>0.4677533039647577</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-112</v>
+        <v>114</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8884,17 +8884,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8904,17 +8904,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4967605633802817</v>
+        <v>0.52885</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>101</v>
+        <v>-112</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8950,37 +8950,37 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.486036866359447</v>
+        <v>0.5410384615384616</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>106</v>
+        <v>-118</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>117</v>
+        <v>-108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9021,32 +9021,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Washington Mystics</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire +7.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5451403846153846</v>
+        <v>0.4366806722689076</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-120</v>
+        <v>129</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-108</v>
+        <v>138</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -9097,22 +9097,22 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5410384615384616</v>
+        <v>0.3847777777777777</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-118</v>
+        <v>160</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>-108</v>
+        <v>170</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 38.5% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9163,22 +9163,22 @@
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.3857777777777778</v>
+        <v>0.5390653846153846</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>159</v>
+        <v>-117</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>170</v>
+        <v>-108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9214,17 +9214,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Detroit Tigers</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9234,17 +9234,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4707727272727273</v>
+        <v>0.4985096153846154</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9285,12 +9285,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Minnesota Lynx @ Dallas Wings</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -9300,17 +9300,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4345378151260504</v>
+        <v>0.6219600000000001</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>130</v>
+        <v>-165</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>138</v>
+        <v>-150</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9346,17 +9346,17 @@
     <row r="24">
       <c r="A24" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Houston Astros @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9366,17 +9366,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4967788461538462</v>
+        <v>0.4707727272727273</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9412,17 +9412,17 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -9432,17 +9432,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5768709251101322</v>
+        <v>0.4967788461538462</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-136</v>
+        <v>101</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-127</v>
+        <v>108</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9483,12 +9483,12 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ Dallas Wings</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -9498,17 +9498,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.6232149606299213</v>
+        <v>0.5768709251101322</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-165</v>
+        <v>-136</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-154</v>
+        <v>-127</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9532,7 +9532,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9549,32 +9549,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs +1.5</t>
+          <t>Las Vegas Aces</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.534547619047619</v>
+        <v>0.738781690140845</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-115</v>
+        <v>-283</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>-110</v>
+        <v>-255</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 73.9% (fair -283). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9607,9 +9607,141 @@
         <v/>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>Chicago Cubs +1.5</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>0.5316403846153847</v>
+      </c>
+      <c r="G28" s="14" t="n">
+        <v>-114</v>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I28" s="13">
+        <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>IF($H$28="","",$F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))</f>
+        <v/>
+      </c>
+      <c r="K28" s="17">
+        <f>IF($H$28="","",MAX(0,($F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))/IF($H$28&lt;0,-100/$H$28,$H$28/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L28" s="18">
+        <f>IF($H$28="","",ROUND(MIN($K$28,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M28" s="12">
+        <f>IF($J$28="","",IF($J$28&lt;0,"Pass",IF($J$28&lt;'Settings'!$B$4,"Thin",IF($J$28&lt;0.06,"✅ Sharp band",IF($J$28&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N28" s="19" t="inlineStr">
+        <is>
+          <t>Model 53.2% (fair -114). Your call.</t>
+        </is>
+      </c>
+      <c r="O28" s="15" t="n"/>
+      <c r="P28" s="16">
+        <f>IF(OR($H$28="",$O$28=""),"",(1+IF($H$28&lt;0,-100/$H$28,$H$28/100))/(1+IF($O$28&lt;0,-100/$O$28,$O$28/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies @ New York Mets</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Spread</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>New York Mets +1.5</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>0.561035135135135</v>
+      </c>
+      <c r="G29" s="14" t="n">
+        <v>-128</v>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>-122</v>
+      </c>
+      <c r="I29" s="13">
+        <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
+        <v/>
+      </c>
+      <c r="J29" s="16">
+        <f>IF($H$29="","",$F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))</f>
+        <v/>
+      </c>
+      <c r="K29" s="17">
+        <f>IF($H$29="","",MAX(0,($F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))/IF($H$29&lt;0,-100/$H$29,$H$29/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L29" s="18">
+        <f>IF($H$29="","",ROUND(MIN($K$29,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M29" s="12">
+        <f>IF($J$29="","",IF($J$29&lt;0,"Pass",IF($J$29&lt;'Settings'!$B$4,"Thin",IF($J$29&lt;0.06,"✅ Sharp band",IF($J$29&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N29" s="19" t="inlineStr">
+        <is>
+          <t>Model 56.1% (fair -128). Your call.</t>
+        </is>
+      </c>
+      <c r="O29" s="15" t="n"/>
+      <c r="P29" s="16">
+        <f>IF(OR($H$29="",$O$29=""),"",(1+IF($H$29&lt;0,-100/$H$29,$H$29/100))/(1+IF($O$29&lt;0,-100/$O$29,$O$29/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J27">
+  <conditionalFormatting sqref="J5:J29">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -9631,7 +9763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P100"/>
+  <dimension ref="A1:P102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9775,13 +9907,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.348705035971223</v>
+        <v>0.3495289855072464</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9805,7 +9937,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 34.9% (fair +187). Your call.</t>
+          <t>Model 35.0% (fair +186). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9841,10 +9973,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6513007194244604</v>
+        <v>0.650468345323741</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-187</v>
+        <v>-186</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-178</v>
@@ -9871,7 +10003,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.1% (fair -187). Your call.</t>
+          <t>Model 65.0% (fair -186). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9913,7 +10045,7 @@
         <v>-136</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9979,7 +10111,7 @@
         <v>136</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10111,7 +10243,7 @@
         <v>116</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -10171,13 +10303,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3704932735426009</v>
+        <v>0.3714864864864865</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -10201,7 +10333,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 37.0% (fair +170). Your call.</t>
+          <t>Model 37.1% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10237,13 +10369,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.628525</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-170</v>
+        <v>-169</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-125</v>
+        <v>-124</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -10267,7 +10399,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -170). Your call.</t>
+          <t>Model 62.9% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10299,17 +10431,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5841465116279071</v>
+        <v>0.5379</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-140</v>
+        <v>-116</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-115</v>
+        <v>108</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10333,7 +10465,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10365,14 +10497,14 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.415868544600939</v>
+        <v>0.4621</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>113</v>
@@ -10399,7 +10531,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10507,7 +10639,7 @@
         <v>136</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-122</v>
+        <v>-121</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10567,13 +10699,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4894009216589862</v>
+        <v>0.4877272727272727</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10597,7 +10729,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10633,10 +10765,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5105944700460829</v>
+        <v>0.5122658986175115</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>-117</v>
@@ -10663,7 +10795,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10699,10 +10831,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5578</v>
+        <v>0.5264705882352941</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-126</v>
+        <v>-111</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>104</v>
@@ -10729,7 +10861,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10765,13 +10897,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4422</v>
+        <v>0.47355</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10795,7 +10927,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10903,7 +11035,7 @@
         <v>-180</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-126</v>
+        <v>-124</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11227,13 +11359,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5282587064676618</v>
+        <v>0.52885</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>-112</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11257,7 +11389,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11293,7 +11425,7 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4717725490196078</v>
+        <v>0.4711098039215686</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>112</v>
@@ -11323,7 +11455,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11623,10 +11755,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3857777777777778</v>
+        <v>0.3847777777777777</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>170</v>
@@ -11653,7 +11785,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 38.5% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11689,13 +11821,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6142037037037037</v>
+        <v>0.6152233576642336</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-159</v>
+        <v>-160</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-170</v>
+        <v>-174</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11719,7 +11851,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 61.5% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11751,17 +11883,17 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.4802</v>
+        <v>0.5390653846153846</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>108</v>
+        <v>-117</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>117</v>
+        <v>-108</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11785,7 +11917,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11817,17 +11949,17 @@
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 7.5</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.5198</v>
+        <v>0.4609223300970874</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>-108</v>
+        <v>117</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -11851,7 +11983,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 46.1% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -12019,13 +12151,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5783243697478991</v>
+        <v>0.577168085106383</v>
       </c>
       <c r="G39" s="14" t="n">
         <v>-137</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-138</v>
+        <v>-135</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12049,7 +12181,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 57.8% (fair -137). Your call.</t>
+          <t>Model 57.7% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12085,7 +12217,7 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4216738197424893</v>
+        <v>0.4228326180257511</v>
       </c>
       <c r="G40" s="14" t="n">
         <v>137</v>
@@ -12115,7 +12247,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 42.2% (fair +137). Your call.</t>
+          <t>Model 42.3% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12157,7 +12289,7 @@
         <v>136</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12264,32 +12396,32 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Philadelphia Phillies @ New York Mets</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.4345378151260504</v>
+        <v>0.561035135135135</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>130</v>
+        <v>-128</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>138</v>
+        <v>-122</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12313,7 +12445,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 43.5% (fair +130). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12330,32 +12462,32 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Philadelphia Phillies @ New York Mets</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Philadelphia Phillies -1.5</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5654360655737705</v>
+        <v>0.4389545454545454</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-130</v>
+        <v>128</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-144</v>
+        <v>120</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12379,7 +12511,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 56.5% (fair -130). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12406,22 +12538,22 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.5232</v>
+        <v>0.4366806722689076</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>-110</v>
+        <v>129</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12445,7 +12577,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12472,22 +12604,22 @@
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.4768</v>
+        <v>0.5633067226890757</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>110</v>
+        <v>-129</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>120</v>
+        <v>-138</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12511,7 +12643,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12538,22 +12670,22 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.421</v>
+        <v>0.5232</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>138</v>
+        <v>-110</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>144</v>
+        <v>122</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12577,7 +12709,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +138). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12604,22 +12736,22 @@
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.579</v>
+        <v>0.4768</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>-138</v>
+        <v>110</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-110</v>
+        <v>120</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12643,7 +12775,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -138). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12660,7 +12792,7 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -12670,22 +12802,22 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4231111111111111</v>
+        <v>0.421</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12709,7 +12841,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 42.1% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12726,7 +12858,7 @@
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
@@ -12736,22 +12868,22 @@
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Colorado Rockies +1.5</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5768709251101322</v>
+        <v>0.579</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-136</v>
+        <v>-138</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-127</v>
+        <v>-110</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12775,7 +12907,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 57.9% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12802,22 +12934,22 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.5663</v>
+        <v>0.4231111111111111</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-131</v>
+        <v>136</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12841,7 +12973,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12868,22 +13000,22 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.4337</v>
+        <v>0.5768709251101322</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>131</v>
+        <v>-136</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>115</v>
+        <v>-127</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12907,7 +13039,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12934,22 +13066,22 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.4723</v>
+        <v>0.5663</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>112</v>
+        <v>-131</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -12973,7 +13105,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13000,22 +13132,22 @@
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.5277000000000001</v>
+        <v>0.4337</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>-112</v>
+        <v>131</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-119</v>
+        <v>115</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13039,7 +13171,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13056,7 +13188,7 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -13066,22 +13198,22 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.3853846153846154</v>
+        <v>0.4723</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13105,7 +13237,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 38.5% (fair +159). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13122,7 +13254,7 @@
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
@@ -13132,22 +13264,22 @@
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.6146357142857143</v>
+        <v>0.5277000000000001</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-159</v>
+        <v>-112</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-180</v>
+        <v>-118</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13171,7 +13303,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -159). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13198,22 +13330,22 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.5941</v>
+        <v>0.3886330935251798</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>-146</v>
+        <v>157</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13237,7 +13369,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13264,22 +13396,22 @@
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.4059</v>
+        <v>0.6113571428571428</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>146</v>
+        <v>-157</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>114</v>
+        <v>-180</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13303,7 +13435,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13330,22 +13462,22 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4654326923076923</v>
+        <v>0.5941</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>115</v>
+        <v>-146</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -13369,7 +13501,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13396,22 +13528,22 @@
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs +1.5</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.534547619047619</v>
+        <v>0.4059</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-115</v>
+        <v>146</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>-110</v>
+        <v>114</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -13435,7 +13567,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13452,31 +13584,33 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ St. Louis Cardinals</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4834</v>
+        <v>0.4683414634146342</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>107</v>
-      </c>
-      <c r="H61" s="15" t="n"/>
+        <v>114</v>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>105</v>
+      </c>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
         <v/>
@@ -13499,7 +13633,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13516,31 +13650,33 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ St. Louis Cardinals</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Chicago Cubs +1.5</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5316403846153847</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-107</v>
-      </c>
-      <c r="H62" s="15" t="n"/>
+        <v>-114</v>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-108</v>
+      </c>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
         <v/>
@@ -13563,7 +13699,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13580,12 +13716,12 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Los Angeles Angels</t>
+          <t>Miami Marlins @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -13595,14 +13731,14 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.4657</v>
+        <v>0.4834</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13">
@@ -13627,7 +13763,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13644,12 +13780,12 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Los Angeles Angels</t>
+          <t>Miami Marlins @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -13659,14 +13795,14 @@
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5343</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-115</v>
+        <v>-107</v>
       </c>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="13">
@@ -13691,7 +13827,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13708,12 +13844,12 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ San Francisco Giants</t>
+          <t>Athletics @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -13723,14 +13859,14 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.521</v>
+        <v>0.4649</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>-109</v>
+        <v>115</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13755,7 +13891,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13772,12 +13908,12 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ San Francisco Giants</t>
+          <t>Athletics @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -13787,14 +13923,14 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.479</v>
+        <v>0.5351</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>109</v>
+        <v>-115</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13819,7 +13955,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13836,12 +13972,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ San Diego Padres</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -13851,14 +13987,14 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.5511</v>
+        <v>0.521</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-123</v>
+        <v>-109</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -13883,7 +14019,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -13900,12 +14036,12 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ San Diego Padres</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -13915,14 +14051,14 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.4489</v>
+        <v>0.479</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -13947,7 +14083,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -13964,12 +14100,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Boston Red Sox</t>
+          <t>Los Angeles Dodgers @ San Diego Padres</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -13979,14 +14115,14 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5324</v>
+        <v>0.5511</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>-114</v>
+        <v>-123</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14011,7 +14147,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14028,12 +14164,12 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Boston Red Sox</t>
+          <t>Los Angeles Dodgers @ San Diego Padres</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -14043,18 +14179,16 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4676061674008811</v>
+        <v>0.4489</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>114</v>
-      </c>
-      <c r="H70" s="15" t="n">
-        <v>-127</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
         <v/>
@@ -14077,7 +14211,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14104,23 +14238,21 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.428</v>
+        <v>0.5324</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>134</v>
-      </c>
-      <c r="H71" s="15" t="n">
-        <v>105</v>
-      </c>
+        <v>-114</v>
+      </c>
+      <c r="H71" s="15" t="n"/>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
         <v/>
@@ -14143,7 +14275,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14170,22 +14302,22 @@
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.4676061674008811</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-134</v>
+        <v>114</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>115</v>
+        <v>-127</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14209,7 +14341,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14236,22 +14368,22 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox -1.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.3379615384615385</v>
+        <v>0.428</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>196</v>
+        <v>134</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14275,7 +14407,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 33.8% (fair +196). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14302,21 +14434,23 @@
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees +1.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.6621</v>
+        <v>0.5720000000000001</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-196</v>
-      </c>
-      <c r="H74" s="15" t="n"/>
+        <v>-134</v>
+      </c>
+      <c r="H74" s="15" t="n">
+        <v>115</v>
+      </c>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
         <v/>
@@ -14339,7 +14473,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 66.2% (fair -196). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14351,37 +14485,37 @@
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>New York Yankees @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Boston Red Sox -1.5</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.495</v>
+        <v>0.3379615384615385</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>102</v>
+        <v>196</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14405,7 +14539,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 33.8% (fair +196). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14417,38 +14551,36 @@
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>New York Yankees @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>New York Yankees +1.5</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.505</v>
+        <v>0.6621</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-102</v>
-      </c>
-      <c r="H76" s="15" t="n">
-        <v>-127</v>
-      </c>
+        <v>-196</v>
+      </c>
+      <c r="H76" s="15" t="n"/>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
         <v/>
@@ -14471,7 +14603,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 50.5% (fair -102). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14488,12 +14620,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -14503,17 +14635,17 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.486036866359447</v>
+        <v>0.4677533039647577</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14537,7 +14669,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14554,12 +14686,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -14569,17 +14701,17 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5139346153846154</v>
+        <v>0.5322251101321587</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-106</v>
+        <v>-114</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-108</v>
+        <v>-127</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14603,7 +14735,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14620,12 +14752,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -14635,17 +14767,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4562605042016807</v>
+        <v>0.5033803921568627</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>119</v>
+        <v>-101</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>138</v>
+        <v>-104</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14669,7 +14801,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14686,12 +14818,12 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -14701,17 +14833,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5437587982832618</v>
+        <v>0.4966</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-119</v>
+        <v>101</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-133</v>
+        <v>100</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14735,7 +14867,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14752,12 +14884,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -14767,17 +14899,17 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.5117</v>
+        <v>0.4885</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>-105</v>
+        <v>105</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14801,7 +14933,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14818,12 +14950,12 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -14833,17 +14965,17 @@
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.4883</v>
+        <v>0.5115</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>105</v>
+        <v>-105</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-104</v>
+        <v>-127</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -14867,7 +14999,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14884,12 +15016,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -14899,17 +15031,17 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.4985096153846154</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-102</v>
+        <v>101</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14933,7 +15065,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14950,12 +15082,12 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -14965,17 +15097,17 @@
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.4955</v>
+        <v>0.5014941176470588</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>102</v>
+        <v>-101</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>144</v>
+        <v>-104</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -14999,7 +15131,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 50.1% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15016,7 +15148,7 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Washington Nationals @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -15031,17 +15163,17 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4967788461538462</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>101</v>
+        <v>-102</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15065,7 +15197,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15082,7 +15214,7 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Washington Nationals @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
@@ -15097,17 +15229,17 @@
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5031948356807512</v>
+        <v>0.4955</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-101</v>
+        <v>102</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-113</v>
+        <v>127</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15131,7 +15263,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15148,12 +15280,12 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -15163,17 +15295,17 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3578540772532189</v>
+        <v>0.4967788461538462</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>179</v>
+        <v>101</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -15197,7 +15329,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 35.8% (fair +179). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15214,12 +15346,12 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -15229,17 +15361,17 @@
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6421200000000001</v>
+        <v>0.5031948356807512</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-179</v>
+        <v>-101</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-150</v>
+        <v>-113</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15263,7 +15395,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -179). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15280,12 +15412,12 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -15295,17 +15427,17 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4338325991189427</v>
+        <v>0.3578540772532189</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>131</v>
+        <v>179</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15329,7 +15461,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 35.8% (fair +179). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15346,12 +15478,12 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -15361,17 +15493,17 @@
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5662058823529411</v>
+        <v>0.6421200000000001</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-131</v>
+        <v>-179</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-138</v>
+        <v>-150</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -15395,7 +15527,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 64.2% (fair -179). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15412,12 +15544,12 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -15427,17 +15559,17 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4967605633802817</v>
+        <v>0.4338325991189427</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -15461,7 +15593,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15478,12 +15610,12 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -15493,17 +15625,17 @@
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5032225225225225</v>
+        <v>0.5662058823529411</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-101</v>
+        <v>-131</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>-122</v>
+        <v>-138</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -15527,7 +15659,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15544,12 +15676,12 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -15559,17 +15691,17 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5260800000000001</v>
+        <v>0.4944700460829493</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-111</v>
+        <v>102</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>-150</v>
+        <v>117</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -15593,7 +15725,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15610,12 +15742,12 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -15625,17 +15757,17 @@
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.473920704845815</v>
+        <v>0.5055306306306306</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>111</v>
+        <v>-102</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>127</v>
+        <v>-122</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -15659,7 +15791,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15676,12 +15808,12 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -15691,16 +15823,18 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.5488</v>
+        <v>0.5260800000000001</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-122</v>
-      </c>
-      <c r="H95" s="15" t="n"/>
+        <v>-111</v>
+      </c>
+      <c r="H95" s="15" t="n">
+        <v>-150</v>
+      </c>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
         <v/>
@@ -15723,7 +15857,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 54.9% (fair -122). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15740,12 +15874,12 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -15755,16 +15889,18 @@
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.4512</v>
+        <v>0.473920704845815</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>122</v>
-      </c>
-      <c r="H96" s="15" t="n"/>
+        <v>111</v>
+      </c>
+      <c r="H96" s="15" t="n">
+        <v>127</v>
+      </c>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
         <v/>
@@ -15787,7 +15923,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 45.1% (fair +122). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15804,7 +15940,7 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Los Angeles Dodgers @ Athletics</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -15819,14 +15955,14 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4845</v>
+        <v>0.5462</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>106</v>
+        <v>-120</v>
       </c>
       <c r="H97" s="15" t="n"/>
       <c r="I97" s="13">
@@ -15851,7 +15987,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +106). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -15868,7 +16004,7 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>Los Angeles Dodgers @ Athletics</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
@@ -15883,14 +16019,14 @@
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5155</v>
+        <v>0.4538</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-106</v>
+        <v>120</v>
       </c>
       <c r="H98" s="15" t="n"/>
       <c r="I98" s="13">
@@ -15915,7 +16051,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 51.5% (fair -106). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -15932,7 +16068,7 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -15947,14 +16083,14 @@
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.5699</v>
+        <v>0.4819</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-133</v>
+        <v>108</v>
       </c>
       <c r="H99" s="15" t="n"/>
       <c r="I99" s="13">
@@ -15979,7 +16115,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -15996,7 +16132,7 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C100" s="20" t="inlineStr">
@@ -16011,14 +16147,14 @@
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.43</v>
+        <v>0.5181</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>133</v>
+        <v>-108</v>
       </c>
       <c r="H100" s="15" t="n"/>
       <c r="I100" s="13">
@@ -16043,7 +16179,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +133). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16052,9 +16188,137 @@
         <v/>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="inlineStr">
+        <is>
+          <t>San Francisco Giants</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="n">
+        <v>0.5699</v>
+      </c>
+      <c r="G101" s="14" t="n">
+        <v>-133</v>
+      </c>
+      <c r="H101" s="15" t="n"/>
+      <c r="I101" s="13">
+        <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
+        <v/>
+      </c>
+      <c r="J101" s="16">
+        <f>IF($H$101="","",$F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))</f>
+        <v/>
+      </c>
+      <c r="K101" s="17">
+        <f>IF($H$101="","",MAX(0,($F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))/IF($H$101&lt;0,-100/$H$101,$H$101/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L101" s="18">
+        <f>IF($H$101="","",ROUND(MIN($K$101,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M101" s="12">
+        <f>IF($J$101="","",IF($J$101&lt;0,"Pass",IF($J$101&lt;'Settings'!$B$4,"Thin",IF($J$101&lt;0.06,"✅ Sharp band",IF($J$101&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N101" s="19" t="inlineStr">
+        <is>
+          <t>Model 57.0% (fair -133). Your call.</t>
+        </is>
+      </c>
+      <c r="O101" s="15" t="n"/>
+      <c r="P101" s="16">
+        <f>IF(OR($H$101="",$O$101=""),"",(1+IF($H$101&lt;0,-100/$H$101,$H$101/100))/(1+IF($O$101&lt;0,-100/$O$101,$O$101/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B102" s="20" t="inlineStr">
+        <is>
+          <t>San Francisco Giants @ Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>01:40</t>
+        </is>
+      </c>
+      <c r="D102" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E102" s="20" t="inlineStr">
+        <is>
+          <t>Arizona Diamondbacks</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G102" s="14" t="n">
+        <v>133</v>
+      </c>
+      <c r="H102" s="15" t="n"/>
+      <c r="I102" s="13">
+        <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
+        <v/>
+      </c>
+      <c r="J102" s="16">
+        <f>IF($H$102="","",$F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))</f>
+        <v/>
+      </c>
+      <c r="K102" s="17">
+        <f>IF($H$102="","",MAX(0,($F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))/IF($H$102&lt;0,-100/$H$102,$H$102/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L102" s="18">
+        <f>IF($H$102="","",ROUND(MIN($K$102,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M102" s="12">
+        <f>IF($J$102="","",IF($J$102&lt;0,"Pass",IF($J$102&lt;'Settings'!$B$4,"Thin",IF($J$102&lt;0.06,"✅ Sharp band",IF($J$102&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N102" s="19" t="inlineStr">
+        <is>
+          <t>Model 43.0% (fair +133). Your call.</t>
+        </is>
+      </c>
+      <c r="O102" s="15" t="n"/>
+      <c r="P102" s="16">
+        <f>IF(OR($H$102="",$O$102=""),"",(1+IF($H$102&lt;0,-100/$H$102,$H$102/100))/(1+IF($O$102&lt;0,-100/$O$102,$O$102/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J100">
+  <conditionalFormatting sqref="J5:J102">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -16220,13 +16484,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6232149606299213</v>
+        <v>0.6219600000000001</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-165</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-154</v>
+        <v>-150</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -16250,7 +16514,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 62.3% (fair -165). Your call.</t>
+          <t>Model 62.2% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -16286,7 +16550,7 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3767843137254902</v>
+        <v>0.3780392156862745</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>165</v>
@@ -16316,7 +16580,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 37.7% (fair +165). Your call.</t>
+          <t>Model 37.8% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -16348,17 +16612,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 177.5</t>
+          <t>Over 179.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4101</v>
+        <v>0.3591705069124424</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -16382,7 +16646,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 35.9% (fair +178). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -16414,17 +16678,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 177.5</t>
+          <t>Under 179.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5899</v>
+        <v>0.6408</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-144</v>
+        <v>-178</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -16448,7 +16712,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 64.1% (fair -178). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -16480,17 +16744,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Dallas Wings +2.5</t>
+          <t>Dallas Wings +3.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4447</v>
+        <v>0.4792</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -16514,7 +16778,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -16546,14 +16810,14 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -2.5</t>
+          <t>Minnesota Lynx -3.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5553</v>
+        <v>0.5207999999999999</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-125</v>
+        <v>-109</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>113</v>
@@ -16580,7 +16844,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -16616,13 +16880,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3070153846153846</v>
+        <v>0.3076780185758514</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -16646,7 +16910,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 30.7% (fair +226). Your call.</t>
+          <t>Model 30.8% (fair +225). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -16682,10 +16946,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6929825825825825</v>
+        <v>0.6923528528528529</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-226</v>
+        <v>-225</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-233</v>
@@ -16712,7 +16976,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 69.3% (fair -226). Your call.</t>
+          <t>Model 69.2% (fair -225). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -16876,17 +17140,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics -7.5</t>
+          <t>Washington Mystics -6.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4548847926267281</v>
+        <v>0.4796634615384615</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -16910,7 +17174,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 45.5% (fair +120). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -16942,17 +17206,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +7.5</t>
+          <t>Portland Fire +6.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5451403846153846</v>
+        <v>0.5203058823529411</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-120</v>
+        <v>-108</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -16976,7 +17240,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 54.5% (fair -120). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -17012,13 +17276,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.7403837837837838</v>
+        <v>0.738781690140845</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-285</v>
+        <v>-283</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-270</v>
+        <v>-255</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -17042,7 +17306,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 74.0% (fair -285). Your call.</t>
+          <t>Model 73.9% (fair -283). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -17078,10 +17342,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.2596111111111111</v>
+        <v>0.2611944444444445</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>260</v>
@@ -17108,7 +17372,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 26.0% (fair +285). Your call.</t>
+          <t>Model 26.1% (fair +283). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -17272,14 +17536,14 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky +5.5</t>
+          <t>Chicago Sky -1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4143</v>
+        <v>0.2046</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>141</v>
+        <v>389</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>117</v>
@@ -17306,7 +17570,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +141). Your call.</t>
+          <t>Model 20.5% (fair +389). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -17338,17 +17602,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces -5.5</t>
+          <t>Las Vegas Aces +1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5857</v>
+        <v>0.7954</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-141</v>
+        <v>-389</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -17372,7 +17636,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -141). Your call.</t>
+          <t>Model 79.5% (fair -389). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -17540,13 +17804,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5769059405940594</v>
+        <v>0.5769</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>-136</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -17612,7 +17876,7 @@
         <v>136</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -17744,7 +18008,7 @@
         <v>145</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>

--- a/data/output/workbook/2026-06-28.xlsx
+++ b/data/output/workbook/2026-06-28.xlsx
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9429750"/>
+    <ext cx="10125075" cy="9277350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28 06:29</t>
+          <t>2026-06-28 08:19</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4535,807 +4535,807 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies offense vs New York Mets defense</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="29" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies offense vs New York Mets defense</t>
+      <c r="A61" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B61" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C61" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D61" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E61" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F61" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G61" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H61" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I61" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J61" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K61" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L61" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M61" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N61" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O61" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P61" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q61" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B62" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C62" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D62" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E62" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F62" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G62" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H62" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I62" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J62" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K62" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L62" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M62" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N62" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O62" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P62" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q62" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C62" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="D62" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E62" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F62" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G62" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H62" s="36" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I62" s="32" t="inlineStr"/>
+      <c r="J62" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K62" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L62" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M62" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="N62" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O62" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P62" s="32" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="Q62" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B63" s="32" t="n">
-        <v>4.1</v>
+        <v>7.568</v>
       </c>
       <c r="C63" s="32" t="n">
-        <v>4.067</v>
+        <v>7.37</v>
       </c>
       <c r="D63" s="32" t="n">
-        <v>3.95</v>
+        <v>7.5</v>
       </c>
       <c r="E63" s="32" t="n">
-        <v>4.6</v>
+        <v>7.923</v>
       </c>
       <c r="F63" s="32" t="n">
-        <v>4.3</v>
+        <v>8</v>
       </c>
       <c r="G63" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H63" s="36" t="inlineStr">
-        <is>
-          <t>20th</t>
+        <v>5.8</v>
+      </c>
+      <c r="H63" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
         </is>
       </c>
       <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
+      <c r="J63" s="36" t="inlineStr">
+        <is>
+          <t>12th</t>
         </is>
       </c>
       <c r="K63" s="32" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="L63" s="32" t="n">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="M63" s="32" t="n">
-        <v>4.067</v>
+        <v>7.6</v>
       </c>
       <c r="N63" s="32" t="n">
-        <v>4.6</v>
+        <v>7.9</v>
       </c>
       <c r="O63" s="32" t="n">
-        <v>4.5</v>
+        <v>7.862</v>
       </c>
       <c r="P63" s="32" t="n">
-        <v>4.214</v>
+        <v>7.842</v>
       </c>
       <c r="Q63" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B64" s="32" t="n">
-        <v>7.568</v>
+        <v>1.135</v>
       </c>
       <c r="C64" s="32" t="n">
-        <v>7.37</v>
+        <v>1.148</v>
       </c>
       <c r="D64" s="32" t="n">
-        <v>7.5</v>
+        <v>1.222</v>
       </c>
       <c r="E64" s="32" t="n">
-        <v>7.923</v>
+        <v>1.385</v>
       </c>
       <c r="F64" s="32" t="n">
-        <v>8</v>
+        <v>1.333</v>
       </c>
       <c r="G64" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H64" s="34" t="inlineStr">
-        <is>
-          <t>25th</t>
+        <v>0.8</v>
+      </c>
+      <c r="H64" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
         </is>
       </c>
       <c r="I64" s="32" t="inlineStr"/>
-      <c r="J64" s="36" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K64" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L64" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="M64" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="N64" s="32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O64" s="32" t="n">
-        <v>7.862</v>
-      </c>
-      <c r="P64" s="32" t="n">
-        <v>7.842</v>
+      <c r="J64" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P64" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q64" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>1.135</v>
+        <v>8.568</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>1.148</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>1.222</v>
+        <v>8.611000000000001</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>1.385</v>
+        <v>9.077</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>1.333</v>
+        <v>9.555999999999999</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H65" s="36" t="inlineStr">
-        <is>
-          <t>16th</t>
+        <v>10.6</v>
+      </c>
+      <c r="H65" s="34" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J65" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L65" s="32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="M65" s="32" t="n">
+        <v>8.933</v>
+      </c>
+      <c r="N65" s="32" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="O65" s="32" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="P65" s="32" t="n">
+        <v>8.920999999999999</v>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B66" s="32" t="n">
-        <v>8.568</v>
+        <v>0.649</v>
       </c>
       <c r="C66" s="32" t="n">
-        <v>8.704000000000001</v>
+        <v>0.481</v>
       </c>
       <c r="D66" s="32" t="n">
-        <v>8.611000000000001</v>
+        <v>0.389</v>
       </c>
       <c r="E66" s="32" t="n">
-        <v>9.077</v>
+        <v>0.385</v>
       </c>
       <c r="F66" s="32" t="n">
-        <v>9.555999999999999</v>
+        <v>0.444</v>
       </c>
       <c r="G66" s="32" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H66" s="34" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr"/>
-      <c r="J66" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
+        <v>0.8</v>
+      </c>
+      <c r="H66" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J66" s="36" t="inlineStr">
+        <is>
+          <t>20th</t>
         </is>
       </c>
       <c r="K66" s="32" t="n">
-        <v>6.4</v>
+        <v>0.6</v>
       </c>
       <c r="L66" s="32" t="n">
-        <v>8.5</v>
+        <v>0.3</v>
       </c>
       <c r="M66" s="32" t="n">
-        <v>8.933</v>
+        <v>0.267</v>
       </c>
       <c r="N66" s="32" t="n">
-        <v>8.699999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="O66" s="32" t="n">
-        <v>8.69</v>
+        <v>0.379</v>
       </c>
       <c r="P66" s="32" t="n">
-        <v>8.920999999999999</v>
+        <v>0.474</v>
       </c>
       <c r="Q66" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H67" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J67" s="36" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="N67" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>New York Mets offense vs Philadelphia Phillies defense</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>New York Mets offense vs Philadelphia Phillies defense</t>
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B69" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C69" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D69" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E69" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F69" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I69" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J69" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K69" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L69" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M69" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N69" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O69" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P69" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q69" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>3.357</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>5.633</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>5.375</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>3.357</v>
+        <v>7.053</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>2.667</v>
+        <v>6.586</v>
       </c>
       <c r="D71" s="32" t="n">
-        <v>2.85</v>
+        <v>6.55</v>
       </c>
       <c r="E71" s="32" t="n">
-        <v>3</v>
+        <v>6.333</v>
       </c>
       <c r="F71" s="32" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="G71" s="32" t="n">
-        <v>2.8</v>
+        <v>5.8</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
-          <t>22nd</t>
+          <t>26th</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
       <c r="J71" s="33" t="inlineStr">
         <is>
-          <t>8th</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="K71" s="32" t="n">
-        <v>2.8</v>
+        <v>7.4</v>
       </c>
       <c r="L71" s="32" t="n">
-        <v>4.7</v>
+        <v>8.888999999999999</v>
       </c>
       <c r="M71" s="32" t="n">
-        <v>5.067</v>
+        <v>9.769</v>
       </c>
       <c r="N71" s="32" t="n">
-        <v>5.1</v>
+        <v>9.888999999999999</v>
       </c>
       <c r="O71" s="32" t="n">
-        <v>5.633</v>
+        <v>10.222</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>5.375</v>
+        <v>9.891999999999999</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.053</v>
+        <v>0.737</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>6.586</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D72" s="32" t="n">
-        <v>6.55</v>
+        <v>0.7</v>
       </c>
       <c r="E72" s="32" t="n">
-        <v>6.333</v>
+        <v>0.733</v>
       </c>
       <c r="F72" s="32" t="n">
-        <v>5.6</v>
+        <v>0.8</v>
       </c>
       <c r="G72" s="32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
+        <v>1.2</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L72" s="32" t="n">
-        <v>8.888999999999999</v>
-      </c>
-      <c r="M72" s="32" t="n">
-        <v>9.769</v>
-      </c>
-      <c r="N72" s="32" t="n">
-        <v>9.888999999999999</v>
-      </c>
-      <c r="O72" s="32" t="n">
-        <v>10.222</v>
-      </c>
-      <c r="P72" s="32" t="n">
-        <v>9.891999999999999</v>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P72" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.737</v>
+        <v>8.395</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>0.6899999999999999</v>
+        <v>8.448</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>0.7</v>
+        <v>8.85</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>0.733</v>
+        <v>8.867000000000001</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>0.8</v>
+        <v>9.5</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
+        <v>10</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>23rd</t>
         </is>
       </c>
       <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="L73" s="32" t="n">
+        <v>10.444</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>9.154</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>9.055999999999999</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>9.074</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>9.486000000000001</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>8.395</v>
+        <v>0.553</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>8.448</v>
+        <v>0.414</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>8.85</v>
+        <v>0.4</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>8.867000000000001</v>
+        <v>0.533</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>9.5</v>
+        <v>0.4</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="H74" s="34" t="inlineStr">
-        <is>
-          <t>23rd</t>
+        <v>0.8</v>
+      </c>
+      <c r="H74" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
       <c r="J74" s="33" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="L74" s="32" t="n">
-        <v>10.444</v>
+        <v>0.556</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>9.154</v>
+        <v>0.615</v>
       </c>
       <c r="N74" s="32" t="n">
-        <v>9.055999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>9.074</v>
+        <v>0.519</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>9.486000000000001</v>
+        <v>0.595</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H75" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7972,7 +7972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8116,13 +8116,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.5769</v>
+        <v>0.5769059405940594</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-136</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8314,13 +8314,13 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5835634615384615</v>
+        <v>0.5862737089201878</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-140</v>
+        <v>-142</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-108</v>
+        <v>-113</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8361,32 +8361,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Over 179.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.3886330935251798</v>
+        <v>0.526298076923077</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>157</v>
+        <v>-111</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 38.9% (fair +157). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8422,17 +8422,17 @@
     <row r="10">
       <c r="A10" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -8442,17 +8442,17 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.473920704845815</v>
+        <v>0.3882014388489208</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 38.8% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8488,37 +8488,37 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5264705882352941</v>
+        <v>0.473920704845815</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-111</v>
+        <v>111</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8554,37 +8554,37 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5263235294117647</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-111</v>
+        <v>-181</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>104</v>
+        <v>-150</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 64.5% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8620,17 +8620,17 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8640,17 +8640,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4877272727272727</v>
+        <v>0.4944700460829493</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8686,17 +8686,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Texas Rangers @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8706,17 +8706,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4944700460829493</v>
+        <v>0.4873853211009175</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8757,12 +8757,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -8772,17 +8772,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.6421200000000001</v>
+        <v>0.4677533039647577</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-179</v>
+        <v>114</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>-150</v>
+        <v>127</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -179). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8818,17 +8818,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8838,17 +8838,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4677533039647577</v>
+        <v>0.52885</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>114</v>
+        <v>-112</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8889,12 +8889,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8904,17 +8904,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.52885</v>
+        <v>0.4366806722689076</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-112</v>
+        <v>129</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -8965,22 +8965,22 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5410384615384616</v>
+        <v>0.3847777777777777</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-118</v>
+        <v>160</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-108</v>
+        <v>170</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 38.5% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9021,32 +9021,32 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Over 7.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4366806722689076</v>
+        <v>0.5390653846153846</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>129</v>
+        <v>-117</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>138</v>
+        <v>-108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 53.9% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9082,17 +9082,17 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9102,17 +9102,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.3847777777777777</v>
+        <v>0.4985096153846154</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>160</v>
+        <v>101</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 38.5% (fair +160). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9148,37 +9148,37 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5390653846153846</v>
+        <v>0.4967788461538462</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-117</v>
+        <v>101</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>-108</v>
+        <v>108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9214,17 +9214,17 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9234,17 +9234,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Las Vegas Aces</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4985096153846154</v>
+        <v>0.733295652173913</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>101</v>
+        <v>-275</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>108</v>
+        <v>-245</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 73.3% (fair -275). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9285,12 +9285,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ Dallas Wings</t>
+          <t>Houston Astros @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -9300,17 +9300,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.6219600000000001</v>
+        <v>0.4708675799086758</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-165</v>
+        <v>112</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-150</v>
+        <v>119</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -165). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9351,12 +9351,12 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Detroit Tigers</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -9366,17 +9366,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4707727272727273</v>
+        <v>0.5768709251101322</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>112</v>
+        <v>-136</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>120</v>
+        <v>-127</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9412,17 +9412,17 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Minnesota Lynx @ Dallas Wings</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -9432,17 +9432,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.4967788461538462</v>
+        <v>0.6238171875</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>101</v>
+        <v>-166</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>108</v>
+        <v>-156</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 62.4% (fair -166). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9475,273 +9475,9 @@
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>Chicago White Sox</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>0.5768709251101322</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>-136</v>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>-127</v>
-      </c>
-      <c r="I26" s="13">
-        <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
-        <v/>
-      </c>
-      <c r="J26" s="16">
-        <f>IF($H$26="","",$F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))</f>
-        <v/>
-      </c>
-      <c r="K26" s="17">
-        <f>IF($H$26="","",MAX(0,($F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))/IF($H$26&lt;0,-100/$H$26,$H$26/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L26" s="18">
-        <f>IF($H$26="","",ROUND(MIN($K$26,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M26" s="12">
-        <f>IF($J$26="","",IF($J$26&lt;0,"Pass",IF($J$26&lt;'Settings'!$B$4,"Thin",IF($J$26&lt;0.06,"✅ Sharp band",IF($J$26&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N26" s="19" t="inlineStr">
-        <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
-        </is>
-      </c>
-      <c r="O26" s="15" t="n"/>
-      <c r="P26" s="16">
-        <f>IF(OR($H$26="",$O$26=""),"",(1+IF($H$26&lt;0,-100/$H$26,$H$26/100))/(1+IF($O$26&lt;0,-100/$O$26,$O$26/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>Las Vegas Aces</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>0.738781690140845</v>
-      </c>
-      <c r="G27" s="14" t="n">
-        <v>-283</v>
-      </c>
-      <c r="H27" s="15" t="n">
-        <v>-255</v>
-      </c>
-      <c r="I27" s="13">
-        <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
-        <v/>
-      </c>
-      <c r="J27" s="16">
-        <f>IF($H$27="","",$F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))</f>
-        <v/>
-      </c>
-      <c r="K27" s="17">
-        <f>IF($H$27="","",MAX(0,($F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))/IF($H$27&lt;0,-100/$H$27,$H$27/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L27" s="18">
-        <f>IF($H$27="","",ROUND(MIN($K$27,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M27" s="12">
-        <f>IF($J$27="","",IF($J$27&lt;0,"Pass",IF($J$27&lt;'Settings'!$B$4,"Thin",IF($J$27&lt;0.06,"✅ Sharp band",IF($J$27&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N27" s="19" t="inlineStr">
-        <is>
-          <t>Model 73.9% (fair -283). Your call.</t>
-        </is>
-      </c>
-      <c r="O27" s="15" t="n"/>
-      <c r="P27" s="16">
-        <f>IF(OR($H$27="",$O$27=""),"",(1+IF($H$27&lt;0,-100/$H$27,$H$27/100))/(1+IF($O$27&lt;0,-100/$O$27,$O$27/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>Chicago Cubs +1.5</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>0.5316403846153847</v>
-      </c>
-      <c r="G28" s="14" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H28" s="15" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I28" s="13">
-        <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
-        <v/>
-      </c>
-      <c r="J28" s="16">
-        <f>IF($H$28="","",$F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))</f>
-        <v/>
-      </c>
-      <c r="K28" s="17">
-        <f>IF($H$28="","",MAX(0,($F$28*IF($H$28&lt;0,-100/$H$28,$H$28/100)-(1-$F$28))/IF($H$28&lt;0,-100/$H$28,$H$28/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L28" s="18">
-        <f>IF($H$28="","",ROUND(MIN($K$28,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M28" s="12">
-        <f>IF($J$28="","",IF($J$28&lt;0,"Pass",IF($J$28&lt;'Settings'!$B$4,"Thin",IF($J$28&lt;0.06,"✅ Sharp band",IF($J$28&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N28" s="19" t="inlineStr">
-        <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
-        </is>
-      </c>
-      <c r="O28" s="15" t="n"/>
-      <c r="P28" s="16">
-        <f>IF(OR($H$28="",$O$28=""),"",(1+IF($H$28&lt;0,-100/$H$28,$H$28/100))/(1+IF($O$28&lt;0,-100/$O$28,$O$28/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies @ New York Mets</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Spread</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>New York Mets +1.5</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>0.561035135135135</v>
-      </c>
-      <c r="G29" s="14" t="n">
-        <v>-128</v>
-      </c>
-      <c r="H29" s="15" t="n">
-        <v>-122</v>
-      </c>
-      <c r="I29" s="13">
-        <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
-        <v/>
-      </c>
-      <c r="J29" s="16">
-        <f>IF($H$29="","",$F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))</f>
-        <v/>
-      </c>
-      <c r="K29" s="17">
-        <f>IF($H$29="","",MAX(0,($F$29*IF($H$29&lt;0,-100/$H$29,$H$29/100)-(1-$F$29))/IF($H$29&lt;0,-100/$H$29,$H$29/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L29" s="18">
-        <f>IF($H$29="","",ROUND(MIN($K$29,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M29" s="12">
-        <f>IF($J$29="","",IF($J$29&lt;0,"Pass",IF($J$29&lt;'Settings'!$B$4,"Thin",IF($J$29&lt;0.06,"✅ Sharp band",IF($J$29&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N29" s="19" t="inlineStr">
-        <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
-        </is>
-      </c>
-      <c r="O29" s="15" t="n"/>
-      <c r="P29" s="16">
-        <f>IF(OR($H$29="",$O$29=""),"",(1+IF($H$29&lt;0,-100/$H$29,$H$29/100))/(1+IF($O$29&lt;0,-100/$O$29,$O$29/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J29">
+  <conditionalFormatting sqref="J5:J25">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -9763,7 +9499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P102"/>
+  <dimension ref="A1:P100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9907,13 +9643,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.3495289855072464</v>
+        <v>0.3512132352941177</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9937,7 +9673,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 35.0% (fair +186). Your call.</t>
+          <t>Model 35.1% (fair +185). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9973,10 +9709,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.650468345323741</v>
+        <v>0.6488035971223022</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-186</v>
+        <v>-185</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-178</v>
@@ -10003,7 +9739,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.0% (fair -186). Your call.</t>
+          <t>Model 64.9% (fair -185). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10045,7 +9781,7 @@
         <v>-136</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -10111,7 +9847,7 @@
         <v>136</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -10243,7 +9979,7 @@
         <v>116</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -10441,7 +10177,7 @@
         <v>-116</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10507,7 +10243,7 @@
         <v>116</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10639,7 +10375,7 @@
         <v>136</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-121</v>
+        <v>-122</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10699,13 +10435,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4877272727272727</v>
+        <v>0.4873853211009175</v>
       </c>
       <c r="G17" s="14" t="n">
         <v>105</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10729,7 +10465,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 48.7% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10765,13 +10501,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5122658986175115</v>
+        <v>0.5126181818181818</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>-105</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-117</v>
+        <v>-120</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -10795,7 +10531,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 51.3% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10831,13 +10567,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5264705882352941</v>
+        <v>0.5578</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-111</v>
+        <v>-126</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10861,7 +10597,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10897,13 +10633,13 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.47355</v>
+        <v>0.4422</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10927,7 +10663,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -11035,7 +10771,7 @@
         <v>-180</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-124</v>
+        <v>165</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -11095,13 +10831,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5292244343891404</v>
+        <v>0.5291612612612613</v>
       </c>
       <c r="G23" s="14" t="n">
         <v>-112</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-121</v>
+        <v>-122</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -11161,13 +10897,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4707727272727273</v>
+        <v>0.4708675799086758</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>112</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11299,7 +11035,7 @@
         <v>123</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11487,17 +11223,17 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4589523809523809</v>
+        <v>0.3629</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>118</v>
+        <v>176</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11521,7 +11257,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 36.3% (fair +176). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11553,14 +11289,14 @@
       </c>
       <c r="E30" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5410384615384616</v>
+        <v>0.6371</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-118</v>
+        <v>-176</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>-108</v>
@@ -11587,7 +11323,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 63.7% (fair -176). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -12151,13 +11887,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.577168085106383</v>
+        <v>0.5764094420600858</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-137</v>
+        <v>-136</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-135</v>
+        <v>-133</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -12181,7 +11917,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -137). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12217,10 +11953,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4228326180257511</v>
+        <v>0.4236051502145923</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>133</v>
@@ -12247,7 +11983,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +137). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12289,7 +12025,7 @@
         <v>136</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12355,7 +12091,7 @@
         <v>-136</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12396,32 +12132,32 @@
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ New York Mets</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.561035135135135</v>
+        <v>0.4366806722689076</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-128</v>
+        <v>129</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-122</v>
+        <v>138</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12445,7 +12181,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 56.1% (fair -128). Your call.</t>
+          <t>Model 43.7% (fair +129). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12462,32 +12198,32 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ New York Mets</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E44" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies -1.5</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4389545454545454</v>
+        <v>0.5633067226890757</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>128</v>
+        <v>-129</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>120</v>
+        <v>-138</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12511,7 +12247,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 43.9% (fair +128). Your call.</t>
+          <t>Model 56.3% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12538,22 +12274,22 @@
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.4366806722689076</v>
+        <v>0.5232</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>129</v>
+        <v>-110</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12577,7 +12313,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12604,22 +12340,22 @@
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E46" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5633067226890757</v>
+        <v>0.4768</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-129</v>
+        <v>110</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-138</v>
+        <v>117</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12643,7 +12379,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12670,22 +12406,22 @@
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Over 9.5</t>
+          <t>Minnesota Twins -1.5</t>
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.5232</v>
+        <v>0.421</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>-110</v>
+        <v>138</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12709,7 +12445,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 42.1% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12736,22 +12472,22 @@
       </c>
       <c r="D48" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E48" s="20" t="inlineStr">
         <is>
-          <t>Under 9.5</t>
+          <t>Colorado Rockies +1.5</t>
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.4768</v>
+        <v>0.579</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>110</v>
+        <v>-138</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>120</v>
+        <v>-107</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12775,7 +12511,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 57.9% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12792,7 +12528,7 @@
       </c>
       <c r="B49" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
@@ -12802,22 +12538,22 @@
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins -1.5</t>
+          <t>Kansas City Royals</t>
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.421</v>
+        <v>0.4231111111111111</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12841,7 +12577,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +138). Your call.</t>
+          <t>Model 42.3% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12858,7 +12594,7 @@
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
@@ -12868,22 +12604,22 @@
       </c>
       <c r="D50" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E50" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies +1.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.579</v>
+        <v>0.5768709251101322</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-138</v>
+        <v>-136</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-110</v>
+        <v>-127</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12907,7 +12643,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -138). Your call.</t>
+          <t>Model 57.7% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12934,22 +12670,22 @@
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4231111111111111</v>
+        <v>0.5663</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>136</v>
+        <v>-131</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12973,7 +12709,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13000,22 +12736,22 @@
       </c>
       <c r="D52" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5768709251101322</v>
+        <v>0.4337</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-136</v>
+        <v>131</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>-127</v>
+        <v>113</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -13039,7 +12775,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13066,22 +12802,22 @@
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Chicago White Sox -1.5</t>
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.5663</v>
+        <v>0.4723</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>-131</v>
+        <v>112</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13105,7 +12841,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 47.2% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13132,22 +12868,22 @@
       </c>
       <c r="D54" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E54" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Kansas City Royals +1.5</t>
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.4337</v>
+        <v>0.5277000000000001</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>131</v>
+        <v>-112</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>115</v>
+        <v>-118</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13171,7 +12907,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 52.8% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13188,7 +12924,7 @@
       </c>
       <c r="B55" s="12" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
@@ -13198,22 +12934,22 @@
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox -1.5</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4723</v>
+        <v>0.3882014388489208</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13237,7 +12973,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 47.2% (fair +112). Your call.</t>
+          <t>Model 38.8% (fair +158). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13254,7 +12990,7 @@
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
@@ -13264,22 +13000,22 @@
       </c>
       <c r="D56" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E56" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals +1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5277000000000001</v>
+        <v>0.6118297872340425</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-112</v>
+        <v>-158</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-118</v>
+        <v>-182</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13303,7 +13039,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 52.8% (fair -112). Your call.</t>
+          <t>Model 61.2% (fair -158). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13330,22 +13066,22 @@
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.3886330935251798</v>
+        <v>0.5941</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>157</v>
+        <v>-146</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13369,7 +13105,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 38.9% (fair +157). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13396,22 +13132,22 @@
       </c>
       <c r="D58" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E58" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.6113571428571428</v>
+        <v>0.4059</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-157</v>
+        <v>146</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>-180</v>
+        <v>120</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13435,7 +13171,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13462,22 +13198,22 @@
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5941</v>
+        <v>0.4565437788018433</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-146</v>
+        <v>119</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -13501,7 +13237,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 59.4% (fair -146). Your call.</t>
+          <t>Model 45.7% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13528,22 +13264,22 @@
       </c>
       <c r="D60" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E60" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Chicago Cubs +1.5</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4059</v>
+        <v>0.5434299539170507</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>146</v>
+        <v>-119</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>114</v>
+        <v>-117</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -13567,7 +13303,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 40.6% (fair +146). Your call.</t>
+          <t>Model 54.3% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13584,33 +13320,31 @@
       </c>
       <c r="B61" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Miami Marlins @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.4683414634146342</v>
+        <v>0.4834</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>114</v>
-      </c>
-      <c r="H61" s="15" t="n">
-        <v>105</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="H61" s="15" t="n"/>
       <c r="I61" s="13">
         <f>IF($H$61="","",IF($H$61&lt;0,-$H$61/(-$H$61+100),100/($H$61+100)))</f>
         <v/>
@@ -13633,7 +13367,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 48.3% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13650,33 +13384,31 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Miami Marlins @ St. Louis Cardinals</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="D62" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E62" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs +1.5</t>
+          <t>St. Louis Cardinals</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5316403846153847</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H62" s="15" t="n">
-        <v>-108</v>
-      </c>
+        <v>-107</v>
+      </c>
+      <c r="H62" s="15" t="n"/>
       <c r="I62" s="13">
         <f>IF($H$62="","",IF($H$62&lt;0,-$H$62/(-$H$62+100),100/($H$62+100)))</f>
         <v/>
@@ -13699,7 +13431,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 51.7% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13716,12 +13448,12 @@
       </c>
       <c r="B63" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ St. Louis Cardinals</t>
+          <t>Athletics @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -13731,14 +13463,14 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.4834</v>
+        <v>0.4649</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13">
@@ -13763,7 +13495,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13780,12 +13512,12 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ St. Louis Cardinals</t>
+          <t>Athletics @ Los Angeles Angels</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="D64" s="20" t="inlineStr">
@@ -13795,14 +13527,14 @@
       </c>
       <c r="E64" s="20" t="inlineStr">
         <is>
-          <t>St. Louis Cardinals</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5351</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-107</v>
+        <v>-115</v>
       </c>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="13">
@@ -13827,7 +13559,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13844,12 +13576,12 @@
       </c>
       <c r="B65" s="12" t="inlineStr">
         <is>
-          <t>Athletics @ Los Angeles Angels</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -13859,14 +13591,14 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Atlanta Braves</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.4649</v>
+        <v>0.521</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>115</v>
+        <v>-109</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13891,7 +13623,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 52.1% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13908,12 +13640,12 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Athletics @ Los Angeles Angels</t>
+          <t>Atlanta Braves @ San Francisco Giants</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="D66" s="20" t="inlineStr">
@@ -13923,14 +13655,14 @@
       </c>
       <c r="E66" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.5351</v>
+        <v>0.479</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-115</v>
+        <v>109</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13955,7 +13687,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13972,12 +13704,12 @@
       </c>
       <c r="B67" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ San Francisco Giants</t>
+          <t>Los Angeles Dodgers @ San Diego Padres</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -13987,14 +13719,14 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Atlanta Braves</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.521</v>
+        <v>0.5511</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-109</v>
+        <v>-123</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -14019,7 +13751,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14036,12 +13768,12 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Atlanta Braves @ San Francisco Giants</t>
+          <t>Los Angeles Dodgers @ San Diego Padres</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="D68" s="20" t="inlineStr">
@@ -14051,14 +13783,14 @@
       </c>
       <c r="E68" s="20" t="inlineStr">
         <is>
-          <t>San Francisco Giants</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.479</v>
+        <v>0.4489</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -14083,7 +13815,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14100,12 +13832,12 @@
       </c>
       <c r="B69" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ San Diego Padres</t>
+          <t>New York Yankees @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -14115,14 +13847,14 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5511</v>
+        <v>0.5324</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>-123</v>
+        <v>-114</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14147,7 +13879,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14164,12 +13896,12 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ San Diego Padres</t>
+          <t>New York Yankees @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="D70" s="20" t="inlineStr">
@@ -14179,16 +13911,18 @@
       </c>
       <c r="E70" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4489</v>
+        <v>0.4676061674008811</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>123</v>
-      </c>
-      <c r="H70" s="15" t="n"/>
+        <v>114</v>
+      </c>
+      <c r="H70" s="15" t="n">
+        <v>-127</v>
+      </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
         <v/>
@@ -14211,7 +13945,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14238,21 +13972,23 @@
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.5324</v>
+        <v>0.428</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>-114</v>
-      </c>
-      <c r="H71" s="15" t="n"/>
+        <v>134</v>
+      </c>
+      <c r="H71" s="15" t="n">
+        <v>108</v>
+      </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
         <v/>
@@ -14275,7 +14011,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14302,22 +14038,22 @@
       </c>
       <c r="D72" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.4676061674008811</v>
+        <v>0.5720000000000001</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>114</v>
+        <v>-134</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>-127</v>
+        <v>113</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14341,7 +14077,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14368,22 +14104,22 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Boston Red Sox -1.5</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.428</v>
+        <v>0.33796875</v>
       </c>
       <c r="G73" s="14" t="n">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14407,7 +14143,7 @@
       </c>
       <c r="N73" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 33.8% (fair +196). Your call.</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -14434,23 +14170,21 @@
       </c>
       <c r="D74" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E74" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>New York Yankees +1.5</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.6621</v>
       </c>
       <c r="G74" s="14" t="n">
-        <v>-134</v>
-      </c>
-      <c r="H74" s="15" t="n">
-        <v>115</v>
-      </c>
+        <v>-196</v>
+      </c>
+      <c r="H74" s="15" t="n"/>
       <c r="I74" s="13">
         <f>IF($H$74="","",IF($H$74&lt;0,-$H$74/(-$H$74+100),100/($H$74+100)))</f>
         <v/>
@@ -14473,7 +14207,7 @@
       </c>
       <c r="N74" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 66.2% (fair -196). Your call.</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -14485,37 +14219,37 @@
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>New York Yankees @ Boston Red Sox</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Boston Red Sox -1.5</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.3379615384615385</v>
+        <v>0.4677533039647577</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>196</v>
+        <v>114</v>
       </c>
       <c r="H75" s="15" t="n">
-        <v>160</v>
+        <v>127</v>
       </c>
       <c r="I75" s="13">
         <f>IF($H$75="","",IF($H$75&lt;0,-$H$75/(-$H$75+100),100/($H$75+100)))</f>
@@ -14539,7 +14273,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 33.8% (fair +196). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14551,36 +14285,38 @@
     <row r="76">
       <c r="A76" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B76" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees @ Boston Red Sox</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D76" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees +1.5</t>
+          <t>Baltimore Orioles</t>
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.6621</v>
+        <v>0.5322251101321587</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-196</v>
-      </c>
-      <c r="H76" s="15" t="n"/>
+        <v>-114</v>
+      </c>
+      <c r="H76" s="15" t="n">
+        <v>-127</v>
+      </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
         <v/>
@@ -14603,7 +14339,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 66.2% (fair -196). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14620,12 +14356,12 @@
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -14635,17 +14371,17 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4677533039647577</v>
+        <v>0.5033803921568627</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>114</v>
+        <v>-101</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>127</v>
+        <v>-104</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14669,7 +14405,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14686,12 +14422,12 @@
       </c>
       <c r="B78" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D78" s="20" t="inlineStr">
@@ -14701,17 +14437,17 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles</t>
+          <t>Philadelphia Phillies</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5322251101321587</v>
+        <v>0.4966</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-114</v>
+        <v>101</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>-127</v>
+        <v>100</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14735,7 +14471,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14752,12 +14488,12 @@
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -14767,17 +14503,17 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.5033803921568627</v>
+        <v>0.4885</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>-101</v>
+        <v>105</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>-104</v>
+        <v>138</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14801,7 +14537,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 48.9% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14818,12 +14554,12 @@
       </c>
       <c r="B80" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D80" s="20" t="inlineStr">
@@ -14833,17 +14569,17 @@
       </c>
       <c r="E80" s="20" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies</t>
+          <t>New York Yankees</t>
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.4966</v>
+        <v>0.5115</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>101</v>
+        <v>-105</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>100</v>
+        <v>-127</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14867,7 +14603,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 51.1% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14884,12 +14620,12 @@
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -14899,17 +14635,17 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4885</v>
+        <v>0.4985096153846154</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H81" s="15" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="I81" s="13">
         <f>IF($H$81="","",IF($H$81&lt;0,-$H$81/(-$H$81+100),100/($H$81+100)))</f>
@@ -14933,7 +14669,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14950,12 +14686,12 @@
       </c>
       <c r="B82" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D82" s="20" t="inlineStr">
@@ -14965,17 +14701,17 @@
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>New York Yankees</t>
+          <t>Toronto Blue Jays</t>
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5115</v>
+        <v>0.5014941176470588</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-105</v>
+        <v>-101</v>
       </c>
       <c r="H82" s="15" t="n">
-        <v>-127</v>
+        <v>-104</v>
       </c>
       <c r="I82" s="13">
         <f>IF($H$82="","",IF($H$82&lt;0,-$H$82/(-$H$82+100),100/($H$82+100)))</f>
@@ -14999,7 +14735,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 50.1% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15016,12 +14752,12 @@
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Washington Nationals @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -15031,17 +14767,17 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Washington Nationals</t>
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.4985096153846154</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>101</v>
+        <v>-102</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -15065,7 +14801,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15082,12 +14818,12 @@
       </c>
       <c r="B84" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Washington Nationals @ Boston Red Sox</t>
         </is>
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D84" s="20" t="inlineStr">
@@ -15097,17 +14833,17 @@
       </c>
       <c r="E84" s="20" t="inlineStr">
         <is>
-          <t>Toronto Blue Jays</t>
+          <t>Boston Red Sox</t>
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.5014941176470588</v>
+        <v>0.4955</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>-101</v>
+        <v>102</v>
       </c>
       <c r="H84" s="15" t="n">
-        <v>-104</v>
+        <v>127</v>
       </c>
       <c r="I84" s="13">
         <f>IF($H$84="","",IF($H$84&lt;0,-$H$84/(-$H$84+100),100/($H$84+100)))</f>
@@ -15131,7 +14867,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -101). Your call.</t>
+          <t>Model 49.5% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15148,7 +14884,7 @@
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
@@ -15163,17 +14899,17 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Washington Nationals</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.4967788461538462</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-102</v>
+        <v>101</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>186</v>
+        <v>108</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15197,7 +14933,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15214,7 +14950,7 @@
       </c>
       <c r="B86" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Boston Red Sox</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C86" s="20" t="inlineStr">
@@ -15229,17 +14965,17 @@
       </c>
       <c r="E86" s="20" t="inlineStr">
         <is>
-          <t>Boston Red Sox</t>
+          <t>Cleveland Guardians</t>
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4955</v>
+        <v>0.5031948356807512</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>102</v>
+        <v>-101</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>127</v>
+        <v>-113</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -15263,7 +14999,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15280,12 +15016,12 @@
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -15295,17 +15031,17 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Cincinnati Reds</t>
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.4967788461538462</v>
+        <v>0.3552941176470589</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>101</v>
+        <v>181</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -15329,7 +15065,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 35.5% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15346,12 +15082,12 @@
       </c>
       <c r="B88" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C88" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D88" s="20" t="inlineStr">
@@ -15361,17 +15097,17 @@
       </c>
       <c r="E88" s="20" t="inlineStr">
         <is>
-          <t>Cleveland Guardians</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.5031948356807512</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-101</v>
+        <v>-181</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-113</v>
+        <v>-150</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15395,7 +15131,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 64.5% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15412,12 +15148,12 @@
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -15427,17 +15163,17 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds</t>
+          <t>San Diego Padres</t>
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.3578540772532189</v>
+        <v>0.4338325991189427</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="H89" s="15" t="n">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="I89" s="13">
         <f>IF($H$89="","",IF($H$89&lt;0,-$H$89/(-$H$89+100),100/($H$89+100)))</f>
@@ -15461,7 +15197,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 35.8% (fair +179). Your call.</t>
+          <t>Model 43.4% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15478,12 +15214,12 @@
       </c>
       <c r="B90" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>San Diego Padres @ Chicago Cubs</t>
         </is>
       </c>
       <c r="C90" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="D90" s="20" t="inlineStr">
@@ -15493,17 +15229,17 @@
       </c>
       <c r="E90" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.6421200000000001</v>
+        <v>0.5662058823529411</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-179</v>
+        <v>-131</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-150</v>
+        <v>-138</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -15527,7 +15263,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 64.2% (fair -179). Your call.</t>
+          <t>Model 56.6% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15544,12 +15280,12 @@
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -15559,17 +15295,17 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>San Diego Padres</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4338325991189427</v>
+        <v>0.4944700460829493</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -15593,7 +15329,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15610,12 +15346,12 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>San Diego Padres @ Chicago Cubs</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D92" s="20" t="inlineStr">
@@ -15625,17 +15361,17 @@
       </c>
       <c r="E92" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Houston Astros</t>
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5662058823529411</v>
+        <v>0.5055306306306306</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-131</v>
+        <v>-102</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>-138</v>
+        <v>-122</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -15659,7 +15395,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 50.6% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15676,12 +15412,12 @@
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -15691,17 +15427,17 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Miami Marlins</t>
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.4944700460829493</v>
+        <v>0.5260800000000001</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>102</v>
+        <v>-111</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>117</v>
+        <v>-150</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -15725,7 +15461,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 52.6% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15742,12 +15478,12 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D94" s="20" t="inlineStr">
@@ -15757,17 +15493,17 @@
       </c>
       <c r="E94" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.5055306306306306</v>
+        <v>0.473920704845815</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-102</v>
+        <v>111</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>-122</v>
+        <v>127</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -15791,7 +15527,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 47.4% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15808,12 +15544,12 @@
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Los Angeles Dodgers @ Athletics</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -15823,18 +15559,16 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins</t>
+          <t>Los Angeles Dodgers</t>
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.5260800000000001</v>
+        <v>0.5462</v>
       </c>
       <c r="G95" s="14" t="n">
-        <v>-111</v>
-      </c>
-      <c r="H95" s="15" t="n">
-        <v>-150</v>
-      </c>
+        <v>-120</v>
+      </c>
+      <c r="H95" s="15" t="n"/>
       <c r="I95" s="13">
         <f>IF($H$95="","",IF($H$95&lt;0,-$H$95/(-$H$95+100),100/($H$95+100)))</f>
         <v/>
@@ -15857,7 +15591,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15874,12 +15608,12 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Los Angeles Dodgers @ Athletics</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D96" s="20" t="inlineStr">
@@ -15889,18 +15623,16 @@
       </c>
       <c r="E96" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Athletics</t>
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.473920704845815</v>
+        <v>0.4538</v>
       </c>
       <c r="G96" s="14" t="n">
-        <v>111</v>
-      </c>
-      <c r="H96" s="15" t="n">
-        <v>127</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="H96" s="15" t="n"/>
       <c r="I96" s="13">
         <f>IF($H$96="","",IF($H$96&lt;0,-$H$96/(-$H$96+100),100/($H$96+100)))</f>
         <v/>
@@ -15923,7 +15655,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15940,7 +15672,7 @@
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
@@ -15955,14 +15687,14 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers</t>
+          <t>Los Angeles Angels</t>
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.5462</v>
+        <v>0.4819</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>-120</v>
+        <v>108</v>
       </c>
       <c r="H97" s="15" t="n"/>
       <c r="I97" s="13">
@@ -15987,7 +15719,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 54.6% (fair -120). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16004,7 +15736,7 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>Los Angeles Angels @ Seattle Mariners</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
@@ -16019,14 +15751,14 @@
       </c>
       <c r="E98" s="20" t="inlineStr">
         <is>
-          <t>Athletics</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.4538</v>
+        <v>0.5181</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>120</v>
+        <v>-108</v>
       </c>
       <c r="H98" s="15" t="n"/>
       <c r="I98" s="13">
@@ -16051,7 +15783,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 45.4% (fair +120). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16068,7 +15800,7 @@
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>San Francisco Giants @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
@@ -16083,14 +15815,14 @@
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Angels</t>
+          <t>San Francisco Giants</t>
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.4819</v>
+        <v>0.5699</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>108</v>
+        <v>-133</v>
       </c>
       <c r="H99" s="15" t="n"/>
       <c r="I99" s="13">
@@ -16115,7 +15847,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 48.2% (fair +108). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16132,7 +15864,7 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>Los Angeles Angels @ Seattle Mariners</t>
+          <t>San Francisco Giants @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C100" s="20" t="inlineStr">
@@ -16147,14 +15879,14 @@
       </c>
       <c r="E100" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.5181</v>
+        <v>0.43</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>-108</v>
+        <v>133</v>
       </c>
       <c r="H100" s="15" t="n"/>
       <c r="I100" s="13">
@@ -16179,7 +15911,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 51.8% (fair -108). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16188,137 +15920,9 @@
         <v/>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B101" s="12" t="inlineStr">
-        <is>
-          <t>San Francisco Giants @ Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="C101" s="12" t="inlineStr">
-        <is>
-          <t>01:40</t>
-        </is>
-      </c>
-      <c r="D101" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="inlineStr">
-        <is>
-          <t>San Francisco Giants</t>
-        </is>
-      </c>
-      <c r="F101" s="13" t="n">
-        <v>0.5699</v>
-      </c>
-      <c r="G101" s="14" t="n">
-        <v>-133</v>
-      </c>
-      <c r="H101" s="15" t="n"/>
-      <c r="I101" s="13">
-        <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
-        <v/>
-      </c>
-      <c r="J101" s="16">
-        <f>IF($H$101="","",$F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))</f>
-        <v/>
-      </c>
-      <c r="K101" s="17">
-        <f>IF($H$101="","",MAX(0,($F$101*IF($H$101&lt;0,-100/$H$101,$H$101/100)-(1-$F$101))/IF($H$101&lt;0,-100/$H$101,$H$101/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L101" s="18">
-        <f>IF($H$101="","",ROUND(MIN($K$101,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M101" s="12">
-        <f>IF($J$101="","",IF($J$101&lt;0,"Pass",IF($J$101&lt;'Settings'!$B$4,"Thin",IF($J$101&lt;0.06,"✅ Sharp band",IF($J$101&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N101" s="19" t="inlineStr">
-        <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
-        </is>
-      </c>
-      <c r="O101" s="15" t="n"/>
-      <c r="P101" s="16">
-        <f>IF(OR($H$101="",$O$101=""),"",(1+IF($H$101&lt;0,-100/$H$101,$H$101/100))/(1+IF($O$101&lt;0,-100/$O$101,$O$101/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="B102" s="20" t="inlineStr">
-        <is>
-          <t>San Francisco Giants @ Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="C102" s="20" t="inlineStr">
-        <is>
-          <t>01:40</t>
-        </is>
-      </c>
-      <c r="D102" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E102" s="20" t="inlineStr">
-        <is>
-          <t>Arizona Diamondbacks</t>
-        </is>
-      </c>
-      <c r="F102" s="13" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G102" s="14" t="n">
-        <v>133</v>
-      </c>
-      <c r="H102" s="15" t="n"/>
-      <c r="I102" s="13">
-        <f>IF($H$102="","",IF($H$102&lt;0,-$H$102/(-$H$102+100),100/($H$102+100)))</f>
-        <v/>
-      </c>
-      <c r="J102" s="16">
-        <f>IF($H$102="","",$F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))</f>
-        <v/>
-      </c>
-      <c r="K102" s="17">
-        <f>IF($H$102="","",MAX(0,($F$102*IF($H$102&lt;0,-100/$H$102,$H$102/100)-(1-$F$102))/IF($H$102&lt;0,-100/$H$102,$H$102/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L102" s="18">
-        <f>IF($H$102="","",ROUND(MIN($K$102,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M102" s="12">
-        <f>IF($J$102="","",IF($J$102&lt;0,"Pass",IF($J$102&lt;'Settings'!$B$4,"Thin",IF($J$102&lt;0.06,"✅ Sharp band",IF($J$102&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N102" s="19" t="inlineStr">
-        <is>
-          <t>Model 43.0% (fair +133). Your call.</t>
-        </is>
-      </c>
-      <c r="O102" s="15" t="n"/>
-      <c r="P102" s="16">
-        <f>IF(OR($H$102="",$O$102=""),"",(1+IF($H$102&lt;0,-100/$H$102,$H$102/100))/(1+IF($O$102&lt;0,-100/$O$102,$O$102/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J102">
+  <conditionalFormatting sqref="J5:J100">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -16484,13 +16088,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6219600000000001</v>
+        <v>0.6238171875</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-165</v>
+        <v>-166</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-150</v>
+        <v>-156</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -16514,7 +16118,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 62.2% (fair -165). Your call.</t>
+          <t>Model 62.4% (fair -166). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -16550,10 +16154,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3780392156862745</v>
+        <v>0.3761960784313726</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>155</v>
@@ -16580,7 +16184,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 37.8% (fair +165). Your call.</t>
+          <t>Model 37.6% (fair +166). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -16880,13 +16484,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3076780185758514</v>
+        <v>0.3053939393939394</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -16910,7 +16514,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 30.8% (fair +225). Your call.</t>
+          <t>Model 30.5% (fair +227). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -16946,10 +16550,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6923528528528529</v>
+        <v>0.6945918918918919</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-225</v>
+        <v>-227</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-233</v>
@@ -16976,7 +16580,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 69.2% (fair -225). Your call.</t>
+          <t>Model 69.5% (fair -227). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -17140,17 +16744,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics -6.5</t>
+          <t>Washington Mystics -7.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4796634615384615</v>
+        <v>0.4395</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -17174,7 +16778,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 44.0% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -17206,14 +16810,14 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +6.5</t>
+          <t>Portland Fire +7.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5203058823529411</v>
+        <v>0.5605</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-108</v>
+        <v>-128</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-104</v>
@@ -17240,7 +16844,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 56.0% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -17276,13 +16880,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.738781690140845</v>
+        <v>0.733295652173913</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-283</v>
+        <v>-275</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-255</v>
+        <v>-245</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -17306,7 +16910,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 73.9% (fair -283). Your call.</t>
+          <t>Model 73.3% (fair -275). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -17342,13 +16946,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.2611944444444445</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -17372,7 +16976,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 26.1% (fair +283). Your call.</t>
+          <t>Model 26.7% (fair +275). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -17408,13 +17012,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5263235294117647</v>
+        <v>0.526298076923077</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>-111</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -17480,7 +17084,7 @@
         <v>111</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -17612,7 +17216,7 @@
         <v>-389</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -17672,10 +17276,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4164319248826291</v>
+        <v>0.4137558685446009</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>113</v>
@@ -17702,7 +17306,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 41.6% (fair +140). Your call.</t>
+          <t>Model 41.4% (fair +142). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -17738,13 +17342,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5835634615384615</v>
+        <v>0.5862737089201878</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-140</v>
+        <v>-142</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-108</v>
+        <v>-113</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -17768,7 +17372,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 58.4% (fair -140). Your call.</t>
+          <t>Model 58.6% (fair -142). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -17804,13 +17408,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5769</v>
+        <v>0.5769059405940594</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>-136</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -17876,7 +17480,7 @@
         <v>136</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -17942,7 +17546,7 @@
         <v>-145</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -18008,7 +17612,7 @@
         <v>145</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>

--- a/data/output/workbook/2026-06-28.xlsx
+++ b/data/output/workbook/2026-06-28.xlsx
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28 08:19</t>
+          <t>2026-06-28 10:51</t>
         </is>
       </c>
     </row>
@@ -7972,7 +7972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8097,32 +8097,32 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Over 163.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.5769059405940594</v>
+        <v>0.6281900900900901</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-136</v>
+        <v>-169</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-102</v>
+        <v>-122</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8146,7 +8146,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8158,17 +8158,17 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -8178,17 +8178,17 @@
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.628525</v>
+        <v>0.4701680672268908</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-169</v>
+        <v>113</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-124</v>
+        <v>138</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -169). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8229,12 +8229,12 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Washington Mystics</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8244,17 +8244,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 166.5</t>
+          <t>Over 164.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5774549019607843</v>
+        <v>0.5506435643564357</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-137</v>
+        <v>-123</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>-104</v>
+        <v>102</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -137). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8290,17 +8290,17 @@
     <row r="8">
       <c r="A8" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -8310,17 +8310,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Golden State Valkyries</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5862737089201878</v>
+        <v>0.6436134453781512</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-142</v>
+        <v>-181</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-113</v>
+        <v>-138</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8361,32 +8361,32 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Golden State Valkyries</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.526298076923077</v>
+        <v>0.5885549295774647</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-111</v>
+        <v>-143</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>108</v>
+        <v>-113</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8427,32 +8427,32 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Over 167.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.3882014388489208</v>
+        <v>0.5511731707317074</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>158</v>
+        <v>-123</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>178</v>
+        <v>-105</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8488,17 +8488,17 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Texas Rangers @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -8508,17 +8508,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.473920704845815</v>
+        <v>0.4842342342342343</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8559,12 +8559,12 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Minnesota Twins @ Houston Astros</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8574,17 +8574,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Minnesota Twins</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.4944700460829493</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-181</v>
+        <v>102</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-150</v>
+        <v>117</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 64.5% (fair -181). Your call.</t>
+          <t>Model 49.4% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8620,17 +8620,17 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8640,17 +8640,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4944700460829493</v>
+        <v>0.4286</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8691,12 +8691,12 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8706,17 +8706,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4873853211009175</v>
+        <v>0.53255</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>105</v>
+        <v>-114</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8757,12 +8757,12 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -8772,17 +8772,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4677533039647577</v>
+        <v>0.53215</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>114</v>
+        <v>-114</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>127</v>
+        <v>100</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8818,17 +8818,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8838,17 +8838,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.52885</v>
+        <v>0.4620264317180616</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-112</v>
+        <v>116</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8889,12 +8889,12 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8904,17 +8904,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4366806722689076</v>
+        <v>0.3857777777777778</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 38.6% (fair +159). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8950,17 +8950,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8970,17 +8970,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.3847777777777777</v>
+        <v>0.4994711538461538</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 38.5% (fair +160). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9016,37 +9016,37 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>New York Mets @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:07</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>New York Mets</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5390653846153846</v>
+        <v>0.4985096153846154</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-117</v>
+        <v>101</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-108</v>
+        <v>108</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 49.9% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9087,12 +9087,12 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -9102,17 +9102,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4985096153846154</v>
+        <v>0.4563876651982379</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9148,17 +9148,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9168,17 +9168,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4967788461538462</v>
+        <v>0.4045703125</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
+          <t>Houston Astros @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9234,17 +9234,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.733295652173913</v>
+        <v>0.4763594470046084</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-275</v>
+        <v>110</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>-245</v>
+        <v>117</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 73.3% (fair -275). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9285,32 +9285,32 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Houston Astros @ Detroit Tigers</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Portland Fire +6.5</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4708675799086758</v>
+        <v>0.5117326732673267</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>112</v>
+        <v>-105</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9370,13 +9370,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5768709251101322</v>
+        <v>0.5759203539823009</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>-136</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-127</v>
+        <v>-126</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9436,13 +9436,13 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.6238171875</v>
+        <v>0.6202444444444444</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-166</v>
+        <v>-163</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-156</v>
+        <v>-152</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 62.4% (fair -166). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9475,9 +9475,141 @@
         <v/>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces @ Chicago Sky</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>Las Vegas Aces</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>0.7361574229691876</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <v>-279</v>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>-257</v>
+      </c>
+      <c r="I26" s="13">
+        <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
+        <v/>
+      </c>
+      <c r="J26" s="16">
+        <f>IF($H$26="","",$F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))</f>
+        <v/>
+      </c>
+      <c r="K26" s="17">
+        <f>IF($H$26="","",MAX(0,($F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))/IF($H$26&lt;0,-100/$H$26,$H$26/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L26" s="18">
+        <f>IF($H$26="","",ROUND(MIN($K$26,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M26" s="12">
+        <f>IF($J$26="","",IF($J$26&lt;0,"Pass",IF($J$26&lt;'Settings'!$B$4,"Thin",IF($J$26&lt;0.06,"✅ Sharp band",IF($J$26&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>Model 73.6% (fair -279). Your call.</t>
+        </is>
+      </c>
+      <c r="O26" s="15" t="n"/>
+      <c r="P26" s="16">
+        <f>IF(OR($H$26="",$O$26=""),"",(1+IF($H$26&lt;0,-100/$H$26,$H$26/100))/(1+IF($O$26&lt;0,-100/$O$26,$O$26/100))-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="inlineStr">
+        <is>
+          <t>Washington Nationals @ Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Moneyline</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>Baltimore Orioles</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>0.6464544117647059</v>
+      </c>
+      <c r="G27" s="14" t="n">
+        <v>-183</v>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>-172</v>
+      </c>
+      <c r="I27" s="13">
+        <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
+        <v/>
+      </c>
+      <c r="J27" s="16">
+        <f>IF($H$27="","",$F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))</f>
+        <v/>
+      </c>
+      <c r="K27" s="17">
+        <f>IF($H$27="","",MAX(0,($F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))/IF($H$27&lt;0,-100/$H$27,$H$27/100))*'Settings'!$B$3)</f>
+        <v/>
+      </c>
+      <c r="L27" s="18">
+        <f>IF($H$27="","",ROUND(MIN($K$27,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
+        <v/>
+      </c>
+      <c r="M27" s="12">
+        <f>IF($J$27="","",IF($J$27&lt;0,"Pass",IF($J$27&lt;'Settings'!$B$4,"Thin",IF($J$27&lt;0.06,"✅ Sharp band",IF($J$27&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
+        <v/>
+      </c>
+      <c r="N27" s="19" t="inlineStr">
+        <is>
+          <t>Model 64.6% (fair -183). Your call.</t>
+        </is>
+      </c>
+      <c r="O27" s="15" t="n"/>
+      <c r="P27" s="16">
+        <f>IF(OR($H$27="",$O$27=""),"",(1+IF($H$27&lt;0,-100/$H$27,$H$27/100))/(1+IF($O$27&lt;0,-100/$O$27,$O$27/100))-1)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J25">
+  <conditionalFormatting sqref="J5:J27">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -9643,13 +9775,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.3512132352941177</v>
+        <v>0.3535185185185185</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9673,7 +9805,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 35.1% (fair +185). Your call.</t>
+          <t>Model 35.4% (fair +183). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9709,13 +9841,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6488035971223022</v>
+        <v>0.6464544117647059</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-185</v>
+        <v>-183</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-178</v>
+        <v>-172</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -9739,7 +9871,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 64.9% (fair -185). Your call.</t>
+          <t>Model 64.6% (fair -183). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -9781,7 +9913,7 @@
         <v>-136</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -9913,7 +10045,7 @@
         <v>-116</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -9979,7 +10111,7 @@
         <v>116</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -10039,13 +10171,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3714864864864865</v>
+        <v>0.3718385650224215</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>169</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -10069,7 +10201,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 37.1% (fair +169). Your call.</t>
+          <t>Model 37.2% (fair +169). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10105,13 +10237,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.628525</v>
+        <v>0.6281900900900901</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-169</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-124</v>
+        <v>-122</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -10135,7 +10267,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 62.9% (fair -169). Your call.</t>
+          <t>Model 62.8% (fair -169). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10167,7 +10299,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 9.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
@@ -10177,7 +10309,7 @@
         <v>-116</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10233,7 +10365,7 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 9.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
@@ -10243,7 +10375,7 @@
         <v>116</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10375,7 +10507,7 @@
         <v>136</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-122</v>
+        <v>-123</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10435,13 +10567,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4873853211009175</v>
+        <v>0.4842342342342343</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -10465,7 +10597,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 48.7% (fair +105). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10501,13 +10633,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5126181818181818</v>
+        <v>0.5157522522522523</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-105</v>
+        <v>-107</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -10531,7 +10663,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 51.3% (fair -105). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10573,7 +10705,7 @@
         <v>-126</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10639,7 +10771,7 @@
         <v>126</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10831,13 +10963,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5291612612612613</v>
+        <v>0.5236197183098591</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-112</v>
+        <v>-110</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-122</v>
+        <v>-113</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10861,7 +10993,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -10897,13 +11029,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4708675799086758</v>
+        <v>0.4763594470046084</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -10927,7 +11059,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11035,7 +11167,7 @@
         <v>123</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11095,10 +11227,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.52885</v>
+        <v>0.53255</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-112</v>
+        <v>-114</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>100</v>
@@ -11125,7 +11257,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 52.9% (fair -112). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11161,13 +11293,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4711098039215686</v>
+        <v>0.4674752475247525</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>-104</v>
+        <v>102</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11191,7 +11323,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 47.1% (fair +112). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11233,7 +11365,7 @@
         <v>176</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11299,7 +11431,7 @@
         <v>-176</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11431,7 +11563,7 @@
         <v>-244</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11491,10 +11623,10 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3847777777777777</v>
+        <v>0.3857777777777778</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H33" s="15" t="n">
         <v>170</v>
@@ -11521,7 +11653,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 38.5% (fair +160). Your call.</t>
+          <t>Model 38.6% (fair +159). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11557,13 +11689,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6152233576642336</v>
+        <v>0.6142037037037037</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-160</v>
+        <v>-159</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-174</v>
+        <v>-170</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11587,7 +11719,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 61.5% (fair -160). Your call.</t>
+          <t>Model 61.4% (fair -159). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11619,17 +11751,17 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Over 7.5</t>
+          <t>Over 8</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>0.5390653846153846</v>
+        <v>0.4802</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>-117</v>
+        <v>108</v>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-108</v>
+        <v>107</v>
       </c>
       <c r="I35" s="13">
         <f>IF($H$35="","",IF($H$35&lt;0,-$H$35/(-$H$35+100),100/($H$35+100)))</f>
@@ -11653,7 +11785,7 @@
       </c>
       <c r="N35" s="19" t="inlineStr">
         <is>
-          <t>Model 53.9% (fair -117). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -11685,17 +11817,17 @@
       </c>
       <c r="E36" s="20" t="inlineStr">
         <is>
-          <t>Under 7.5</t>
+          <t>Under 8</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>0.4609223300970874</v>
+        <v>0.5198</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>117</v>
+        <v>-108</v>
       </c>
       <c r="H36" s="15" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I36" s="13">
         <f>IF($H$36="","",IF($H$36&lt;0,-$H$36/(-$H$36+100),100/($H$36+100)))</f>
@@ -11719,7 +11851,7 @@
       </c>
       <c r="N36" s="19" t="inlineStr">
         <is>
-          <t>Model 46.1% (fair +117). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -11755,10 +11887,10 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4526</v>
+        <v>0.4498222222222222</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>125</v>
@@ -11785,7 +11917,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 45.3% (fair +121). Your call.</t>
+          <t>Model 45.0% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -11821,13 +11953,13 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5474</v>
+        <v>0.5501540540540542</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-121</v>
+        <v>-122</v>
       </c>
       <c r="H38" s="15" t="n">
-        <v>120</v>
+        <v>-122</v>
       </c>
       <c r="I38" s="13">
         <f>IF($H$38="","",IF($H$38&lt;0,-$H$38/(-$H$38+100),100/($H$38+100)))</f>
@@ -11851,7 +11983,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 54.7% (fair -121). Your call.</t>
+          <t>Model 55.0% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -11887,13 +12019,13 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5764094420600858</v>
+        <v>0.5788462184873949</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-136</v>
+        <v>-137</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>-133</v>
+        <v>-138</v>
       </c>
       <c r="I39" s="13">
         <f>IF($H$39="","",IF($H$39&lt;0,-$H$39/(-$H$39+100),100/($H$39+100)))</f>
@@ -11917,7 +12049,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 57.9% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -11953,13 +12085,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4236051502145923</v>
+        <v>0.4211538461538462</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -11983,7 +12115,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.1% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12025,7 +12157,7 @@
         <v>136</v>
       </c>
       <c r="H41" s="15" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="I41" s="13">
         <f>IF($H$41="","",IF($H$41&lt;0,-$H$41/(-$H$41+100),100/($H$41+100)))</f>
@@ -12091,7 +12223,7 @@
         <v>-136</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12151,13 +12283,13 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.4366806722689076</v>
+        <v>0.4286</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H43" s="15" t="n">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="I43" s="13">
         <f>IF($H$43="","",IF($H$43&lt;0,-$H$43/(-$H$43+100),100/($H$43+100)))</f>
@@ -12181,7 +12313,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 43.7% (fair +129). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12217,13 +12349,13 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.5633067226890757</v>
+        <v>0.5713967213114753</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>-129</v>
+        <v>-133</v>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="I44" s="13">
         <f>IF($H$44="","",IF($H$44&lt;0,-$H$44/(-$H$44+100),100/($H$44+100)))</f>
@@ -12247,7 +12379,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 56.3% (fair -129). Your call.</t>
+          <t>Model 57.1% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12289,7 +12421,7 @@
         <v>-110</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12355,7 +12487,7 @@
         <v>110</v>
       </c>
       <c r="H46" s="15" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="I46" s="13">
         <f>IF($H$46="","",IF($H$46&lt;0,-$H$46/(-$H$46+100),100/($H$46+100)))</f>
@@ -12421,7 +12553,7 @@
         <v>138</v>
       </c>
       <c r="H47" s="15" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I47" s="13">
         <f>IF($H$47="","",IF($H$47&lt;0,-$H$47/(-$H$47+100),100/($H$47+100)))</f>
@@ -12487,7 +12619,7 @@
         <v>-138</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>-107</v>
+        <v>101</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12547,13 +12679,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4231111111111111</v>
+        <v>0.4241071428571428</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>136</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12577,7 +12709,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12613,13 +12745,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5768709251101322</v>
+        <v>0.5759203539823009</v>
       </c>
       <c r="G50" s="14" t="n">
         <v>-136</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-127</v>
+        <v>-126</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12643,7 +12775,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12685,7 +12817,7 @@
         <v>-131</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12751,7 +12883,7 @@
         <v>131</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12817,7 +12949,7 @@
         <v>112</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -12943,13 +13075,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.3882014388489208</v>
+        <v>0.4045703125</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -12973,7 +13105,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 38.8% (fair +158). Your call.</t>
+          <t>Model 40.5% (fair +147). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13009,13 +13141,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.6118297872340425</v>
+        <v>0.5954203125</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-158</v>
+        <v>-147</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-182</v>
+        <v>-156</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13039,7 +13171,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 61.2% (fair -158). Your call.</t>
+          <t>Model 59.5% (fair -147). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13081,7 +13213,7 @@
         <v>-146</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13147,7 +13279,7 @@
         <v>146</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13207,13 +13339,13 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.4565437788018433</v>
+        <v>0.4523</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -13237,7 +13369,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 45.7% (fair +119). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13273,13 +13405,13 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.5434299539170507</v>
+        <v>0.5477000000000001</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>-119</v>
+        <v>-121</v>
       </c>
       <c r="H60" s="15" t="n">
-        <v>-117</v>
+        <v>104</v>
       </c>
       <c r="I60" s="13">
         <f>IF($H$60="","",IF($H$60&lt;0,-$H$60/(-$H$60+100),100/($H$60+100)))</f>
@@ -13303,7 +13435,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 54.3% (fair -119). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13915,13 +14047,13 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4676061674008811</v>
+        <v>0.4675938053097345</v>
       </c>
       <c r="G70" s="14" t="n">
         <v>114</v>
       </c>
       <c r="H70" s="15" t="n">
-        <v>-127</v>
+        <v>-126</v>
       </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
@@ -13987,7 +14119,7 @@
         <v>134</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -14053,7 +14185,7 @@
         <v>-134</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14113,13 +14245,13 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.33796875</v>
+        <v>0.3379615384615385</v>
       </c>
       <c r="G73" s="14" t="n">
         <v>196</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14243,10 +14375,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4677533039647577</v>
+        <v>0.4563876651982379</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H75" s="15" t="n">
         <v>127</v>
@@ -14273,7 +14405,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14309,13 +14441,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5322251101321587</v>
+        <v>0.5436504201680672</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-114</v>
+        <v>-119</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-127</v>
+        <v>-138</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14339,7 +14471,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14375,13 +14507,13 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.5033803921568627</v>
+        <v>0.53215</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-101</v>
+        <v>-114</v>
       </c>
       <c r="H77" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I77" s="13">
         <f>IF($H$77="","",IF($H$77&lt;0,-$H$77/(-$H$77+100),100/($H$77+100)))</f>
@@ -14405,7 +14537,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 53.2% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14441,10 +14573,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.4966</v>
+        <v>0.46785</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>100</v>
@@ -14471,7 +14603,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 46.8% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14507,13 +14639,13 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4885</v>
+        <v>0.4620264317180616</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14537,7 +14669,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +105). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14573,13 +14705,13 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5115</v>
+        <v>0.5379364806866953</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-105</v>
+        <v>-116</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>-127</v>
+        <v>-133</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14603,7 +14735,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -105). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14777,7 +14909,7 @@
         <v>-102</v>
       </c>
       <c r="H83" s="15" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="I83" s="13">
         <f>IF($H$83="","",IF($H$83&lt;0,-$H$83/(-$H$83+100),100/($H$83+100)))</f>
@@ -14903,10 +15035,10 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.4967788461538462</v>
+        <v>0.4994711538461538</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H85" s="15" t="n">
         <v>108</v>
@@ -14933,7 +15065,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 49.7% (fair +101). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -14969,13 +15101,13 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.5031948356807512</v>
+        <v>0.5005384615384615</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>-101</v>
+        <v>-100</v>
       </c>
       <c r="H86" s="15" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="I86" s="13">
         <f>IF($H$86="","",IF($H$86&lt;0,-$H$86/(-$H$86+100),100/($H$86+100)))</f>
@@ -14999,7 +15131,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 50.3% (fair -101). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15035,13 +15167,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3552941176470589</v>
+        <v>0.3563934426229509</v>
       </c>
       <c r="G87" s="14" t="n">
         <v>181</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -15065,7 +15197,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 35.5% (fair +181). Your call.</t>
+          <t>Model 35.6% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15101,13 +15233,13 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6436134453781512</v>
       </c>
       <c r="G88" s="14" t="n">
         <v>-181</v>
       </c>
       <c r="H88" s="15" t="n">
-        <v>-150</v>
+        <v>-138</v>
       </c>
       <c r="I88" s="13">
         <f>IF($H$88="","",IF($H$88&lt;0,-$H$88/(-$H$88+100),100/($H$88+100)))</f>
@@ -15131,7 +15263,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 64.5% (fair -181). Your call.</t>
+          <t>Model 64.4% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15167,10 +15299,10 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4338325991189427</v>
+        <v>0.435726872246696</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H89" s="15" t="n">
         <v>127</v>
@@ -15197,7 +15329,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 43.6% (fair +130). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15233,13 +15365,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5662058823529411</v>
+        <v>0.5642510729613734</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-131</v>
+        <v>-129</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -15263,7 +15395,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 56.4% (fair -129). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15431,13 +15563,13 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5260800000000001</v>
+        <v>0.5297901639344262</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-111</v>
+        <v>-113</v>
       </c>
       <c r="H93" s="15" t="n">
-        <v>-150</v>
+        <v>-144</v>
       </c>
       <c r="I93" s="13">
         <f>IF($H$93="","",IF($H$93&lt;0,-$H$93/(-$H$93+100),100/($H$93+100)))</f>
@@ -15461,7 +15593,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 53.0% (fair -113). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15497,13 +15629,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.473920704845815</v>
+        <v>0.4701680672268908</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -15527,7 +15659,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 47.0% (fair +113). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -16088,13 +16220,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6238171875</v>
+        <v>0.6202444444444444</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-166</v>
+        <v>-163</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-156</v>
+        <v>-152</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -16118,7 +16250,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 62.4% (fair -166). Your call.</t>
+          <t>Model 62.0% (fair -163). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -16154,13 +16286,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.3761960784313726</v>
+        <v>0.37976</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -16184,7 +16316,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 37.6% (fair +166). Your call.</t>
+          <t>Model 38.0% (fair +163). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -16216,17 +16348,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Over 178.5</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.3591705069124424</v>
+        <v>0.3844</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -16250,7 +16382,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 35.9% (fair +178). Your call.</t>
+          <t>Model 38.4% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -16282,17 +16414,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Under 179.5</t>
+          <t>Under 178.5</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6408</v>
+        <v>0.6155999999999999</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-178</v>
+        <v>-160</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -16316,7 +16448,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -178). Your call.</t>
+          <t>Model 61.6% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -16348,17 +16480,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Dallas Wings +3.5</t>
+          <t>Dallas Wings +2.5</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4792</v>
+        <v>0.4447</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -16382,7 +16514,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 44.5% (fair +125). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -16414,14 +16546,14 @@
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Lynx -3.5</t>
+          <t>Minnesota Lynx -2.5</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5207999999999999</v>
+        <v>0.5553</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-109</v>
+        <v>-125</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>113</v>
@@ -16448,7 +16580,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 55.5% (fair -125). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -16484,13 +16616,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3053939393939394</v>
+        <v>0.3044444444444445</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -16514,7 +16646,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 30.5% (fair +227). Your call.</t>
+          <t>Model 30.4% (fair +228). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -16550,10 +16682,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6945918918918919</v>
+        <v>0.6955714714714715</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-227</v>
+        <v>-228</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-233</v>
@@ -16580,7 +16712,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 69.5% (fair -227). Your call.</t>
+          <t>Model 69.6% (fair -228). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -16612,17 +16744,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Over 166.5</t>
+          <t>Over 167.5</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5774549019607843</v>
+        <v>0.5511731707317074</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-137</v>
+        <v>-123</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -16646,7 +16778,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -137). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -16678,17 +16810,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Under 166.5</t>
+          <t>Under 167.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4226</v>
+        <v>0.4488</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-104</v>
+        <v>-105</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -16712,7 +16844,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +137). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -16744,17 +16876,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Washington Mystics -7.5</t>
+          <t>Washington Mystics -6.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4395</v>
+        <v>0.48825</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -16778,7 +16910,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +128). Your call.</t>
+          <t>Model 48.8% (fair +105). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -16810,17 +16942,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +7.5</t>
+          <t>Portland Fire +6.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5605</v>
+        <v>0.5117326732673267</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-128</v>
+        <v>-105</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-104</v>
+        <v>102</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -16844,7 +16976,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -128). Your call.</t>
+          <t>Model 51.2% (fair -105). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -16880,13 +17012,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.733295652173913</v>
+        <v>0.7361574229691876</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-275</v>
+        <v>-279</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>-245</v>
+        <v>-257</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -16910,7 +17042,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 73.3% (fair -275). Your call.</t>
+          <t>Model 73.6% (fair -279). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -16946,13 +17078,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.2666666666666667</v>
+        <v>0.2638</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -16976,7 +17108,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 26.7% (fair +275). Your call.</t>
+          <t>Model 26.4% (fair +279). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -17008,14 +17140,14 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 179.5</t>
+          <t>Over 181.5</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.526298076923077</v>
+        <v>0.4731730769230769</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-111</v>
+        <v>111</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>108</v>
@@ -17042,7 +17174,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 52.6% (fair -111). Your call.</t>
+          <t>Model 47.3% (fair +111). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -17074,14 +17206,14 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 179.5</t>
+          <t>Under 181.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4737</v>
+        <v>0.5267999999999999</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>111</v>
+        <v>-111</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>108</v>
@@ -17108,7 +17240,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 47.4% (fair +111). Your call.</t>
+          <t>Model 52.7% (fair -111). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -17140,17 +17272,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Chicago Sky -1.5</t>
+          <t>Chicago Sky +5.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.2046</v>
+        <v>0.4143</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>389</v>
+        <v>141</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -17174,7 +17306,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 20.5% (fair +389). Your call.</t>
+          <t>Model 41.4% (fair +141). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -17206,17 +17338,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Las Vegas Aces +1.5</t>
+          <t>Las Vegas Aces -5.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.7954</v>
+        <v>0.5857</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-389</v>
+        <v>-141</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -17240,7 +17372,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 79.5% (fair -389). Your call.</t>
+          <t>Model 58.6% (fair -141). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -17276,13 +17408,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.4137558685446009</v>
+        <v>0.4114285714285715</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -17306,7 +17438,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 41.1% (fair +143). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -17342,10 +17474,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5862737089201878</v>
+        <v>0.5885549295774647</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-142</v>
+        <v>-143</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>-113</v>
@@ -17372,7 +17504,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -17404,17 +17536,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 163.5</t>
+          <t>Over 164.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5769059405940594</v>
+        <v>0.5506435643564357</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-136</v>
+        <v>-123</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-102</v>
+        <v>102</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -17438,7 +17570,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 55.1% (fair -123). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -17470,17 +17602,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 163.5</t>
+          <t>Under 164.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4231</v>
+        <v>0.4493</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-102</v>
+        <v>102</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -17504,7 +17636,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 44.9% (fair +123). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -17546,7 +17678,7 @@
         <v>-145</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -17612,7 +17744,7 @@
         <v>145</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>

--- a/data/output/workbook/2026-06-28.xlsx
+++ b/data/output/workbook/2026-06-28.xlsx
@@ -401,7 +401,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9658350"/>
+    <ext cx="10125075" cy="9458325"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -491,7 +491,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9429750"/>
+    <ext cx="10125075" cy="9229725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -551,7 +551,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9277350"/>
+    <ext cx="10125075" cy="9077325"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -581,7 +581,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9858375"/>
+    <ext cx="10125075" cy="9439275"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -954,7 +954,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28 10:51</t>
+          <t>2026-06-28 12:12</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2851,167 +2851,297 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="29" t="inlineStr">
+        <is>
+          <t>Seattle Mariners offense vs Cleveland Guardians defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B60" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C60" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D60" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E60" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F60" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G60" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H60" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I60" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J60" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K60" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L60" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M60" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N60" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O60" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P60" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q60" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="29" t="inlineStr">
-        <is>
-          <t>Seattle Mariners offense vs Cleveland Guardians defense</t>
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C61" s="32" t="n">
+        <v>4.033</v>
+      </c>
+      <c r="D61" s="32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="E61" s="32" t="n">
+        <v>3.933</v>
+      </c>
+      <c r="F61" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G61" s="32" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H61" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I61" s="32" t="inlineStr"/>
+      <c r="J61" s="33" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K61" s="32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L61" s="32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M61" s="32" t="n">
+        <v>3.533</v>
+      </c>
+      <c r="N61" s="32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O61" s="32" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P61" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q61" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B62" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C62" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D62" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E62" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F62" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G62" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H62" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I62" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J62" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K62" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L62" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M62" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N62" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O62" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P62" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q62" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A62" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="n">
+        <v>7.351</v>
+      </c>
+      <c r="C62" s="32" t="n">
+        <v>8.042999999999999</v>
+      </c>
+      <c r="D62" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="E62" s="32" t="n">
+        <v>7.929</v>
+      </c>
+      <c r="F62" s="32" t="n">
+        <v>6.222</v>
+      </c>
+      <c r="G62" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H62" s="34" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I62" s="32" t="inlineStr"/>
+      <c r="J62" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K62" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="L62" s="32" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="M62" s="32" t="n">
+        <v>7.533</v>
+      </c>
+      <c r="N62" s="32" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O62" s="32" t="n">
+        <v>7.833</v>
+      </c>
+      <c r="P62" s="32" t="n">
+        <v>7.538</v>
+      </c>
+      <c r="Q62" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B63" s="32" t="n">
-        <v>3.7</v>
+        <v>1.054</v>
       </c>
       <c r="C63" s="32" t="n">
-        <v>4.033</v>
+        <v>1.174</v>
       </c>
       <c r="D63" s="32" t="n">
-        <v>3.75</v>
+        <v>1.294</v>
       </c>
       <c r="E63" s="32" t="n">
-        <v>3.933</v>
+        <v>1.286</v>
       </c>
       <c r="F63" s="32" t="n">
-        <v>3.4</v>
+        <v>1.111</v>
       </c>
       <c r="G63" s="32" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
-          <t>29th</t>
+          <t>25th</t>
         </is>
       </c>
       <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="33" t="inlineStr">
-        <is>
-          <t>2nd</t>
-        </is>
-      </c>
-      <c r="K63" s="32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="L63" s="32" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="M63" s="32" t="n">
-        <v>3.533</v>
-      </c>
-      <c r="N63" s="32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O63" s="32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="P63" s="32" t="n">
-        <v>4</v>
+      <c r="J63" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P63" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q63" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B64" s="32" t="n">
-        <v>7.351</v>
+        <v>8.865</v>
       </c>
       <c r="C64" s="32" t="n">
         <v>8.042999999999999</v>
@@ -3020,638 +3150,508 @@
         <v>8</v>
       </c>
       <c r="E64" s="32" t="n">
-        <v>7.929</v>
+        <v>8.143000000000001</v>
       </c>
       <c r="F64" s="32" t="n">
-        <v>6.222</v>
+        <v>8.444000000000001</v>
       </c>
       <c r="G64" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="H64" s="34" t="inlineStr">
-        <is>
-          <t>29th</t>
+        <v>7.8</v>
+      </c>
+      <c r="H64" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
         </is>
       </c>
       <c r="I64" s="32" t="inlineStr"/>
       <c r="J64" s="33" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="K64" s="32" t="n">
-        <v>6</v>
+        <v>11.2</v>
       </c>
       <c r="L64" s="32" t="n">
-        <v>7.3</v>
+        <v>10.3</v>
       </c>
       <c r="M64" s="32" t="n">
-        <v>7.533</v>
+        <v>9.132999999999999</v>
       </c>
       <c r="N64" s="32" t="n">
-        <v>7.3</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O64" s="32" t="n">
-        <v>7.833</v>
+        <v>9.233000000000001</v>
       </c>
       <c r="P64" s="32" t="n">
-        <v>7.538</v>
+        <v>9.487</v>
       </c>
       <c r="Q64" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>1.054</v>
+        <v>0.541</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>1.174</v>
+        <v>0.609</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>1.294</v>
+        <v>0.471</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>1.286</v>
+        <v>0.429</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>1.111</v>
+        <v>0.111</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
-          <t>25th</t>
+          <t>24th</t>
         </is>
       </c>
       <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P65" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J65" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="32" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M65" s="32" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="N65" s="32" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O65" s="32" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="P65" s="32" t="n">
+        <v>0.308</v>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="n">
-        <v>8.865</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>8.042999999999999</v>
-      </c>
-      <c r="D66" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="E66" s="32" t="n">
-        <v>8.143000000000001</v>
-      </c>
-      <c r="F66" s="32" t="n">
-        <v>8.444000000000001</v>
-      </c>
-      <c r="G66" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H66" s="33" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr"/>
-      <c r="J66" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="L66" s="32" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="M66" s="32" t="n">
-        <v>9.132999999999999</v>
-      </c>
-      <c r="N66" s="32" t="n">
-        <v>9.449999999999999</v>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>9.233000000000001</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>9.487</v>
-      </c>
-      <c r="Q66" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B67" s="32" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="C67" s="32" t="n">
-        <v>0.609</v>
-      </c>
-      <c r="D67" s="32" t="n">
-        <v>0.471</v>
-      </c>
-      <c r="E67" s="32" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="F67" s="32" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="G67" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H67" s="34" t="inlineStr">
-        <is>
-          <t>24th</t>
-        </is>
-      </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="32" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M67" s="32" t="n">
-        <v>0.467</v>
-      </c>
-      <c r="N67" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="O67" s="32" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="P67" s="32" t="n">
-        <v>0.308</v>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Cleveland Guardians offense vs Seattle Mariners defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
-        <is>
-          <t>Cleveland Guardians offense vs Seattle Mariners defense</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>4.367</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>4.633</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="n">
+        <v>7.308</v>
+      </c>
+      <c r="C70" s="32" t="n">
+        <v>7.733</v>
+      </c>
+      <c r="D70" s="32" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="E70" s="32" t="n">
+        <v>7.267</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H70" s="34" t="inlineStr">
+        <is>
+          <t>28th</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr"/>
+      <c r="J70" s="36" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L70" s="32" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="M70" s="32" t="n">
+        <v>9.071</v>
+      </c>
+      <c r="N70" s="32" t="n">
+        <v>9.294</v>
+      </c>
+      <c r="O70" s="32" t="n">
+        <v>9.478</v>
+      </c>
+      <c r="P70" s="32" t="n">
+        <v>8.404999999999999</v>
+      </c>
+      <c r="Q70" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>4</v>
+        <v>0.949</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>4.367</v>
+        <v>0.967</v>
       </c>
       <c r="D71" s="32" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="E71" s="32" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="F71" s="32" t="n">
-        <v>3.9</v>
+        <v>0.7</v>
       </c>
       <c r="G71" s="32" t="n">
-        <v>2.2</v>
+        <v>0.6</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
-          <t>27th</t>
+          <t>26th</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K71" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L71" s="32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="M71" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="N71" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O71" s="32" t="n">
-        <v>4.633</v>
-      </c>
-      <c r="P71" s="32" t="n">
-        <v>4.1</v>
+      <c r="J71" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P71" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>7.308</v>
+        <v>7.821</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>7.733</v>
+        <v>7.5</v>
       </c>
       <c r="D72" s="32" t="n">
-        <v>7.15</v>
+        <v>8.1</v>
       </c>
       <c r="E72" s="32" t="n">
-        <v>7.267</v>
+        <v>7.933</v>
       </c>
       <c r="F72" s="32" t="n">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
       <c r="G72" s="32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="H72" s="34" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I72" s="32" t="inlineStr"/>
+        <v>7.8</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
       <c r="J72" s="36" t="inlineStr">
         <is>
-          <t>14th</t>
+          <t>13th</t>
         </is>
       </c>
       <c r="K72" s="32" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L72" s="32" t="n">
-        <v>7.778</v>
+        <v>8.222</v>
       </c>
       <c r="M72" s="32" t="n">
-        <v>9.071</v>
+        <v>7.643</v>
       </c>
       <c r="N72" s="32" t="n">
-        <v>9.294</v>
+        <v>8.118</v>
       </c>
       <c r="O72" s="32" t="n">
-        <v>9.478</v>
+        <v>7.739</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>8.404999999999999</v>
+        <v>8.189</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>0.949</v>
+        <v>0.641</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>0.967</v>
+        <v>0.767</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>0.8</v>
+        <v>0.867</v>
       </c>
       <c r="F73" s="32" t="n">
         <v>0.7</v>
       </c>
       <c r="G73" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>30th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="L73" s="32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M73" s="32" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="N73" s="32" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="O73" s="32" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="P73" s="32" t="n">
+        <v>0.541</v>
       </c>
       <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>7.821</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>7.933</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J74" s="36" t="inlineStr">
-        <is>
-          <t>13th</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>8.222</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>7.643</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>8.118</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>7.739</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>8.189</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="32" t="n">
-        <v>0.641</v>
-      </c>
-      <c r="C75" s="32" t="n">
-        <v>0.767</v>
-      </c>
-      <c r="D75" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E75" s="32" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="F75" s="32" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G75" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="34" t="inlineStr">
-        <is>
-          <t>30th</t>
-        </is>
-      </c>
-      <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L75" s="32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="M75" s="32" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="N75" s="32" t="n">
-        <v>0.706</v>
-      </c>
-      <c r="O75" s="32" t="n">
-        <v>0.522</v>
-      </c>
-      <c r="P75" s="32" t="n">
-        <v>0.541</v>
-      </c>
-      <c r="Q75" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4518,7 +4518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4535,807 +4535,807 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="29" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies offense vs New York Mets defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B59" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C59" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D59" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E59" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F59" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G59" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H59" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I59" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J59" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K59" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L59" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M59" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N59" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O59" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P59" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q59" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="60">
-      <c r="A60" s="29" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies offense vs New York Mets defense</t>
+      <c r="A60" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B60" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C60" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="D60" s="32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E60" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F60" s="32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G60" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H60" s="36" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I60" s="32" t="inlineStr"/>
+      <c r="J60" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K60" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L60" s="32" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M60" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="N60" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O60" s="32" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P60" s="32" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="Q60" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B61" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C61" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D61" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E61" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F61" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G61" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H61" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I61" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J61" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K61" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L61" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M61" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N61" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O61" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P61" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q61" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="n">
+        <v>7.568</v>
+      </c>
+      <c r="C61" s="32" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="D61" s="32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E61" s="32" t="n">
+        <v>7.923</v>
+      </c>
+      <c r="F61" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="G61" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H61" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I61" s="32" t="inlineStr"/>
+      <c r="J61" s="36" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K61" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L61" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M61" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N61" s="32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O61" s="32" t="n">
+        <v>7.862</v>
+      </c>
+      <c r="P61" s="32" t="n">
+        <v>7.842</v>
+      </c>
+      <c r="Q61" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B62" s="32" t="n">
-        <v>4.1</v>
+        <v>1.135</v>
       </c>
       <c r="C62" s="32" t="n">
-        <v>4.067</v>
+        <v>1.148</v>
       </c>
       <c r="D62" s="32" t="n">
-        <v>3.95</v>
+        <v>1.222</v>
       </c>
       <c r="E62" s="32" t="n">
-        <v>4.6</v>
+        <v>1.385</v>
       </c>
       <c r="F62" s="32" t="n">
-        <v>4.3</v>
+        <v>1.333</v>
       </c>
       <c r="G62" s="32" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="H62" s="36" t="inlineStr">
         <is>
-          <t>20th</t>
+          <t>16th</t>
         </is>
       </c>
       <c r="I62" s="32" t="inlineStr"/>
-      <c r="J62" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
-        </is>
-      </c>
-      <c r="K62" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L62" s="32" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="M62" s="32" t="n">
-        <v>4.067</v>
-      </c>
-      <c r="N62" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O62" s="32" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="P62" s="32" t="n">
-        <v>4.214</v>
+      <c r="J62" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P62" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q62" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B63" s="32" t="n">
-        <v>7.568</v>
+        <v>8.568</v>
       </c>
       <c r="C63" s="32" t="n">
-        <v>7.37</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="D63" s="32" t="n">
-        <v>7.5</v>
+        <v>8.611000000000001</v>
       </c>
       <c r="E63" s="32" t="n">
-        <v>7.923</v>
+        <v>9.077</v>
       </c>
       <c r="F63" s="32" t="n">
-        <v>8</v>
+        <v>9.555999999999999</v>
       </c>
       <c r="G63" s="32" t="n">
-        <v>5.8</v>
+        <v>10.6</v>
       </c>
       <c r="H63" s="34" t="inlineStr">
         <is>
-          <t>25th</t>
+          <t>28th</t>
         </is>
       </c>
       <c r="I63" s="32" t="inlineStr"/>
-      <c r="J63" s="36" t="inlineStr">
-        <is>
-          <t>12th</t>
+      <c r="J63" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
         </is>
       </c>
       <c r="K63" s="32" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="L63" s="32" t="n">
-        <v>7.4</v>
+        <v>8.5</v>
       </c>
       <c r="M63" s="32" t="n">
-        <v>7.6</v>
+        <v>8.933</v>
       </c>
       <c r="N63" s="32" t="n">
-        <v>7.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O63" s="32" t="n">
-        <v>7.862</v>
+        <v>8.69</v>
       </c>
       <c r="P63" s="32" t="n">
-        <v>7.842</v>
+        <v>8.920999999999999</v>
       </c>
       <c r="Q63" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B64" s="32" t="n">
-        <v>1.135</v>
+        <v>0.649</v>
       </c>
       <c r="C64" s="32" t="n">
-        <v>1.148</v>
+        <v>0.481</v>
       </c>
       <c r="D64" s="32" t="n">
-        <v>1.222</v>
+        <v>0.389</v>
       </c>
       <c r="E64" s="32" t="n">
-        <v>1.385</v>
+        <v>0.385</v>
       </c>
       <c r="F64" s="32" t="n">
-        <v>1.333</v>
+        <v>0.444</v>
       </c>
       <c r="G64" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="H64" s="36" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I64" s="32" t="inlineStr"/>
-      <c r="J64" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P64" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="H64" s="33" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I64" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J64" s="36" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="K64" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L64" s="32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M64" s="32" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="N64" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O64" s="32" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="P64" s="32" t="n">
+        <v>0.474</v>
       </c>
       <c r="Q64" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B65" s="32" t="n">
-        <v>8.568</v>
-      </c>
-      <c r="C65" s="32" t="n">
-        <v>8.704000000000001</v>
-      </c>
-      <c r="D65" s="32" t="n">
-        <v>8.611000000000001</v>
-      </c>
-      <c r="E65" s="32" t="n">
-        <v>9.077</v>
-      </c>
-      <c r="F65" s="32" t="n">
-        <v>9.555999999999999</v>
-      </c>
-      <c r="G65" s="32" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H65" s="34" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L65" s="32" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M65" s="32" t="n">
-        <v>8.933</v>
-      </c>
-      <c r="N65" s="32" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="O65" s="32" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="P65" s="32" t="n">
-        <v>8.920999999999999</v>
-      </c>
-      <c r="Q65" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B66" s="32" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="C66" s="32" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="D66" s="32" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="E66" s="32" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="F66" s="32" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="G66" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H66" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I66" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J66" s="36" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L66" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M66" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="N66" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O66" s="32" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="P66" s="32" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="Q66" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
+      <c r="A66" s="29" t="inlineStr">
+        <is>
+          <t>New York Mets offense vs Philadelphia Phillies defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D67" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E67" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F67" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G67" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I67" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J67" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K67" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L67" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M67" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N67" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O67" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P67" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q67" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
-        <is>
-          <t>New York Mets offense vs Philadelphia Phillies defense</t>
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="n">
+        <v>3.357</v>
+      </c>
+      <c r="C68" s="32" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="D68" s="32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E68" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G68" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H68" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr"/>
+      <c r="J68" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K68" s="32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L68" s="32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M68" s="32" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N68" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O68" s="32" t="n">
+        <v>5.633</v>
+      </c>
+      <c r="P68" s="32" t="n">
+        <v>5.375</v>
+      </c>
+      <c r="Q68" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B69" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C69" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D69" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E69" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F69" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G69" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H69" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I69" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J69" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K69" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L69" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M69" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N69" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O69" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P69" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q69" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A69" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="n">
+        <v>7.053</v>
+      </c>
+      <c r="C69" s="32" t="n">
+        <v>6.586</v>
+      </c>
+      <c r="D69" s="32" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="E69" s="32" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="F69" s="32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G69" s="32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H69" s="34" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr"/>
+      <c r="J69" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K69" s="32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L69" s="32" t="n">
+        <v>8.888999999999999</v>
+      </c>
+      <c r="M69" s="32" t="n">
+        <v>9.769</v>
+      </c>
+      <c r="N69" s="32" t="n">
+        <v>9.888999999999999</v>
+      </c>
+      <c r="O69" s="32" t="n">
+        <v>10.222</v>
+      </c>
+      <c r="P69" s="32" t="n">
+        <v>9.891999999999999</v>
+      </c>
+      <c r="Q69" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B70" s="32" t="n">
-        <v>3.357</v>
+        <v>0.737</v>
       </c>
       <c r="C70" s="32" t="n">
-        <v>2.667</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>2.85</v>
+        <v>0.7</v>
       </c>
       <c r="E70" s="32" t="n">
-        <v>3</v>
+        <v>0.733</v>
       </c>
       <c r="F70" s="32" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="G70" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H70" s="34" t="inlineStr">
-        <is>
-          <t>22nd</t>
+        <v>1.2</v>
+      </c>
+      <c r="H70" s="33" t="inlineStr">
+        <is>
+          <t>9th</t>
         </is>
       </c>
       <c r="I70" s="32" t="inlineStr"/>
-      <c r="J70" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K70" s="32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L70" s="32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="M70" s="32" t="n">
-        <v>5.067</v>
-      </c>
-      <c r="N70" s="32" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O70" s="32" t="n">
-        <v>5.633</v>
-      </c>
-      <c r="P70" s="32" t="n">
-        <v>5.375</v>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P70" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q70" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B71" s="32" t="n">
-        <v>7.053</v>
+        <v>8.395</v>
       </c>
       <c r="C71" s="32" t="n">
-        <v>6.586</v>
+        <v>8.448</v>
       </c>
       <c r="D71" s="32" t="n">
-        <v>6.55</v>
+        <v>8.85</v>
       </c>
       <c r="E71" s="32" t="n">
-        <v>6.333</v>
+        <v>8.867000000000001</v>
       </c>
       <c r="F71" s="32" t="n">
-        <v>5.6</v>
+        <v>9.5</v>
       </c>
       <c r="G71" s="32" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="H71" s="34" t="inlineStr">
         <is>
-          <t>26th</t>
+          <t>23rd</t>
         </is>
       </c>
       <c r="I71" s="32" t="inlineStr"/>
       <c r="J71" s="33" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>7th</t>
         </is>
       </c>
       <c r="K71" s="32" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="L71" s="32" t="n">
-        <v>8.888999999999999</v>
+        <v>10.444</v>
       </c>
       <c r="M71" s="32" t="n">
-        <v>9.769</v>
+        <v>9.154</v>
       </c>
       <c r="N71" s="32" t="n">
-        <v>9.888999999999999</v>
+        <v>9.055999999999999</v>
       </c>
       <c r="O71" s="32" t="n">
-        <v>10.222</v>
+        <v>9.074</v>
       </c>
       <c r="P71" s="32" t="n">
-        <v>9.891999999999999</v>
+        <v>9.486000000000001</v>
       </c>
       <c r="Q71" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>0.737</v>
+        <v>0.553</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.414</v>
       </c>
       <c r="D72" s="32" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="E72" s="32" t="n">
-        <v>0.733</v>
+        <v>0.533</v>
       </c>
       <c r="F72" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G72" s="32" t="n">
         <v>0.8</v>
       </c>
-      <c r="G72" s="32" t="n">
-        <v>1.2</v>
-      </c>
       <c r="H72" s="33" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J72" s="33" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="K72" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>0.595</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B73" s="32" t="n">
-        <v>8.395</v>
-      </c>
-      <c r="C73" s="32" t="n">
-        <v>8.448</v>
-      </c>
-      <c r="D73" s="32" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="E73" s="32" t="n">
-        <v>8.867000000000001</v>
-      </c>
-      <c r="F73" s="32" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G73" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="H73" s="34" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr"/>
-      <c r="J73" s="33" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>10.444</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>9.154</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>9.055999999999999</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>9.074</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>9.486000000000001</v>
-      </c>
-      <c r="Q73" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B74" s="32" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="C74" s="32" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="D74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E74" s="32" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F74" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G74" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="33" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" s="32" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="M74" s="32" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="N74" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O74" s="32" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="P74" s="32" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="Q74" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -5354,7 +5354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5371,595 +5371,729 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr">
+        <is>
+          <t>Colorado Rockies offense vs Minnesota Twins defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B62" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C62" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D62" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E62" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F62" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G62" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H62" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I62" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J62" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K62" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L62" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M62" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N62" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O62" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P62" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q62" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
     <row r="63">
-      <c r="A63" s="29" t="inlineStr">
-        <is>
-          <t>Colorado Rockies offense vs Minnesota Twins defense</t>
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C63" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D63" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E63" s="32" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="F63" s="32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G63" s="32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H63" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I63" s="32" t="inlineStr"/>
+      <c r="J63" s="33" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="K63" s="32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L63" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M63" s="32" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="N63" s="32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="O63" s="32" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="P63" s="32" t="n">
+        <v>4.378</v>
+      </c>
+      <c r="Q63" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B64" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C64" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D64" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E64" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F64" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G64" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H64" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I64" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J64" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K64" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L64" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M64" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N64" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O64" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P64" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q64" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A64" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="n">
+        <v>8.128</v>
+      </c>
+      <c r="C64" s="32" t="n">
+        <v>8.207000000000001</v>
+      </c>
+      <c r="D64" s="32" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="E64" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F64" s="32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="G64" s="32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H64" s="34" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="I64" s="32" t="inlineStr"/>
+      <c r="J64" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K64" s="32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L64" s="32" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="M64" s="32" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="N64" s="32" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="O64" s="32" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="P64" s="32" t="n">
+        <v>7.811</v>
+      </c>
+      <c r="Q64" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>3.9</v>
+        <v>0.846</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>3.9</v>
+        <v>0.828</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>3.9</v>
+        <v>0.65</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>4.067</v>
+        <v>0.667</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>2.4</v>
+        <v>0.2</v>
       </c>
       <c r="H65" s="34" t="inlineStr">
         <is>
-          <t>25th</t>
+          <t>30th</t>
         </is>
       </c>
       <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="33" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L65" s="32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M65" s="32" t="n">
-        <v>4.133</v>
-      </c>
-      <c r="N65" s="32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="O65" s="32" t="n">
-        <v>4.333</v>
-      </c>
-      <c r="P65" s="32" t="n">
-        <v>4.378</v>
+      <c r="J65" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B66" s="32" t="n">
-        <v>8.128</v>
+        <v>9.103</v>
       </c>
       <c r="C66" s="32" t="n">
-        <v>8.207000000000001</v>
+        <v>8.516999999999999</v>
       </c>
       <c r="D66" s="32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="E66" s="32" t="n">
         <v>8.4</v>
       </c>
       <c r="F66" s="32" t="n">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G66" s="32" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H66" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
+        <v>7.2</v>
+      </c>
+      <c r="H66" s="33" t="inlineStr">
+        <is>
+          <t>4th</t>
         </is>
       </c>
       <c r="I66" s="32" t="inlineStr"/>
       <c r="J66" s="33" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="K66" s="32" t="n">
-        <v>5.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L66" s="32" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
       <c r="M66" s="32" t="n">
-        <v>6.667</v>
+        <v>7.667</v>
       </c>
       <c r="N66" s="32" t="n">
-        <v>7.05</v>
+        <v>8.15</v>
       </c>
       <c r="O66" s="32" t="n">
-        <v>7.667</v>
+        <v>8.032999999999999</v>
       </c>
       <c r="P66" s="32" t="n">
-        <v>7.811</v>
+        <v>8.054</v>
       </c>
       <c r="Q66" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B67" s="32" t="n">
-        <v>0.846</v>
+        <v>0.462</v>
       </c>
       <c r="C67" s="32" t="n">
-        <v>0.828</v>
+        <v>0.414</v>
       </c>
       <c r="D67" s="32" t="n">
-        <v>0.65</v>
+        <v>0.4</v>
       </c>
       <c r="E67" s="32" t="n">
-        <v>0.667</v>
+        <v>0.4</v>
       </c>
       <c r="F67" s="32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G67" s="32" t="n">
         <v>0.2</v>
       </c>
       <c r="H67" s="34" t="inlineStr">
         <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J67" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="K67" s="32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L67" s="32" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M67" s="32" t="n">
+        <v>1.067</v>
+      </c>
+      <c r="N67" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O67" s="32" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="P67" s="32" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="Q67" s="35" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Minnesota Twins offense vs Colorado Rockies defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B70" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C70" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D70" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E70" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F70" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G70" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H70" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I70" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J70" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K70" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L70" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M70" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N70" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O70" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P70" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q70" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>4.405</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>4.233</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H71" s="36" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>23rd</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>4.667</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>4.725</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="C72" s="32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="E72" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="G72" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J72" s="34" t="inlineStr">
+        <is>
           <t>30th</t>
         </is>
       </c>
-      <c r="I67" s="32" t="inlineStr"/>
-      <c r="J67" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P67" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q67" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>9.103</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>8.516999999999999</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>8.050000000000001</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H68" s="33" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="33" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>7.667</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>8.032999999999999</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>8.054</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B69" s="32" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="C69" s="32" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="D69" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E69" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F69" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G69" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H69" s="34" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I69" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J69" s="34" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K69" s="32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L69" s="32" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M69" s="32" t="n">
-        <v>1.067</v>
-      </c>
-      <c r="N69" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O69" s="32" t="n">
-        <v>0.633</v>
-      </c>
-      <c r="P69" s="32" t="n">
-        <v>0.5679999999999999</v>
-      </c>
-      <c r="Q69" s="35" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="29" t="inlineStr">
-        <is>
-          <t>Minnesota Twins offense vs Colorado Rockies defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B72" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C72" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D72" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E72" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F72" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G72" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H72" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I72" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J72" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K72" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L72" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M72" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N72" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O72" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P72" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q72" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="K72" s="32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L72" s="32" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="M72" s="32" t="n">
+        <v>9.532999999999999</v>
+      </c>
+      <c r="N72" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="O72" s="32" t="n">
+        <v>9.207000000000001</v>
+      </c>
+      <c r="P72" s="32" t="n">
+        <v>9.231</v>
+      </c>
+      <c r="Q72" s="35" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>4.405</v>
+        <v>1.108</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>4.233</v>
+        <v>1.1</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>3.55</v>
+        <v>1</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>3.3</v>
+        <v>0.9</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>3.6</v>
+        <v>1</v>
       </c>
       <c r="H73" s="36" t="inlineStr">
         <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>4.933</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>4.725</v>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>7.73</v>
+        <v>8.973000000000001</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>7.9</v>
+        <v>8.667</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>7.95</v>
+        <v>8.75</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>8</v>
+        <v>9.266999999999999</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>10th</t>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H74" s="36" t="inlineStr">
+        <is>
+          <t>15th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr">
@@ -5969,221 +6103,87 @@
       </c>
       <c r="J74" s="34" t="inlineStr">
         <is>
-          <t>30th</t>
+          <t>28th</t>
         </is>
       </c>
       <c r="K74" s="32" t="n">
-        <v>10.2</v>
+        <v>6.4</v>
       </c>
       <c r="L74" s="32" t="n">
-        <v>10.2</v>
+        <v>6.5</v>
       </c>
       <c r="M74" s="32" t="n">
-        <v>9.532999999999999</v>
+        <v>7.067</v>
       </c>
       <c r="N74" s="32" t="n">
-        <v>10</v>
+        <v>7.55</v>
       </c>
       <c r="O74" s="32" t="n">
-        <v>9.207000000000001</v>
+        <v>7.31</v>
       </c>
       <c r="P74" s="32" t="n">
-        <v>9.231</v>
+        <v>7.462</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B75" s="32" t="n">
-        <v>1.108</v>
+        <v>0.595</v>
       </c>
       <c r="C75" s="32" t="n">
-        <v>1.1</v>
+        <v>0.733</v>
       </c>
       <c r="D75" s="32" t="n">
-        <v>1</v>
+        <v>0.45</v>
       </c>
       <c r="E75" s="32" t="n">
-        <v>1</v>
+        <v>0.267</v>
       </c>
       <c r="F75" s="32" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="G75" s="32" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H75" s="36" t="inlineStr">
         <is>
-          <t>14th</t>
+          <t>18th</t>
         </is>
       </c>
       <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P75" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J75" s="36" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="K75" s="32" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L75" s="32" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M75" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N75" s="32" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O75" s="32" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="P75" s="32" t="n">
+        <v>0.718</v>
       </c>
       <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>8.973000000000001</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>9.266999999999999</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H76" s="36" t="inlineStr">
-        <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J76" s="34" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>7.067</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>7.462</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B77" s="32" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="C77" s="32" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="D77" s="32" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E77" s="32" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="F77" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G77" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H77" s="36" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
-      <c r="I77" s="32" t="inlineStr"/>
-      <c r="J77" s="36" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="K77" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L77" s="32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M77" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="N77" s="32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="O77" s="32" t="n">
-        <v>0.586</v>
-      </c>
-      <c r="P77" s="32" t="n">
-        <v>0.718</v>
-      </c>
-      <c r="Q77" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -7972,7 +7972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8116,7 +8116,7 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6281900900900901</v>
+        <v>0.6276405405405406</v>
       </c>
       <c r="G5" s="14" t="n">
         <v>-169</v>
@@ -8158,37 +8158,37 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Over 165.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.4701680672268908</v>
+        <v>0.5241935483870968</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>113</v>
+        <v>-110</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Over 164.5</t>
+          <t>Golden State Valkyries</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.5506435643564357</v>
+        <v>0.5885549295774647</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-123</v>
+        <v>-143</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>102</v>
+        <v>-113</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 58.9% (fair -143). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8295,12 +8295,12 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -8310,17 +8310,17 @@
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.6436134453781512</v>
+        <v>0.4727896995708154</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-181</v>
+        <v>112</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-138</v>
+        <v>133</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8344,7 +8344,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8361,12 +8361,12 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Seattle Mariners @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -8376,17 +8376,17 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries</t>
+          <t>Seattle Mariners</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5885549295774647</v>
+        <v>0.5239903846153846</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-143</v>
+        <v>-110</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>-113</v>
+        <v>108</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8410,7 +8410,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8512,10 +8512,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.4842342342342343</v>
+        <v>0.4846846846846848</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>122</v>
@@ -8542,7 +8542,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8554,17 +8554,17 @@
     <row r="12">
       <c r="A12" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins @ Houston Astros</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>00:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -8574,17 +8574,17 @@
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Minnesota Twins</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.4944700460829493</v>
+        <v>0.4286</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8608,7 +8608,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 42.9% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8620,17 +8620,17 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -8640,17 +8640,17 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4286</v>
+        <v>0.53465</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>133</v>
+        <v>-115</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8674,7 +8674,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 42.9% (fair +133). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8686,17 +8686,17 @@
     <row r="14">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners @ Cleveland Guardians</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -8706,17 +8706,17 @@
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Seattle Mariners</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.53255</v>
+        <v>0.4588412017167381</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-114</v>
+        <v>118</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8740,7 +8740,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8752,17 +8752,17 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -8772,17 +8772,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.53215</v>
+        <v>0.3821167883211679</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-114</v>
+        <v>162</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8818,17 +8818,17 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Minnesota Lynx @ Dallas Wings</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -8838,17 +8838,17 @@
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Minnesota Lynx</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4620264317180616</v>
+        <v>0.6146557377049181</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>116</v>
+        <v>-160</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>127</v>
+        <v>-144</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 61.5% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8884,17 +8884,17 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Texas Rangers @ Cleveland Guardians</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -8904,17 +8904,17 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.3857777777777778</v>
+        <v>0.4994711538461538</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>159</v>
+        <v>100</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>170</v>
+        <v>108</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8950,17 +8950,17 @@
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Cleveland Guardians</t>
+          <t>Kansas City Royals @ Chicago White Sox</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -8970,17 +8970,17 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4994711538461538</v>
+        <v>0.5796123348017621</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>100</v>
+        <v>-138</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>108</v>
+        <v>-127</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +100). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4985096153846154</v>
+        <v>0.496875</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>101</v>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9082,37 +9082,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox @ Baltimore Orioles</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Portland Fire +6.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4563876651982379</v>
+        <v>0.50871921182266</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>119</v>
+        <v>-104</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9136,7 +9136,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9148,17 +9148,17 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs @ Milwaukee Brewers</t>
+          <t>Chicago White Sox @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -9168,17 +9168,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Chicago Cubs</t>
+          <t>Chicago White Sox</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.4045703125</v>
+        <v>0.4547136563876652</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -9202,7 +9202,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Houston Astros @ Detroit Tigers</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -9234,17 +9234,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Las Vegas Aces</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4763594470046084</v>
+        <v>0.7401168067226891</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>110</v>
+        <v>-285</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>117</v>
+        <v>-257</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9268,7 +9268,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 74.0% (fair -285). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9285,32 +9285,32 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Washington Mystics</t>
+          <t>Houston Astros @ Detroit Tigers</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire +6.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5117326732673267</v>
+        <v>0.4813615023474179</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-105</v>
+        <v>108</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Kansas City Royals @ Chicago White Sox</t>
+          <t>Chicago Cubs @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -9366,17 +9366,17 @@
       </c>
       <c r="E24" s="20" t="inlineStr">
         <is>
-          <t>Chicago White Sox</t>
+          <t>Chicago Cubs</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5759203539823009</v>
+        <v>0.40988</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-136</v>
+        <v>144</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>-126</v>
+        <v>150</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9417,12 +9417,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx @ Dallas Wings</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -9432,17 +9432,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Minnesota Lynx</t>
+          <t>Portland Fire</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.6202444444444444</v>
+        <v>0.300735294117647</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-163</v>
+        <v>233</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-152</v>
+        <v>240</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9466,7 +9466,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 30.1% (fair +233). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9475,141 +9475,9 @@
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="20" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>Las Vegas Aces @ Chicago Sky</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>Las Vegas Aces</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>0.7361574229691876</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>-279</v>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>-257</v>
-      </c>
-      <c r="I26" s="13">
-        <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
-        <v/>
-      </c>
-      <c r="J26" s="16">
-        <f>IF($H$26="","",$F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))</f>
-        <v/>
-      </c>
-      <c r="K26" s="17">
-        <f>IF($H$26="","",MAX(0,($F$26*IF($H$26&lt;0,-100/$H$26,$H$26/100)-(1-$F$26))/IF($H$26&lt;0,-100/$H$26,$H$26/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L26" s="18">
-        <f>IF($H$26="","",ROUND(MIN($K$26,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M26" s="12">
-        <f>IF($J$26="","",IF($J$26&lt;0,"Pass",IF($J$26&lt;'Settings'!$B$4,"Thin",IF($J$26&lt;0.06,"✅ Sharp band",IF($J$26&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N26" s="19" t="inlineStr">
-        <is>
-          <t>Model 73.6% (fair -279). Your call.</t>
-        </is>
-      </c>
-      <c r="O26" s="15" t="n"/>
-      <c r="P26" s="16">
-        <f>IF(OR($H$26="",$O$26=""),"",(1+IF($H$26&lt;0,-100/$H$26,$H$26/100))/(1+IF($O$26&lt;0,-100/$O$26,$O$26/100))-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="inlineStr">
-        <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>17:35</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Moneyline</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>Baltimore Orioles</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>0.6464544117647059</v>
-      </c>
-      <c r="G27" s="14" t="n">
-        <v>-183</v>
-      </c>
-      <c r="H27" s="15" t="n">
-        <v>-172</v>
-      </c>
-      <c r="I27" s="13">
-        <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
-        <v/>
-      </c>
-      <c r="J27" s="16">
-        <f>IF($H$27="","",$F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))</f>
-        <v/>
-      </c>
-      <c r="K27" s="17">
-        <f>IF($H$27="","",MAX(0,($F$27*IF($H$27&lt;0,-100/$H$27,$H$27/100)-(1-$F$27))/IF($H$27&lt;0,-100/$H$27,$H$27/100))*'Settings'!$B$3)</f>
-        <v/>
-      </c>
-      <c r="L27" s="18">
-        <f>IF($H$27="","",ROUND(MIN($K$27,'Settings'!$B$5)*'Settings'!$B$2,2))</f>
-        <v/>
-      </c>
-      <c r="M27" s="12">
-        <f>IF($J$27="","",IF($J$27&lt;0,"Pass",IF($J$27&lt;'Settings'!$B$4,"Thin",IF($J$27&lt;0.06,"✅ Sharp band",IF($J$27&lt;0.08,"Strong","⚠ Verify (stale?)")))))</f>
-        <v/>
-      </c>
-      <c r="N27" s="19" t="inlineStr">
-        <is>
-          <t>Model 64.6% (fair -183). Your call.</t>
-        </is>
-      </c>
-      <c r="O27" s="15" t="n"/>
-      <c r="P27" s="16">
-        <f>IF(OR($H$27="",$O$27=""),"",(1+IF($H$27&lt;0,-100/$H$27,$H$27/100))/(1+IF($O$27&lt;0,-100/$O$27,$O$27/100))-1)</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
-  <conditionalFormatting sqref="J5:J27">
+  <conditionalFormatting sqref="J5:J25">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="-0.05"/>
@@ -9775,13 +9643,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.3535185185185185</v>
+        <v>0.3470567375886525</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -9805,7 +9673,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 35.4% (fair +183). Your call.</t>
+          <t>Model 34.7% (fair +188). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9841,13 +9709,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6464544117647059</v>
+        <v>0.6529654676258992</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-183</v>
+        <v>-188</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-172</v>
+        <v>-178</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -9871,7 +9739,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 64.6% (fair -183). Your call.</t>
+          <t>Model 65.3% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10045,7 +9913,7 @@
         <v>-116</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -10111,7 +9979,7 @@
         <v>116</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -10171,13 +10039,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3718385650224215</v>
+        <v>0.3723873873873874</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>169</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -10237,7 +10105,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6281900900900901</v>
+        <v>0.6276405405405406</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>-169</v>
@@ -10309,7 +10177,7 @@
         <v>-116</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -10375,7 +10243,7 @@
         <v>116</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -10507,7 +10375,7 @@
         <v>136</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>-123</v>
+        <v>-121</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -10567,10 +10435,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4842342342342343</v>
+        <v>0.4846846846846848</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>122</v>
@@ -10597,7 +10465,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10633,13 +10501,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5157522522522523</v>
+        <v>0.5153176470588235</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-107</v>
+        <v>-106</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-122</v>
+        <v>-121</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -10663,7 +10531,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10695,17 +10563,17 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Over 9</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5578</v>
+        <v>0.4591</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-126</v>
+        <v>118</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>-102</v>
+        <v>106</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -10729,7 +10597,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 55.8% (fair -126). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10761,17 +10629,17 @@
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Under 8.5</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4422</v>
+        <v>0.5408999999999999</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>126</v>
+        <v>-118</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -10795,7 +10663,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 44.2% (fair +126). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10903,7 +10771,7 @@
         <v>-180</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>165</v>
+        <v>-127</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -10963,13 +10831,13 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.5236197183098591</v>
+        <v>0.5186076923076923</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>-113</v>
+        <v>-108</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -10993,7 +10861,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 51.9% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11029,13 +10897,13 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.4763594470046084</v>
+        <v>0.4813615023474179</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H24" s="15" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="I24" s="13">
         <f>IF($H$24="","",IF($H$24&lt;0,-$H$24/(-$H$24+100),100/($H$24+100)))</f>
@@ -11059,7 +10927,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 48.1% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11167,7 +11035,7 @@
         <v>123</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -11227,13 +11095,13 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.53255</v>
+        <v>0.5239903846153846</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-114</v>
+        <v>-110</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -11257,7 +11125,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11293,13 +11161,13 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4674752475247525</v>
+        <v>0.4760039215686274</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>102</v>
+        <v>-104</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -11323,7 +11191,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11365,7 +11233,7 @@
         <v>176</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -11431,7 +11299,7 @@
         <v>-176</v>
       </c>
       <c r="H30" s="15" t="n">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="I30" s="13">
         <f>IF($H$30="","",IF($H$30&lt;0,-$H$30/(-$H$30+100),100/($H$30+100)))</f>
@@ -11497,7 +11365,7 @@
         <v>244</v>
       </c>
       <c r="H31" s="15" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I31" s="13">
         <f>IF($H$31="","",IF($H$31&lt;0,-$H$31/(-$H$31+100),100/($H$31+100)))</f>
@@ -11563,7 +11431,7 @@
         <v>-244</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="I32" s="13">
         <f>IF($H$32="","",IF($H$32&lt;0,-$H$32/(-$H$32+100),100/($H$32+100)))</f>
@@ -11623,13 +11491,13 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>0.3857777777777778</v>
+        <v>0.3821167883211679</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="H33" s="15" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="I33" s="13">
         <f>IF($H$33="","",IF($H$33&lt;0,-$H$33/(-$H$33+100),100/($H$33+100)))</f>
@@ -11653,7 +11521,7 @@
       </c>
       <c r="N33" s="19" t="inlineStr">
         <is>
-          <t>Model 38.6% (fair +159). Your call.</t>
+          <t>Model 38.2% (fair +162). Your call.</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -11689,13 +11557,13 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>0.6142037037037037</v>
+        <v>0.6178776978417266</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>-159</v>
+        <v>-162</v>
       </c>
       <c r="H34" s="15" t="n">
-        <v>-170</v>
+        <v>-178</v>
       </c>
       <c r="I34" s="13">
         <f>IF($H$34="","",IF($H$34&lt;0,-$H$34/(-$H$34+100),100/($H$34+100)))</f>
@@ -11719,7 +11587,7 @@
       </c>
       <c r="N34" s="19" t="inlineStr">
         <is>
-          <t>Model 61.4% (fair -159). Your call.</t>
+          <t>Model 61.8% (fair -162). Your call.</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -11887,13 +11755,13 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>0.4498222222222222</v>
+        <v>0.4514864864864865</v>
       </c>
       <c r="G37" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="H37" s="15" t="n">
         <v>122</v>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>125</v>
       </c>
       <c r="I37" s="13">
         <f>IF($H$37="","",IF($H$37&lt;0,-$H$37/(-$H$37+100),100/($H$37+100)))</f>
@@ -11917,7 +11785,7 @@
       </c>
       <c r="N37" s="19" t="inlineStr">
         <is>
-          <t>Model 45.0% (fair +122). Your call.</t>
+          <t>Model 45.1% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -11953,10 +11821,10 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>0.5501540540540542</v>
+        <v>0.5485054054054054</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>-122</v>
+        <v>-121</v>
       </c>
       <c r="H38" s="15" t="n">
         <v>-122</v>
@@ -11983,7 +11851,7 @@
       </c>
       <c r="N38" s="19" t="inlineStr">
         <is>
-          <t>Model 55.0% (fair -122). Your call.</t>
+          <t>Model 54.9% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -12019,10 +11887,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.5788462184873949</v>
+        <v>0.582</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-137</v>
+        <v>-139</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>-138</v>
@@ -12049,7 +11917,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 57.9% (fair -137). Your call.</t>
+          <t>Model 58.2% (fair -139). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12085,13 +11953,13 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.4211538461538462</v>
+        <v>0.418</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H40" s="15" t="n">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="I40" s="13">
         <f>IF($H$40="","",IF($H$40&lt;0,-$H$40/(-$H$40+100),100/($H$40+100)))</f>
@@ -12115,7 +11983,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 42.1% (fair +137). Your call.</t>
+          <t>Model 41.8% (fair +139). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12223,7 +12091,7 @@
         <v>-136</v>
       </c>
       <c r="H42" s="15" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I42" s="13">
         <f>IF($H$42="","",IF($H$42&lt;0,-$H$42/(-$H$42+100),100/($H$42+100)))</f>
@@ -12421,7 +12289,7 @@
         <v>-110</v>
       </c>
       <c r="H45" s="15" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="I45" s="13">
         <f>IF($H$45="","",IF($H$45&lt;0,-$H$45/(-$H$45+100),100/($H$45+100)))</f>
@@ -12619,7 +12487,7 @@
         <v>-138</v>
       </c>
       <c r="H48" s="15" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I48" s="13">
         <f>IF($H$48="","",IF($H$48&lt;0,-$H$48/(-$H$48+100),100/($H$48+100)))</f>
@@ -12679,13 +12547,13 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4241071428571428</v>
+        <v>0.4203913043478261</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H49" s="15" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="I49" s="13">
         <f>IF($H$49="","",IF($H$49&lt;0,-$H$49/(-$H$49+100),100/($H$49+100)))</f>
@@ -12709,7 +12577,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 42.4% (fair +136). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12745,13 +12613,13 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5759203539823009</v>
+        <v>0.5796123348017621</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-136</v>
+        <v>-138</v>
       </c>
       <c r="H50" s="15" t="n">
-        <v>-126</v>
+        <v>-127</v>
       </c>
       <c r="I50" s="13">
         <f>IF($H$50="","",IF($H$50&lt;0,-$H$50/(-$H$50+100),100/($H$50+100)))</f>
@@ -12775,7 +12643,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 57.6% (fair -136). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12807,17 +12675,17 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.5663</v>
+        <v>0.6612</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>-131</v>
+        <v>-195</v>
       </c>
       <c r="H51" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I51" s="13">
         <f>IF($H$51="","",IF($H$51&lt;0,-$H$51/(-$H$51+100),100/($H$51+100)))</f>
@@ -12841,7 +12709,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 56.6% (fair -131). Your call.</t>
+          <t>Model 66.1% (fair -195). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -12873,17 +12741,17 @@
       </c>
       <c r="E52" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.4337</v>
+        <v>0.3388</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>131</v>
+        <v>195</v>
       </c>
       <c r="H52" s="15" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="I52" s="13">
         <f>IF($H$52="","",IF($H$52&lt;0,-$H$52/(-$H$52+100),100/($H$52+100)))</f>
@@ -12907,7 +12775,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 43.4% (fair +131). Your call.</t>
+          <t>Model 33.9% (fair +195). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -12949,7 +12817,7 @@
         <v>112</v>
       </c>
       <c r="H53" s="15" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I53" s="13">
         <f>IF($H$53="","",IF($H$53&lt;0,-$H$53/(-$H$53+100),100/($H$53+100)))</f>
@@ -13015,7 +12883,7 @@
         <v>-112</v>
       </c>
       <c r="H54" s="15" t="n">
-        <v>-118</v>
+        <v>-117</v>
       </c>
       <c r="I54" s="13">
         <f>IF($H$54="","",IF($H$54&lt;0,-$H$54/(-$H$54+100),100/($H$54+100)))</f>
@@ -13075,13 +12943,13 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4045703125</v>
+        <v>0.40988</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H55" s="15" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I55" s="13">
         <f>IF($H$55="","",IF($H$55&lt;0,-$H$55/(-$H$55+100),100/($H$55+100)))</f>
@@ -13105,7 +12973,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 40.5% (fair +147). Your call.</t>
+          <t>Model 41.0% (fair +144). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13141,13 +13009,13 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5954203125</v>
+        <v>0.5900903225806452</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-147</v>
+        <v>-144</v>
       </c>
       <c r="H56" s="15" t="n">
-        <v>-156</v>
+        <v>-148</v>
       </c>
       <c r="I56" s="13">
         <f>IF($H$56="","",IF($H$56&lt;0,-$H$56/(-$H$56+100),100/($H$56+100)))</f>
@@ -13171,7 +13039,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 59.5% (fair -147). Your call.</t>
+          <t>Model 59.0% (fair -144). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13213,7 +13081,7 @@
         <v>-146</v>
       </c>
       <c r="H57" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I57" s="13">
         <f>IF($H$57="","",IF($H$57&lt;0,-$H$57/(-$H$57+100),100/($H$57+100)))</f>
@@ -13279,7 +13147,7 @@
         <v>146</v>
       </c>
       <c r="H58" s="15" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I58" s="13">
         <f>IF($H$58="","",IF($H$58&lt;0,-$H$58/(-$H$58+100),100/($H$58+100)))</f>
@@ -13345,7 +13213,7 @@
         <v>121</v>
       </c>
       <c r="H59" s="15" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="I59" s="13">
         <f>IF($H$59="","",IF($H$59&lt;0,-$H$59/(-$H$59+100),100/($H$59+100)))</f>
@@ -14047,13 +13915,13 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4675938053097345</v>
+        <v>0.4676061674008811</v>
       </c>
       <c r="G70" s="14" t="n">
         <v>114</v>
       </c>
       <c r="H70" s="15" t="n">
-        <v>-126</v>
+        <v>-127</v>
       </c>
       <c r="I70" s="13">
         <f>IF($H$70="","",IF($H$70&lt;0,-$H$70/(-$H$70+100),100/($H$70+100)))</f>
@@ -14109,17 +13977,17 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Over 9</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>0.428</v>
+        <v>0.5239</v>
       </c>
       <c r="G71" s="14" t="n">
-        <v>134</v>
+        <v>-110</v>
       </c>
       <c r="H71" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I71" s="13">
         <f>IF($H$71="","",IF($H$71&lt;0,-$H$71/(-$H$71+100),100/($H$71+100)))</f>
@@ -14143,7 +14011,7 @@
       </c>
       <c r="N71" s="19" t="inlineStr">
         <is>
-          <t>Model 42.8% (fair +134). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -14175,17 +14043,17 @@
       </c>
       <c r="E72" s="20" t="inlineStr">
         <is>
-          <t>Under 9</t>
+          <t>Under 8.5</t>
         </is>
       </c>
       <c r="F72" s="13" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.4761</v>
       </c>
       <c r="G72" s="14" t="n">
-        <v>-134</v>
+        <v>110</v>
       </c>
       <c r="H72" s="15" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="I72" s="13">
         <f>IF($H$72="","",IF($H$72&lt;0,-$H$72/(-$H$72+100),100/($H$72+100)))</f>
@@ -14209,7 +14077,7 @@
       </c>
       <c r="N72" s="19" t="inlineStr">
         <is>
-          <t>Model 57.2% (fair -134). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -14245,13 +14113,13 @@
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>0.3379615384615385</v>
+        <v>0.3379467680608365</v>
       </c>
       <c r="G73" s="14" t="n">
         <v>196</v>
       </c>
       <c r="H73" s="15" t="n">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="I73" s="13">
         <f>IF($H$73="","",IF($H$73&lt;0,-$H$73/(-$H$73+100),100/($H$73+100)))</f>
@@ -14375,10 +14243,10 @@
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>0.4563876651982379</v>
+        <v>0.4547136563876652</v>
       </c>
       <c r="G75" s="14" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H75" s="15" t="n">
         <v>127</v>
@@ -14405,7 +14273,7 @@
       </c>
       <c r="N75" s="19" t="inlineStr">
         <is>
-          <t>Model 45.6% (fair +119). Your call.</t>
+          <t>Model 45.5% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -14441,13 +14309,13 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>0.5436504201680672</v>
+        <v>0.5453</v>
       </c>
       <c r="G76" s="14" t="n">
-        <v>-119</v>
+        <v>-120</v>
       </c>
       <c r="H76" s="15" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="I76" s="13">
         <f>IF($H$76="","",IF($H$76&lt;0,-$H$76/(-$H$76+100),100/($H$76+100)))</f>
@@ -14471,7 +14339,7 @@
       </c>
       <c r="N76" s="19" t="inlineStr">
         <is>
-          <t>Model 54.4% (fair -119). Your call.</t>
+          <t>Model 54.5% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -14507,10 +14375,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.53215</v>
+        <v>0.53465</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="H77" s="15" t="n">
         <v>100</v>
@@ -14537,7 +14405,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 53.2% (fair -114). Your call.</t>
+          <t>Model 53.5% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14573,13 +14441,13 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.46785</v>
+        <v>0.4653921568627451</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H78" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I78" s="13">
         <f>IF($H$78="","",IF($H$78&lt;0,-$H$78/(-$H$78+100),100/($H$78+100)))</f>
@@ -14603,7 +14471,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 46.8% (fair +114). Your call.</t>
+          <t>Model 46.5% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14639,13 +14507,13 @@
         </is>
       </c>
       <c r="F79" s="13" t="n">
-        <v>0.4620264317180616</v>
+        <v>0.4588412017167381</v>
       </c>
       <c r="G79" s="14" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H79" s="15" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="I79" s="13">
         <f>IF($H$79="","",IF($H$79&lt;0,-$H$79/(-$H$79+100),100/($H$79+100)))</f>
@@ -14669,7 +14537,7 @@
       </c>
       <c r="N79" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -14705,10 +14573,10 @@
         </is>
       </c>
       <c r="F80" s="13" t="n">
-        <v>0.5379364806866953</v>
+        <v>0.5411330472103004</v>
       </c>
       <c r="G80" s="14" t="n">
-        <v>-116</v>
+        <v>-118</v>
       </c>
       <c r="H80" s="15" t="n">
         <v>-133</v>
@@ -14735,7 +14603,7 @@
       </c>
       <c r="N80" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -14771,7 +14639,7 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.4985096153846154</v>
+        <v>0.496875</v>
       </c>
       <c r="G81" s="14" t="n">
         <v>101</v>
@@ -14801,7 +14669,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 49.9% (fair +101). Your call.</t>
+          <t>Model 49.7% (fair +101). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14837,7 +14705,7 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.5014941176470588</v>
+        <v>0.5031254901960784</v>
       </c>
       <c r="G82" s="14" t="n">
         <v>-101</v>
@@ -14867,7 +14735,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 50.1% (fair -101). Your call.</t>
+          <t>Model 50.3% (fair -101). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -14903,10 +14771,10 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.5044999999999999</v>
+        <v>0.4533</v>
       </c>
       <c r="G83" s="14" t="n">
-        <v>-102</v>
+        <v>121</v>
       </c>
       <c r="H83" s="15" t="n">
         <v>186</v>
@@ -14933,7 +14801,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 50.4% (fair -102). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -14969,10 +14837,10 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.4955</v>
+        <v>0.5467</v>
       </c>
       <c r="G84" s="14" t="n">
-        <v>102</v>
+        <v>-121</v>
       </c>
       <c r="H84" s="15" t="n">
         <v>127</v>
@@ -14999,7 +14867,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 49.5% (fair +102). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15167,13 +15035,13 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.3563934426229509</v>
+        <v>0.2987</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>181</v>
+        <v>235</v>
       </c>
       <c r="H87" s="15" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I87" s="13">
         <f>IF($H$87="","",IF($H$87&lt;0,-$H$87/(-$H$87+100),100/($H$87+100)))</f>
@@ -15197,7 +15065,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 35.6% (fair +181). Your call.</t>
+          <t>Model 29.9% (fair +235). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15233,10 +15101,10 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.6436134453781512</v>
+        <v>0.7013</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-181</v>
+        <v>-235</v>
       </c>
       <c r="H88" s="15" t="n">
         <v>-138</v>
@@ -15263,7 +15131,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 64.4% (fair -181). Your call.</t>
+          <t>Model 70.1% (fair -235). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15299,10 +15167,10 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.435726872246696</v>
+        <v>0.4381938325991189</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="H89" s="15" t="n">
         <v>127</v>
@@ -15329,7 +15197,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 43.6% (fair +130). Your call.</t>
+          <t>Model 43.8% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15365,13 +15233,13 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5642510729613734</v>
+        <v>0.5617651982378855</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-129</v>
+        <v>-128</v>
       </c>
       <c r="H90" s="15" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="I90" s="13">
         <f>IF($H$90="","",IF($H$90&lt;0,-$H$90/(-$H$90+100),100/($H$90+100)))</f>
@@ -15395,7 +15263,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 56.4% (fair -129). Your call.</t>
+          <t>Model 56.2% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15431,13 +15299,13 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.4944700460829493</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>102</v>
+        <v>-114</v>
       </c>
       <c r="H91" s="15" t="n">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="I91" s="13">
         <f>IF($H$91="","",IF($H$91&lt;0,-$H$91/(-$H$91+100),100/($H$91+100)))</f>
@@ -15461,7 +15329,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 49.4% (fair +102). Your call.</t>
+          <t>Model 53.3% (fair -114). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15497,10 +15365,10 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5055306306306306</v>
+        <v>0.4672</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-102</v>
+        <v>114</v>
       </c>
       <c r="H92" s="15" t="n">
         <v>-122</v>
@@ -15527,7 +15395,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 50.6% (fair -102). Your call.</t>
+          <t>Model 46.7% (fair +114). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15563,10 +15431,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.5297901639344262</v>
+        <v>0.5272524590163934</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>-113</v>
+        <v>-112</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>-144</v>
@@ -15593,7 +15461,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 53.0% (fair -113). Your call.</t>
+          <t>Model 52.7% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15629,13 +15497,13 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.4701680672268908</v>
+        <v>0.4727896995708154</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H94" s="15" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I94" s="13">
         <f>IF($H$94="","",IF($H$94&lt;0,-$H$94/(-$H$94+100),100/($H$94+100)))</f>
@@ -15659,7 +15527,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 47.0% (fair +113). Your call.</t>
+          <t>Model 47.3% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15951,10 +15819,10 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.5699</v>
+        <v>0.5568</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>-133</v>
+        <v>-126</v>
       </c>
       <c r="H99" s="15" t="n"/>
       <c r="I99" s="13">
@@ -15979,7 +15847,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -133). Your call.</t>
+          <t>Model 55.7% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16015,10 +15883,10 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.43</v>
+        <v>0.4432</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="H100" s="15" t="n"/>
       <c r="I100" s="13">
@@ -16043,7 +15911,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +133). Your call.</t>
+          <t>Model 44.3% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16220,13 +16088,13 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.6202444444444444</v>
+        <v>0.6146557377049181</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>-163</v>
+        <v>-160</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-152</v>
+        <v>-144</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -16250,7 +16118,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 62.0% (fair -163). Your call.</t>
+          <t>Model 61.5% (fair -160). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -16286,13 +16154,13 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.37976</v>
+        <v>0.3853278688524591</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -16316,7 +16184,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 38.0% (fair +163). Your call.</t>
+          <t>Model 38.5% (fair +160). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -16490,7 +16358,7 @@
         <v>125</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -16556,7 +16424,7 @@
         <v>-125</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I10" s="13">
         <f>IF($H$10="","",IF($H$10&lt;0,-$H$10/(-$H$10+100),100/($H$10+100)))</f>
@@ -16616,13 +16484,13 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3044444444444445</v>
+        <v>0.300735294117647</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -16646,7 +16514,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 30.4% (fair +228). Your call.</t>
+          <t>Model 30.1% (fair +233). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -16682,13 +16550,13 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6955714714714715</v>
+        <v>0.6992797101449275</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-228</v>
+        <v>-233</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>-233</v>
+        <v>-245</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -16712,7 +16580,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 69.6% (fair -228). Your call.</t>
+          <t>Model 69.9% (fair -233). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -16880,13 +16748,13 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.48825</v>
+        <v>0.4912980392156863</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>100</v>
+        <v>-104</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -16910,7 +16778,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 48.8% (fair +105). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -16946,13 +16814,13 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5117326732673267</v>
+        <v>0.50871921182266</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-105</v>
+        <v>-104</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -16976,7 +16844,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 51.2% (fair -105). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -17012,10 +16880,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.7361574229691876</v>
+        <v>0.7401168067226891</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-279</v>
+        <v>-285</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>-257</v>
@@ -17042,7 +16910,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 73.6% (fair -279). Your call.</t>
+          <t>Model 74.0% (fair -285). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -17078,13 +16946,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.2638</v>
+        <v>0.2598626373626373</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -17108,7 +16976,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 26.4% (fair +279). Your call.</t>
+          <t>Model 26.0% (fair +285). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -17144,13 +17012,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4731730769230769</v>
+        <v>0.4731372549019608</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>111</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -17216,7 +17084,7 @@
         <v>-111</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -17282,7 +17150,7 @@
         <v>141</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -17348,7 +17216,7 @@
         <v>-141</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -17536,17 +17404,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Over 164.5</t>
+          <t>Over 165.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5506435643564357</v>
+        <v>0.5241935483870968</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-123</v>
+        <v>-110</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -17570,7 +17438,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -17602,17 +17470,17 @@
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Under 164.5</t>
+          <t>Under 165.5</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4493</v>
+        <v>0.4758</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -17636,7 +17504,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 47.6% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -17668,17 +17536,17 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries -1.5</t>
+          <t>Golden State Valkyries -2</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.5921</v>
+        <v>0.5752</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-145</v>
+        <v>-135</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -17702,7 +17570,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 59.2% (fair -145). Your call.</t>
+          <t>Model 57.5% (fair -135). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -17734,17 +17602,17 @@
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty +1.5</t>
+          <t>New York Liberty +2</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.4079</v>
+        <v>0.4248</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -17768,7 +17636,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 40.8% (fair +145). Your call.</t>
+          <t>Model 42.5% (fair +135). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -19181,7 +19049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:Q75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19198,532 +19066,595 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="29" t="inlineStr">
+        <is>
+          <t>Cincinnati Reds offense vs Pittsburgh Pirates defense</t>
+        </is>
+      </c>
+    </row>
     <row r="62">
-      <c r="A62" s="29" t="inlineStr">
-        <is>
-          <t>Cincinnati Reds offense vs Pittsburgh Pirates defense</t>
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B62" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C62" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D62" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E62" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F62" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G62" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H62" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I62" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J62" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K62" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L62" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M62" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N62" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O62" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P62" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q62" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B63" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C63" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D63" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E63" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F63" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G63" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H63" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I63" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J63" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K63" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L63" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M63" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N63" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O63" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P63" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q63" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="n">
+        <v>4.132</v>
+      </c>
+      <c r="C63" s="32" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="D63" s="32" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="E63" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="F63" s="32" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G63" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="H63" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I63" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J63" s="36" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="K63" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L63" s="32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M63" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="N63" s="32" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O63" s="32" t="n">
+        <v>4.267</v>
+      </c>
+      <c r="P63" s="32" t="n">
+        <v>4.209</v>
+      </c>
+      <c r="Q63" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B64" s="32" t="n">
-        <v>4.132</v>
+        <v>7.216</v>
       </c>
       <c r="C64" s="32" t="n">
-        <v>4.433</v>
+        <v>7.345</v>
       </c>
       <c r="D64" s="32" t="n">
-        <v>4.65</v>
+        <v>7.632</v>
       </c>
       <c r="E64" s="32" t="n">
-        <v>4.867</v>
+        <v>8</v>
       </c>
       <c r="F64" s="32" t="n">
-        <v>3.9</v>
+        <v>7.667</v>
       </c>
       <c r="G64" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="H64" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I64" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
+        <v>7.8</v>
+      </c>
+      <c r="H64" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I64" s="32" t="inlineStr"/>
       <c r="J64" s="36" t="inlineStr">
         <is>
-          <t>20th</t>
+          <t>16th</t>
         </is>
       </c>
       <c r="K64" s="32" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="L64" s="32" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="M64" s="32" t="n">
-        <v>4.267</v>
+        <v>7.643</v>
       </c>
       <c r="N64" s="32" t="n">
-        <v>4.4</v>
+        <v>7.625</v>
       </c>
       <c r="O64" s="32" t="n">
-        <v>4.267</v>
+        <v>7.808</v>
       </c>
       <c r="P64" s="32" t="n">
-        <v>4.209</v>
+        <v>7.658</v>
       </c>
       <c r="Q64" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B65" s="32" t="n">
-        <v>7.216</v>
+        <v>1.216</v>
       </c>
       <c r="C65" s="32" t="n">
-        <v>7.345</v>
+        <v>1.241</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>7.632</v>
+        <v>1.263</v>
       </c>
       <c r="E65" s="32" t="n">
-        <v>8</v>
+        <v>1.643</v>
       </c>
       <c r="F65" s="32" t="n">
-        <v>7.667</v>
+        <v>0.889</v>
       </c>
       <c r="G65" s="32" t="n">
-        <v>7.8</v>
+        <v>1</v>
       </c>
       <c r="H65" s="36" t="inlineStr">
         <is>
-          <t>16th</t>
+          <t>13th</t>
         </is>
       </c>
       <c r="I65" s="32" t="inlineStr"/>
-      <c r="J65" s="36" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="K65" s="32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L65" s="32" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="M65" s="32" t="n">
-        <v>7.643</v>
-      </c>
-      <c r="N65" s="32" t="n">
-        <v>7.625</v>
-      </c>
-      <c r="O65" s="32" t="n">
-        <v>7.808</v>
-      </c>
-      <c r="P65" s="32" t="n">
-        <v>7.658</v>
+      <c r="J65" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P65" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q65" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B66" s="32" t="n">
-        <v>1.216</v>
+        <v>9.27</v>
       </c>
       <c r="C66" s="32" t="n">
-        <v>1.241</v>
+        <v>9.103</v>
       </c>
       <c r="D66" s="32" t="n">
-        <v>1.263</v>
+        <v>9.420999999999999</v>
       </c>
       <c r="E66" s="32" t="n">
-        <v>1.643</v>
+        <v>9.286</v>
       </c>
       <c r="F66" s="32" t="n">
-        <v>0.889</v>
+        <v>8.888999999999999</v>
       </c>
       <c r="G66" s="32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66" s="36" t="inlineStr">
-        <is>
-          <t>13th</t>
+        <v>9.6</v>
+      </c>
+      <c r="H66" s="34" t="inlineStr">
+        <is>
+          <t>22nd</t>
         </is>
       </c>
       <c r="I66" s="32" t="inlineStr"/>
-      <c r="J66" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P66" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J66" s="36" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="K66" s="32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="L66" s="32" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M66" s="32" t="n">
+        <v>8.071</v>
+      </c>
+      <c r="N66" s="32" t="n">
+        <v>8.311999999999999</v>
+      </c>
+      <c r="O66" s="32" t="n">
+        <v>8.462</v>
+      </c>
+      <c r="P66" s="32" t="n">
+        <v>8.946999999999999</v>
       </c>
       <c r="Q66" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B67" s="32" t="n">
-        <v>9.27</v>
+        <v>0.595</v>
       </c>
       <c r="C67" s="32" t="n">
-        <v>9.103</v>
+        <v>0.621</v>
       </c>
       <c r="D67" s="32" t="n">
-        <v>9.420999999999999</v>
+        <v>0.421</v>
       </c>
       <c r="E67" s="32" t="n">
-        <v>9.286</v>
+        <v>0.429</v>
       </c>
       <c r="F67" s="32" t="n">
-        <v>8.888999999999999</v>
+        <v>0</v>
       </c>
       <c r="G67" s="32" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="H67" s="34" t="inlineStr">
         <is>
-          <t>22nd</t>
+          <t>26th</t>
         </is>
       </c>
       <c r="I67" s="32" t="inlineStr"/>
       <c r="J67" s="36" t="inlineStr">
         <is>
-          <t>15th</t>
+          <t>14th</t>
         </is>
       </c>
       <c r="K67" s="32" t="n">
-        <v>8.6</v>
+        <v>0.2</v>
       </c>
       <c r="L67" s="32" t="n">
-        <v>7.9</v>
+        <v>0.5</v>
       </c>
       <c r="M67" s="32" t="n">
-        <v>8.071</v>
+        <v>0.357</v>
       </c>
       <c r="N67" s="32" t="n">
-        <v>8.311999999999999</v>
+        <v>0.312</v>
       </c>
       <c r="O67" s="32" t="n">
-        <v>8.462</v>
+        <v>0.346</v>
       </c>
       <c r="P67" s="32" t="n">
-        <v>8.946999999999999</v>
+        <v>0.368</v>
       </c>
       <c r="Q67" s="35" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B68" s="32" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="C68" s="32" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="D68" s="32" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="E68" s="32" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="34" t="inlineStr">
-        <is>
-          <t>26th</t>
-        </is>
-      </c>
-      <c r="I68" s="32" t="inlineStr"/>
-      <c r="J68" s="36" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K68" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L68" s="32" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M68" s="32" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="N68" s="32" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="O68" s="32" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="P68" s="32" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="Q68" s="35" t="inlineStr">
-        <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
+        <is>
+          <t>Pittsburgh Pirates offense vs Cincinnati Reds defense</t>
+        </is>
+      </c>
+    </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Pittsburgh Pirates offense vs Cincinnati Reds defense</t>
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B70" s="30" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C70" s="30" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D70" s="30" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E70" s="30" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F70" s="30" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G70" s="30" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H70" s="30" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I70" s="30" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J70" s="30" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K70" s="30" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L70" s="30" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M70" s="30" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N70" s="30" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O70" s="30" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P70" s="30" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q70" s="30" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B71" s="30" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C71" s="30" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D71" s="30" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E71" s="30" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F71" s="30" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G71" s="30" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H71" s="30" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I71" s="30" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J71" s="30" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K71" s="30" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L71" s="30" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M71" s="30" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N71" s="30" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O71" s="30" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P71" s="30" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q71" s="30" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A71" s="31" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="C71" s="32" t="n">
+        <v>5.033</v>
+      </c>
+      <c r="D71" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="E71" s="32" t="n">
+        <v>4.867</v>
+      </c>
+      <c r="F71" s="32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G71" s="32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H71" s="36" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J71" s="34" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="K71" s="32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L71" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="M71" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="N71" s="32" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O71" s="32" t="n">
+        <v>4.933</v>
+      </c>
+      <c r="P71" s="32" t="n">
+        <v>4.658</v>
+      </c>
+      <c r="Q71" s="35" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="31" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B72" s="32" t="n">
-        <v>4.767</v>
+        <v>8.737</v>
       </c>
       <c r="C72" s="32" t="n">
-        <v>5.033</v>
+        <v>8.962</v>
       </c>
       <c r="D72" s="32" t="n">
-        <v>4.6</v>
+        <v>8.625</v>
       </c>
       <c r="E72" s="32" t="n">
-        <v>4.867</v>
+        <v>8.786</v>
       </c>
       <c r="F72" s="32" t="n">
-        <v>5.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G72" s="32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H72" s="36" t="inlineStr">
-        <is>
-          <t>12th</t>
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H72" s="33" t="inlineStr">
+        <is>
+          <t>3rd</t>
         </is>
       </c>
       <c r="I72" s="32" t="inlineStr">
@@ -19733,280 +19664,217 @@
       </c>
       <c r="J72" s="34" t="inlineStr">
         <is>
-          <t>25th</t>
+          <t>21st</t>
         </is>
       </c>
       <c r="K72" s="32" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="L72" s="32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M72" s="32" t="n">
-        <v>6</v>
+        <v>8.714</v>
       </c>
       <c r="N72" s="32" t="n">
-        <v>5.15</v>
+        <v>8.263</v>
       </c>
       <c r="O72" s="32" t="n">
-        <v>4.933</v>
+        <v>8.207000000000001</v>
       </c>
       <c r="P72" s="32" t="n">
-        <v>4.658</v>
+        <v>8.054</v>
       </c>
       <c r="Q72" s="35" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="31" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B73" s="32" t="n">
-        <v>8.737</v>
+        <v>1</v>
       </c>
       <c r="C73" s="32" t="n">
-        <v>8.962</v>
+        <v>1</v>
       </c>
       <c r="D73" s="32" t="n">
-        <v>8.625</v>
+        <v>0.75</v>
       </c>
       <c r="E73" s="32" t="n">
-        <v>8.786</v>
+        <v>0.786</v>
       </c>
       <c r="F73" s="32" t="n">
-        <v>9.800000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="G73" s="32" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I73" s="32" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K73" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="L73" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="M73" s="32" t="n">
-        <v>8.714</v>
-      </c>
-      <c r="N73" s="32" t="n">
-        <v>8.263</v>
-      </c>
-      <c r="O73" s="32" t="n">
-        <v>8.207000000000001</v>
-      </c>
-      <c r="P73" s="32" t="n">
-        <v>8.054</v>
+        <v>0.6</v>
+      </c>
+      <c r="H73" s="34" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr"/>
+      <c r="J73" s="35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P73" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="Q73" s="35" t="inlineStr">
         <is>
-          <t>Opp Hits/G</t>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="31" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B74" s="32" t="n">
-        <v>1</v>
+        <v>9.816000000000001</v>
       </c>
       <c r="C74" s="32" t="n">
-        <v>1</v>
+        <v>10.462</v>
       </c>
       <c r="D74" s="32" t="n">
-        <v>0.75</v>
+        <v>10.688</v>
       </c>
       <c r="E74" s="32" t="n">
-        <v>0.786</v>
+        <v>10.929</v>
       </c>
       <c r="F74" s="32" t="n">
-        <v>0.9</v>
+        <v>10.2</v>
       </c>
       <c r="G74" s="32" t="n">
-        <v>0.6</v>
+        <v>10.2</v>
       </c>
       <c r="H74" s="34" t="inlineStr">
         <is>
-          <t>27th</t>
+          <t>26th</t>
         </is>
       </c>
       <c r="I74" s="32" t="inlineStr"/>
-      <c r="J74" s="35" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="32" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J74" s="36" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="K74" s="32" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="L74" s="32" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="M74" s="32" t="n">
+        <v>7.143</v>
+      </c>
+      <c r="N74" s="32" t="n">
+        <v>7.105</v>
+      </c>
+      <c r="O74" s="32" t="n">
+        <v>6.966</v>
+      </c>
+      <c r="P74" s="32" t="n">
+        <v>7.432</v>
       </c>
       <c r="Q74" s="35" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="31" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B75" s="32" t="n">
-        <v>9.816000000000001</v>
+        <v>0.526</v>
       </c>
       <c r="C75" s="32" t="n">
-        <v>10.462</v>
+        <v>0.462</v>
       </c>
       <c r="D75" s="32" t="n">
-        <v>10.688</v>
+        <v>0.312</v>
       </c>
       <c r="E75" s="32" t="n">
-        <v>10.929</v>
+        <v>0.214</v>
       </c>
       <c r="F75" s="32" t="n">
-        <v>10.2</v>
+        <v>0.3</v>
       </c>
       <c r="G75" s="32" t="n">
-        <v>10.2</v>
+        <v>0.4</v>
       </c>
       <c r="H75" s="34" t="inlineStr">
         <is>
-          <t>26th</t>
+          <t>21st</t>
         </is>
       </c>
       <c r="I75" s="32" t="inlineStr"/>
-      <c r="J75" s="36" t="inlineStr">
-        <is>
-          <t>16th</t>
+      <c r="J75" s="33" t="inlineStr">
+        <is>
+          <t>8th</t>
         </is>
       </c>
       <c r="K75" s="32" t="n">
-        <v>8.4</v>
+        <v>0.2</v>
       </c>
       <c r="L75" s="32" t="n">
-        <v>6.667</v>
+        <v>0.111</v>
       </c>
       <c r="M75" s="32" t="n">
-        <v>7.143</v>
+        <v>0.286</v>
       </c>
       <c r="N75" s="32" t="n">
-        <v>7.105</v>
+        <v>0.421</v>
       </c>
       <c r="O75" s="32" t="n">
-        <v>6.966</v>
+        <v>0.483</v>
       </c>
       <c r="P75" s="32" t="n">
-        <v>7.432</v>
+        <v>0.459</v>
       </c>
       <c r="Q75" s="35" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="31" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B76" s="32" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="C76" s="32" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="D76" s="32" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="E76" s="32" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="F76" s="32" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G76" s="32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H76" s="34" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="I76" s="32" t="inlineStr"/>
-      <c r="J76" s="33" t="inlineStr">
-        <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="K76" s="32" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L76" s="32" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="M76" s="32" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="N76" s="32" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="O76" s="32" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="P76" s="32" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="Q76" s="35" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>

--- a/data/output/workbook/2026-06-28.xlsx
+++ b/data/output/workbook/2026-06-28.xlsx
@@ -430,7 +430,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9620250"/>
+    <ext cx="10125075" cy="9220200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -550,7 +550,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9429750"/>
+    <ext cx="10125075" cy="9048750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -610,7 +610,7 @@
       <row>3</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10125075" cy="9258300"/>
+    <ext cx="10125075" cy="9658350"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -953,7 +953,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-06-28 18:04</t>
+          <t>2026-06-28 19:18</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:Q73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1174,811 +1174,811 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>Texas Rangers offense vs Toronto Blue Jays defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B60" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D60" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E60" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F60" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G60" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H60" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I60" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J60" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K60" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L60" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M60" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N60" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O60" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P60" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q60" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B61" s="31" t="n">
+        <v>3.909</v>
+      </c>
+      <c r="C61" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D61" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E61" s="31" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="F61" s="31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G61" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H61" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
+        </is>
+      </c>
+      <c r="I61" s="31" t="inlineStr"/>
+      <c r="J61" s="32" t="inlineStr">
+        <is>
+          <t>3rd</t>
+        </is>
+      </c>
+      <c r="K61" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L61" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M61" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N61" s="31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O61" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="P61" s="31" t="n">
+        <v>4.135</v>
+      </c>
+      <c r="Q61" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
     <row r="62">
-      <c r="A62" s="28" t="inlineStr">
-        <is>
-          <t>Texas Rangers offense vs Toronto Blue Jays defense</t>
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B62" s="31" t="n">
+        <v>7.919</v>
+      </c>
+      <c r="C62" s="31" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="D62" s="31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E62" s="31" t="n">
+        <v>7.692</v>
+      </c>
+      <c r="F62" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="G62" s="31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H62" s="32" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="I62" s="31" t="inlineStr"/>
+      <c r="J62" s="32" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="K62" s="31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="L62" s="31" t="n">
+        <v>6.111</v>
+      </c>
+      <c r="M62" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="N62" s="31" t="n">
+        <v>7.316</v>
+      </c>
+      <c r="O62" s="31" t="n">
+        <v>7.828</v>
+      </c>
+      <c r="P62" s="31" t="n">
+        <v>7.889</v>
+      </c>
+      <c r="Q62" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B63" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C63" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D63" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E63" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F63" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G63" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H63" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I63" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J63" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K63" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L63" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M63" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N63" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O63" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P63" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q63" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A63" s="30" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B63" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" s="31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D63" s="31" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="E63" s="31" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="F63" s="31" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G63" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H63" s="32" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="I63" s="31" t="inlineStr"/>
+      <c r="J63" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K63" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L63" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M63" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N63" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O63" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P63" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q63" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B64" s="31" t="n">
-        <v>3.909</v>
+        <v>8.595000000000001</v>
       </c>
       <c r="C64" s="31" t="n">
-        <v>4.1</v>
+        <v>8.44</v>
       </c>
       <c r="D64" s="31" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="E64" s="31" t="n">
-        <v>3.467</v>
+        <v>6.846</v>
       </c>
       <c r="F64" s="31" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="G64" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H64" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
+        <v>7.2</v>
+      </c>
+      <c r="H64" s="32" t="inlineStr">
+        <is>
+          <t>3rd</t>
         </is>
       </c>
       <c r="I64" s="31" t="inlineStr"/>
       <c r="J64" s="32" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="K64" s="31" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="L64" s="31" t="n">
-        <v>2</v>
+        <v>11.444</v>
       </c>
       <c r="M64" s="31" t="n">
-        <v>2.8</v>
+        <v>10.143</v>
       </c>
       <c r="N64" s="31" t="n">
-        <v>3.1</v>
+        <v>9.579000000000001</v>
       </c>
       <c r="O64" s="31" t="n">
-        <v>4</v>
+        <v>9.414</v>
       </c>
       <c r="P64" s="31" t="n">
-        <v>4.135</v>
+        <v>10.222</v>
       </c>
       <c r="Q64" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B65" s="31" t="n">
-        <v>7.919</v>
+        <v>0.297</v>
       </c>
       <c r="C65" s="31" t="n">
-        <v>7.96</v>
+        <v>0.32</v>
       </c>
       <c r="D65" s="31" t="n">
-        <v>7.5</v>
+        <v>0.125</v>
       </c>
       <c r="E65" s="31" t="n">
-        <v>7.692</v>
+        <v>0.154</v>
       </c>
       <c r="F65" s="31" t="n">
-        <v>7.8</v>
+        <v>0.2</v>
       </c>
       <c r="G65" s="31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H65" s="32" t="inlineStr">
-        <is>
-          <t>2nd</t>
+        <v>0.4</v>
+      </c>
+      <c r="H65" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
         </is>
       </c>
       <c r="I65" s="31" t="inlineStr"/>
       <c r="J65" s="32" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="K65" s="31" t="n">
-        <v>5.2</v>
+        <v>0.2</v>
       </c>
       <c r="L65" s="31" t="n">
-        <v>6.111</v>
+        <v>0.111</v>
       </c>
       <c r="M65" s="31" t="n">
-        <v>7</v>
+        <v>0.429</v>
       </c>
       <c r="N65" s="31" t="n">
-        <v>7.316</v>
+        <v>0.421</v>
       </c>
       <c r="O65" s="31" t="n">
-        <v>7.828</v>
+        <v>0.517</v>
       </c>
       <c r="P65" s="31" t="n">
-        <v>7.889</v>
+        <v>0.444</v>
       </c>
       <c r="Q65" s="34" t="inlineStr">
         <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>Toronto Blue Jays offense vs Texas Rangers defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C68" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D68" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E68" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F68" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G68" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H68" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I68" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J68" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K68" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L68" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M68" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N68" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O68" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P68" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q68" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B69" s="31" t="n">
+        <v>4.054</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>3.967</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="G69" s="31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H69" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr"/>
+      <c r="J69" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>4.133</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>3.773</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B70" s="31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>8.414</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>8.683999999999999</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>8.356999999999999</v>
+      </c>
+      <c r="F70" s="31" t="n">
+        <v>8.111000000000001</v>
+      </c>
+      <c r="G70" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="H70" s="35" t="inlineStr">
+        <is>
+          <t>15th</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="35" t="inlineStr">
+        <is>
+          <t>13th</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L70" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="M70" s="31" t="n">
+        <v>7.769</v>
+      </c>
+      <c r="N70" s="31" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="O70" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P70" s="31" t="n">
+        <v>7.703</v>
+      </c>
+      <c r="Q70" s="34" t="inlineStr">
+        <is>
           <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="30" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="30" t="inlineStr">
         <is>
           <t>HR/G</t>
         </is>
       </c>
-      <c r="B66" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" s="31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="D66" s="31" t="n">
-        <v>0.8120000000000001</v>
-      </c>
-      <c r="E66" s="31" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="F66" s="31" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G66" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H66" s="32" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I66" s="31" t="inlineStr"/>
-      <c r="J66" s="34" t="inlineStr">
+      <c r="B71" s="31" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="C71" s="31" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="D71" s="31" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="E71" s="31" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="F71" s="31" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="G71" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H71" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
+        </is>
+      </c>
+      <c r="I71" s="31" t="inlineStr"/>
+      <c r="J71" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K66" s="31" t="inlineStr">
+      <c r="K71" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L66" s="31" t="inlineStr">
+      <c r="L71" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M66" s="31" t="inlineStr">
+      <c r="M71" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N66" s="31" t="inlineStr">
+      <c r="N71" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O66" s="31" t="inlineStr">
+      <c r="O71" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P66" s="31" t="inlineStr">
+      <c r="P71" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q66" s="34" t="inlineStr">
+      <c r="Q71" s="34" t="inlineStr">
         <is>
           <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B67" s="31" t="n">
-        <v>8.595000000000001</v>
-      </c>
-      <c r="C67" s="31" t="n">
-        <v>8.44</v>
-      </c>
-      <c r="D67" s="31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E67" s="31" t="n">
-        <v>6.846</v>
-      </c>
-      <c r="F67" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="G67" s="31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H67" s="32" t="inlineStr">
-        <is>
-          <t>3rd</t>
-        </is>
-      </c>
-      <c r="I67" s="31" t="inlineStr"/>
-      <c r="J67" s="32" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K67" s="31" t="n">
-        <v>12</v>
-      </c>
-      <c r="L67" s="31" t="n">
-        <v>11.444</v>
-      </c>
-      <c r="M67" s="31" t="n">
-        <v>10.143</v>
-      </c>
-      <c r="N67" s="31" t="n">
-        <v>9.579000000000001</v>
-      </c>
-      <c r="O67" s="31" t="n">
-        <v>9.414</v>
-      </c>
-      <c r="P67" s="31" t="n">
-        <v>10.222</v>
-      </c>
-      <c r="Q67" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B68" s="31" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="C68" s="31" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="D68" s="31" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E68" s="31" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="F68" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G68" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H68" s="35" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I68" s="31" t="inlineStr"/>
-      <c r="J68" s="32" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="K68" s="31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L68" s="31" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="M68" s="31" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="N68" s="31" t="n">
-        <v>0.421</v>
-      </c>
-      <c r="O68" s="31" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="P68" s="31" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="Q68" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="28" t="inlineStr">
-        <is>
-          <t>Toronto Blue Jays offense vs Texas Rangers defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B71" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C71" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D71" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E71" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F71" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G71" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H71" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I71" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J71" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K71" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L71" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M71" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N71" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O71" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P71" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q71" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>4.054</v>
+        <v>7.167</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>3.967</v>
+        <v>6.966</v>
       </c>
       <c r="D72" s="31" t="n">
-        <v>4.15</v>
+        <v>7.421</v>
       </c>
       <c r="E72" s="31" t="n">
-        <v>4.133</v>
+        <v>7.571</v>
       </c>
       <c r="F72" s="31" t="n">
-        <v>4</v>
+        <v>7.778</v>
       </c>
       <c r="G72" s="31" t="n">
-        <v>3.8</v>
+        <v>9.4</v>
       </c>
       <c r="H72" s="35" t="inlineStr">
         <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="J72" s="33" t="inlineStr">
+        <is>
+          <t>23rd</t>
         </is>
       </c>
       <c r="K72" s="31" t="n">
-        <v>4</v>
+        <v>7.4</v>
       </c>
       <c r="L72" s="31" t="n">
-        <v>4.2</v>
+        <v>6.8</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>4.2</v>
+        <v>7.385</v>
       </c>
       <c r="N72" s="31" t="n">
-        <v>4.3</v>
+        <v>7.562</v>
       </c>
       <c r="O72" s="31" t="n">
-        <v>4.133</v>
+        <v>7.84</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>3.773</v>
+        <v>8.513999999999999</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>8.5</v>
+        <v>0.583</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>8.414</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D73" s="31" t="n">
-        <v>8.683999999999999</v>
+        <v>0.789</v>
       </c>
       <c r="E73" s="31" t="n">
-        <v>8.356999999999999</v>
+        <v>0.429</v>
       </c>
       <c r="F73" s="31" t="n">
-        <v>8.111000000000001</v>
+        <v>0.222</v>
       </c>
       <c r="G73" s="31" t="n">
-        <v>8</v>
+        <v>0.4</v>
       </c>
       <c r="H73" s="35" t="inlineStr">
         <is>
-          <t>15th</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>13th</t>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J73" s="33" t="inlineStr">
+        <is>
+          <t>29th</t>
         </is>
       </c>
       <c r="K73" s="31" t="n">
-        <v>7.4</v>
+        <v>1.4</v>
       </c>
       <c r="L73" s="31" t="n">
-        <v>8</v>
+        <v>1.3</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>7.769</v>
+        <v>1.231</v>
       </c>
       <c r="N73" s="31" t="n">
-        <v>7.75</v>
+        <v>1.188</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>7.703</v>
+        <v>0.892</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="D74" s="31" t="n">
-        <v>0.737</v>
-      </c>
-      <c r="E74" s="31" t="n">
-        <v>0.786</v>
-      </c>
-      <c r="F74" s="31" t="n">
-        <v>0.778</v>
-      </c>
-      <c r="G74" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H74" s="35" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P74" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>7.167</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>6.966</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>7.421</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>7.571</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>7.778</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="H75" s="35" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr">
-        <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="J75" s="33" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>7.385</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>7.562</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>7.84</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>8.513999999999999</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B76" s="31" t="n">
-        <v>0.583</v>
-      </c>
-      <c r="C76" s="31" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D76" s="31" t="n">
-        <v>0.789</v>
-      </c>
-      <c r="E76" s="31" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="F76" s="31" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="G76" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H76" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I76" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J76" s="33" t="inlineStr">
-        <is>
-          <t>29th</t>
-        </is>
-      </c>
-      <c r="K76" s="31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="L76" s="31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="M76" s="31" t="n">
-        <v>1.231</v>
-      </c>
-      <c r="N76" s="31" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="O76" s="31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="P76" s="31" t="n">
-        <v>0.892</v>
-      </c>
-      <c r="Q76" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -4517,7 +4517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:Q72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4534,807 +4534,807 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="28" t="inlineStr">
+        <is>
+          <t>Philadelphia Phillies offense vs New York Mets defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B59" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C59" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D59" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E59" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F59" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G59" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H59" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I59" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J59" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K59" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L59" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M59" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N59" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O59" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P59" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q59" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B60" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C60" s="31" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="D60" s="31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="E60" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F60" s="31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G60" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H60" s="35" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="I60" s="31" t="inlineStr"/>
+      <c r="J60" s="33" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="K60" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L60" s="31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M60" s="31" t="n">
+        <v>4.067</v>
+      </c>
+      <c r="N60" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O60" s="31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P60" s="31" t="n">
+        <v>4.214</v>
+      </c>
+      <c r="Q60" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
-      <c r="A61" s="28" t="inlineStr">
-        <is>
-          <t>Philadelphia Phillies offense vs New York Mets defense</t>
+      <c r="A61" s="30" t="inlineStr">
+        <is>
+          <t>Hits/G</t>
+        </is>
+      </c>
+      <c r="B61" s="31" t="n">
+        <v>7.568</v>
+      </c>
+      <c r="C61" s="31" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="D61" s="31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E61" s="31" t="n">
+        <v>7.923</v>
+      </c>
+      <c r="F61" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="G61" s="31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H61" s="33" t="inlineStr">
+        <is>
+          <t>25th</t>
+        </is>
+      </c>
+      <c r="I61" s="31" t="inlineStr"/>
+      <c r="J61" s="35" t="inlineStr">
+        <is>
+          <t>12th</t>
+        </is>
+      </c>
+      <c r="K61" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L61" s="31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="M61" s="31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N61" s="31" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="O61" s="31" t="n">
+        <v>7.862</v>
+      </c>
+      <c r="P61" s="31" t="n">
+        <v>7.842</v>
+      </c>
+      <c r="Q61" s="34" t="inlineStr">
+        <is>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B62" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C62" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D62" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E62" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F62" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G62" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H62" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I62" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J62" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K62" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L62" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M62" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N62" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O62" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P62" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q62" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B62" s="31" t="n">
+        <v>1.135</v>
+      </c>
+      <c r="C62" s="31" t="n">
+        <v>1.148</v>
+      </c>
+      <c r="D62" s="31" t="n">
+        <v>1.222</v>
+      </c>
+      <c r="E62" s="31" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="F62" s="31" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="G62" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H62" s="35" t="inlineStr">
+        <is>
+          <t>16th</t>
+        </is>
+      </c>
+      <c r="I62" s="31" t="inlineStr"/>
+      <c r="J62" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K62" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L62" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M62" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N62" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O62" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P62" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q62" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B63" s="31" t="n">
-        <v>4.1</v>
+        <v>8.568</v>
       </c>
       <c r="C63" s="31" t="n">
-        <v>4.067</v>
+        <v>8.704000000000001</v>
       </c>
       <c r="D63" s="31" t="n">
-        <v>3.95</v>
+        <v>8.611000000000001</v>
       </c>
       <c r="E63" s="31" t="n">
-        <v>4.6</v>
+        <v>9.077</v>
       </c>
       <c r="F63" s="31" t="n">
-        <v>4.3</v>
+        <v>9.555999999999999</v>
       </c>
       <c r="G63" s="31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="H63" s="35" t="inlineStr">
-        <is>
-          <t>20th</t>
+        <v>10.6</v>
+      </c>
+      <c r="H63" s="33" t="inlineStr">
+        <is>
+          <t>28th</t>
         </is>
       </c>
       <c r="I63" s="31" t="inlineStr"/>
       <c r="J63" s="33" t="inlineStr">
         <is>
-          <t>22nd</t>
+          <t>27th</t>
         </is>
       </c>
       <c r="K63" s="31" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="L63" s="31" t="n">
-        <v>4.1</v>
+        <v>8.5</v>
       </c>
       <c r="M63" s="31" t="n">
-        <v>4.067</v>
+        <v>8.933</v>
       </c>
       <c r="N63" s="31" t="n">
-        <v>4.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O63" s="31" t="n">
-        <v>4.5</v>
+        <v>8.69</v>
       </c>
       <c r="P63" s="31" t="n">
-        <v>4.214</v>
+        <v>8.920999999999999</v>
       </c>
       <c r="Q63" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="30" t="inlineStr">
         <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B64" s="31" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="C64" s="31" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="D64" s="31" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="E64" s="31" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="F64" s="31" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="G64" s="31" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H64" s="32" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="I64" s="31" t="inlineStr">
+        <is>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="J64" s="35" t="inlineStr">
+        <is>
+          <t>20th</t>
+        </is>
+      </c>
+      <c r="K64" s="31" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L64" s="31" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M64" s="31" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="N64" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O64" s="31" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="P64" s="31" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="Q64" s="34" t="inlineStr">
+        <is>
+          <t>Opp 1st Inn R/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t>New York Mets offense vs Philadelphia Phillies defense</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>Stat</t>
+        </is>
+      </c>
+      <c r="B67" s="29" t="inlineStr">
+        <is>
+          <t>A Season</t>
+        </is>
+      </c>
+      <c r="C67" s="29" t="inlineStr">
+        <is>
+          <t>A L30</t>
+        </is>
+      </c>
+      <c r="D67" s="29" t="inlineStr">
+        <is>
+          <t>A L20</t>
+        </is>
+      </c>
+      <c r="E67" s="29" t="inlineStr">
+        <is>
+          <t>A L15</t>
+        </is>
+      </c>
+      <c r="F67" s="29" t="inlineStr">
+        <is>
+          <t>A L10</t>
+        </is>
+      </c>
+      <c r="G67" s="29" t="inlineStr">
+        <is>
+          <t>A L5</t>
+        </is>
+      </c>
+      <c r="H67" s="29" t="inlineStr">
+        <is>
+          <t>A Rk</t>
+        </is>
+      </c>
+      <c r="I67" s="29" t="inlineStr">
+        <is>
+          <t>Adv</t>
+        </is>
+      </c>
+      <c r="J67" s="29" t="inlineStr">
+        <is>
+          <t>H Rk</t>
+        </is>
+      </c>
+      <c r="K67" s="29" t="inlineStr">
+        <is>
+          <t>H L5</t>
+        </is>
+      </c>
+      <c r="L67" s="29" t="inlineStr">
+        <is>
+          <t>H L10</t>
+        </is>
+      </c>
+      <c r="M67" s="29" t="inlineStr">
+        <is>
+          <t>H L15</t>
+        </is>
+      </c>
+      <c r="N67" s="29" t="inlineStr">
+        <is>
+          <t>H L20</t>
+        </is>
+      </c>
+      <c r="O67" s="29" t="inlineStr">
+        <is>
+          <t>H L30</t>
+        </is>
+      </c>
+      <c r="P67" s="29" t="inlineStr">
+        <is>
+          <t>H Season</t>
+        </is>
+      </c>
+      <c r="Q67" s="29" t="inlineStr">
+        <is>
+          <t>Opp stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>Runs/G</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="n">
+        <v>3.357</v>
+      </c>
+      <c r="C68" s="31" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="D68" s="31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E68" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G68" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H68" s="33" t="inlineStr">
+        <is>
+          <t>22nd</t>
+        </is>
+      </c>
+      <c r="I68" s="31" t="inlineStr"/>
+      <c r="J68" s="32" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="K68" s="31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L68" s="31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M68" s="31" t="n">
+        <v>5.067</v>
+      </c>
+      <c r="N68" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O68" s="31" t="n">
+        <v>5.633</v>
+      </c>
+      <c r="P68" s="31" t="n">
+        <v>5.375</v>
+      </c>
+      <c r="Q68" s="34" t="inlineStr">
+        <is>
+          <t>Opp Runs/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
           <t>Hits/G</t>
         </is>
       </c>
-      <c r="B64" s="31" t="n">
-        <v>7.568</v>
-      </c>
-      <c r="C64" s="31" t="n">
-        <v>7.37</v>
-      </c>
-      <c r="D64" s="31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E64" s="31" t="n">
-        <v>7.923</v>
-      </c>
-      <c r="F64" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="G64" s="31" t="n">
+      <c r="B69" s="31" t="n">
+        <v>7.053</v>
+      </c>
+      <c r="C69" s="31" t="n">
+        <v>6.586</v>
+      </c>
+      <c r="D69" s="31" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="E69" s="31" t="n">
+        <v>6.333</v>
+      </c>
+      <c r="F69" s="31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="G69" s="31" t="n">
         <v>5.8</v>
       </c>
-      <c r="H64" s="33" t="inlineStr">
-        <is>
-          <t>25th</t>
-        </is>
-      </c>
-      <c r="I64" s="31" t="inlineStr"/>
-      <c r="J64" s="35" t="inlineStr">
-        <is>
-          <t>12th</t>
-        </is>
-      </c>
-      <c r="K64" s="31" t="n">
+      <c r="H69" s="33" t="inlineStr">
+        <is>
+          <t>26th</t>
+        </is>
+      </c>
+      <c r="I69" s="31" t="inlineStr"/>
+      <c r="J69" s="32" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="n">
         <v>7.4</v>
       </c>
-      <c r="L64" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="M64" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="N64" s="31" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="O64" s="31" t="n">
-        <v>7.862</v>
-      </c>
-      <c r="P64" s="31" t="n">
-        <v>7.842</v>
-      </c>
-      <c r="Q64" s="34" t="inlineStr">
+      <c r="L69" s="31" t="n">
+        <v>8.888999999999999</v>
+      </c>
+      <c r="M69" s="31" t="n">
+        <v>9.769</v>
+      </c>
+      <c r="N69" s="31" t="n">
+        <v>9.888999999999999</v>
+      </c>
+      <c r="O69" s="31" t="n">
+        <v>10.222</v>
+      </c>
+      <c r="P69" s="31" t="n">
+        <v>9.891999999999999</v>
+      </c>
+      <c r="Q69" s="34" t="inlineStr">
         <is>
           <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="30" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>HR/G</t>
         </is>
       </c>
-      <c r="B65" s="31" t="n">
-        <v>1.135</v>
-      </c>
-      <c r="C65" s="31" t="n">
-        <v>1.148</v>
-      </c>
-      <c r="D65" s="31" t="n">
-        <v>1.222</v>
-      </c>
-      <c r="E65" s="31" t="n">
-        <v>1.385</v>
-      </c>
-      <c r="F65" s="31" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="G65" s="31" t="n">
+      <c r="B70" s="31" t="n">
+        <v>0.737</v>
+      </c>
+      <c r="C70" s="31" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D70" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E70" s="31" t="n">
+        <v>0.733</v>
+      </c>
+      <c r="F70" s="31" t="n">
         <v>0.8</v>
       </c>
-      <c r="H65" s="35" t="inlineStr">
-        <is>
-          <t>16th</t>
-        </is>
-      </c>
-      <c r="I65" s="31" t="inlineStr"/>
-      <c r="J65" s="34" t="inlineStr">
+      <c r="G70" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H70" s="32" t="inlineStr">
+        <is>
+          <t>9th</t>
+        </is>
+      </c>
+      <c r="I70" s="31" t="inlineStr"/>
+      <c r="J70" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K65" s="31" t="inlineStr">
+      <c r="K70" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L65" s="31" t="inlineStr">
+      <c r="L70" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M65" s="31" t="inlineStr">
+      <c r="M70" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="N65" s="31" t="inlineStr">
+      <c r="N70" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O65" s="31" t="inlineStr">
+      <c r="O70" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P65" s="31" t="inlineStr">
+      <c r="P70" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q65" s="34" t="inlineStr">
+      <c r="Q70" s="34" t="inlineStr">
         <is>
           <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B66" s="31" t="n">
-        <v>8.568</v>
-      </c>
-      <c r="C66" s="31" t="n">
-        <v>8.704000000000001</v>
-      </c>
-      <c r="D66" s="31" t="n">
-        <v>8.611000000000001</v>
-      </c>
-      <c r="E66" s="31" t="n">
-        <v>9.077</v>
-      </c>
-      <c r="F66" s="31" t="n">
-        <v>9.555999999999999</v>
-      </c>
-      <c r="G66" s="31" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="H66" s="33" t="inlineStr">
-        <is>
-          <t>28th</t>
-        </is>
-      </c>
-      <c r="I66" s="31" t="inlineStr"/>
-      <c r="J66" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K66" s="31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L66" s="31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="M66" s="31" t="n">
-        <v>8.933</v>
-      </c>
-      <c r="N66" s="31" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="O66" s="31" t="n">
-        <v>8.69</v>
-      </c>
-      <c r="P66" s="31" t="n">
-        <v>8.920999999999999</v>
-      </c>
-      <c r="Q66" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B67" s="31" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="C67" s="31" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="D67" s="31" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="E67" s="31" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="F67" s="31" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="G67" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H67" s="32" t="inlineStr">
-        <is>
-          <t>6th</t>
-        </is>
-      </c>
-      <c r="I67" s="31" t="inlineStr">
-        <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="J67" s="35" t="inlineStr">
-        <is>
-          <t>20th</t>
-        </is>
-      </c>
-      <c r="K67" s="31" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L67" s="31" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="M67" s="31" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="N67" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O67" s="31" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="P67" s="31" t="n">
-        <v>0.474</v>
-      </c>
-      <c r="Q67" s="34" t="inlineStr">
-        <is>
-          <t>Opp 1st Inn R/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>New York Mets offense vs Philadelphia Phillies defense</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="29" t="inlineStr">
-        <is>
-          <t>Stat</t>
-        </is>
-      </c>
-      <c r="B70" s="29" t="inlineStr">
-        <is>
-          <t>A Season</t>
-        </is>
-      </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>A L30</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
-        <is>
-          <t>A L20</t>
-        </is>
-      </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>A L15</t>
-        </is>
-      </c>
-      <c r="F70" s="29" t="inlineStr">
-        <is>
-          <t>A L10</t>
-        </is>
-      </c>
-      <c r="G70" s="29" t="inlineStr">
-        <is>
-          <t>A L5</t>
-        </is>
-      </c>
-      <c r="H70" s="29" t="inlineStr">
-        <is>
-          <t>A Rk</t>
-        </is>
-      </c>
-      <c r="I70" s="29" t="inlineStr">
-        <is>
-          <t>Adv</t>
-        </is>
-      </c>
-      <c r="J70" s="29" t="inlineStr">
-        <is>
-          <t>H Rk</t>
-        </is>
-      </c>
-      <c r="K70" s="29" t="inlineStr">
-        <is>
-          <t>H L5</t>
-        </is>
-      </c>
-      <c r="L70" s="29" t="inlineStr">
-        <is>
-          <t>H L10</t>
-        </is>
-      </c>
-      <c r="M70" s="29" t="inlineStr">
-        <is>
-          <t>H L15</t>
-        </is>
-      </c>
-      <c r="N70" s="29" t="inlineStr">
-        <is>
-          <t>H L20</t>
-        </is>
-      </c>
-      <c r="O70" s="29" t="inlineStr">
-        <is>
-          <t>H L30</t>
-        </is>
-      </c>
-      <c r="P70" s="29" t="inlineStr">
-        <is>
-          <t>H Season</t>
-        </is>
-      </c>
-      <c r="Q70" s="29" t="inlineStr">
-        <is>
-          <t>Opp stat</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>Runs/G</t>
+          <t>Batter K/G</t>
         </is>
       </c>
       <c r="B71" s="31" t="n">
-        <v>3.357</v>
+        <v>8.395</v>
       </c>
       <c r="C71" s="31" t="n">
-        <v>2.667</v>
+        <v>8.448</v>
       </c>
       <c r="D71" s="31" t="n">
-        <v>2.85</v>
+        <v>8.85</v>
       </c>
       <c r="E71" s="31" t="n">
-        <v>3</v>
+        <v>8.867000000000001</v>
       </c>
       <c r="F71" s="31" t="n">
-        <v>2.8</v>
+        <v>9.5</v>
       </c>
       <c r="G71" s="31" t="n">
-        <v>2.8</v>
+        <v>10</v>
       </c>
       <c r="H71" s="33" t="inlineStr">
         <is>
-          <t>22nd</t>
+          <t>23rd</t>
         </is>
       </c>
       <c r="I71" s="31" t="inlineStr"/>
       <c r="J71" s="32" t="inlineStr">
         <is>
-          <t>8th</t>
+          <t>7th</t>
         </is>
       </c>
       <c r="K71" s="31" t="n">
-        <v>2.8</v>
+        <v>9.6</v>
       </c>
       <c r="L71" s="31" t="n">
-        <v>4.7</v>
+        <v>10.444</v>
       </c>
       <c r="M71" s="31" t="n">
-        <v>5.067</v>
+        <v>9.154</v>
       </c>
       <c r="N71" s="31" t="n">
-        <v>5.1</v>
+        <v>9.055999999999999</v>
       </c>
       <c r="O71" s="31" t="n">
-        <v>5.633</v>
+        <v>9.074</v>
       </c>
       <c r="P71" s="31" t="n">
-        <v>5.375</v>
+        <v>9.486000000000001</v>
       </c>
       <c r="Q71" s="34" t="inlineStr">
         <is>
-          <t>Opp Runs/G</t>
+          <t>Opp Batter K/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>Hits/G</t>
+          <t>1st Inn R/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>7.053</v>
+        <v>0.553</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>6.586</v>
+        <v>0.414</v>
       </c>
       <c r="D72" s="31" t="n">
-        <v>6.55</v>
+        <v>0.4</v>
       </c>
       <c r="E72" s="31" t="n">
-        <v>6.333</v>
+        <v>0.533</v>
       </c>
       <c r="F72" s="31" t="n">
-        <v>5.6</v>
+        <v>0.4</v>
       </c>
       <c r="G72" s="31" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H72" s="33" t="inlineStr">
-        <is>
-          <t>26th</t>
+        <v>0.8</v>
+      </c>
+      <c r="H72" s="32" t="inlineStr">
+        <is>
+          <t>10th</t>
         </is>
       </c>
       <c r="I72" s="31" t="inlineStr"/>
       <c r="J72" s="32" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="K72" s="31" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="L72" s="31" t="n">
-        <v>8.888999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="M72" s="31" t="n">
-        <v>9.769</v>
+        <v>0.615</v>
       </c>
       <c r="N72" s="31" t="n">
-        <v>9.888999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="O72" s="31" t="n">
-        <v>10.222</v>
+        <v>0.519</v>
       </c>
       <c r="P72" s="31" t="n">
-        <v>9.891999999999999</v>
+        <v>0.595</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="30" t="inlineStr">
-        <is>
-          <t>HR/G</t>
-        </is>
-      </c>
-      <c r="B73" s="31" t="n">
-        <v>0.737</v>
-      </c>
-      <c r="C73" s="31" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="D73" s="31" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E73" s="31" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="F73" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G73" s="31" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H73" s="32" t="inlineStr">
-        <is>
-          <t>9th</t>
-        </is>
-      </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P73" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q73" s="34" t="inlineStr">
-        <is>
-          <t>Opp HR/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="30" t="inlineStr">
-        <is>
-          <t>Batter K/G</t>
-        </is>
-      </c>
-      <c r="B74" s="31" t="n">
-        <v>8.395</v>
-      </c>
-      <c r="C74" s="31" t="n">
-        <v>8.448</v>
-      </c>
-      <c r="D74" s="31" t="n">
-        <v>8.85</v>
-      </c>
-      <c r="E74" s="31" t="n">
-        <v>8.867000000000001</v>
-      </c>
-      <c r="F74" s="31" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G74" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="H74" s="33" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="32" t="inlineStr">
-        <is>
-          <t>7th</t>
-        </is>
-      </c>
-      <c r="K74" s="31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="L74" s="31" t="n">
-        <v>10.444</v>
-      </c>
-      <c r="M74" s="31" t="n">
-        <v>9.154</v>
-      </c>
-      <c r="N74" s="31" t="n">
-        <v>9.055999999999999</v>
-      </c>
-      <c r="O74" s="31" t="n">
-        <v>9.074</v>
-      </c>
-      <c r="P74" s="31" t="n">
-        <v>9.486000000000001</v>
-      </c>
-      <c r="Q74" s="34" t="inlineStr">
-        <is>
-          <t>Opp Batter K/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="30" t="inlineStr">
-        <is>
-          <t>1st Inn R/G</t>
-        </is>
-      </c>
-      <c r="B75" s="31" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="C75" s="31" t="n">
-        <v>0.414</v>
-      </c>
-      <c r="D75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E75" s="31" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="F75" s="31" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G75" s="31" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H75" s="32" t="inlineStr">
-        <is>
-          <t>10th</t>
-        </is>
-      </c>
-      <c r="I75" s="31" t="inlineStr"/>
-      <c r="J75" s="32" t="inlineStr">
-        <is>
-          <t>1st</t>
-        </is>
-      </c>
-      <c r="K75" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="31" t="n">
-        <v>0.556</v>
-      </c>
-      <c r="M75" s="31" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="N75" s="31" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O75" s="31" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="P75" s="31" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="Q75" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -6201,7 +6201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6218,815 +6218,815 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="28" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="28" t="inlineStr">
         <is>
           <t>Kansas City Royals offense vs Chicago White Sox defense</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="29" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B61" s="29" t="inlineStr">
+      <c r="B63" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C61" s="29" t="inlineStr">
+      <c r="C63" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D61" s="29" t="inlineStr">
+      <c r="D63" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E61" s="29" t="inlineStr">
+      <c r="E63" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F61" s="29" t="inlineStr">
+      <c r="F63" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G61" s="29" t="inlineStr">
+      <c r="G63" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H61" s="29" t="inlineStr">
+      <c r="H63" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I61" s="29" t="inlineStr">
+      <c r="I63" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J61" s="29" t="inlineStr">
+      <c r="J63" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K61" s="29" t="inlineStr">
+      <c r="K63" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L61" s="29" t="inlineStr">
+      <c r="L63" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M61" s="29" t="inlineStr">
+      <c r="M63" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N61" s="29" t="inlineStr">
+      <c r="N63" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O61" s="29" t="inlineStr">
+      <c r="O63" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P61" s="29" t="inlineStr">
+      <c r="P63" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q61" s="29" t="inlineStr">
+      <c r="Q63" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B62" s="31" t="n">
-        <v>3.875</v>
-      </c>
-      <c r="C62" s="31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D62" s="31" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E62" s="31" t="n">
-        <v>4.867</v>
-      </c>
-      <c r="F62" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G62" s="31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H62" s="33" t="inlineStr">
-        <is>
-          <t>23rd</t>
-        </is>
-      </c>
-      <c r="I62" s="31" t="inlineStr"/>
-      <c r="J62" s="33" t="inlineStr">
-        <is>
-          <t>21st</t>
-        </is>
-      </c>
-      <c r="K62" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L62" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="M62" s="31" t="n">
-        <v>5.133</v>
-      </c>
-      <c r="N62" s="31" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="O62" s="31" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="P62" s="31" t="n">
-        <v>5.105</v>
-      </c>
-      <c r="Q62" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B63" s="31" t="n">
-        <v>7.838</v>
-      </c>
-      <c r="C63" s="31" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="D63" s="31" t="n">
-        <v>8.555999999999999</v>
-      </c>
-      <c r="E63" s="31" t="n">
-        <v>8.692</v>
-      </c>
-      <c r="F63" s="31" t="n">
-        <v>7.556</v>
-      </c>
-      <c r="G63" s="31" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="H63" s="35" t="inlineStr">
-        <is>
-          <t>19th</t>
-        </is>
-      </c>
-      <c r="I63" s="31" t="inlineStr"/>
-      <c r="J63" s="35" t="inlineStr">
-        <is>
-          <t>11th</t>
-        </is>
-      </c>
-      <c r="K63" s="31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L63" s="31" t="n">
-        <v>7.889</v>
-      </c>
-      <c r="M63" s="31" t="n">
-        <v>8.214</v>
-      </c>
-      <c r="N63" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="O63" s="31" t="n">
-        <v>7.586</v>
-      </c>
-      <c r="P63" s="31" t="n">
-        <v>8.111000000000001</v>
-      </c>
-      <c r="Q63" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B64" s="31" t="n">
-        <v>0.919</v>
+        <v>3.875</v>
       </c>
       <c r="C64" s="31" t="n">
-        <v>0.929</v>
+        <v>3.9</v>
       </c>
       <c r="D64" s="31" t="n">
-        <v>1.056</v>
+        <v>4.5</v>
       </c>
       <c r="E64" s="31" t="n">
-        <v>1.154</v>
+        <v>4.867</v>
       </c>
       <c r="F64" s="31" t="n">
-        <v>0.778</v>
+        <v>3.6</v>
       </c>
       <c r="G64" s="31" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="H64" s="33" t="inlineStr">
         <is>
-          <t>29th</t>
+          <t>23rd</t>
         </is>
       </c>
       <c r="I64" s="31" t="inlineStr"/>
-      <c r="J64" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P64" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="J64" s="33" t="inlineStr">
+        <is>
+          <t>21st</t>
+        </is>
+      </c>
+      <c r="K64" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L64" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="M64" s="31" t="n">
+        <v>5.133</v>
+      </c>
+      <c r="N64" s="31" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="O64" s="31" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="P64" s="31" t="n">
+        <v>5.105</v>
       </c>
       <c r="Q64" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B65" s="31" t="n">
-        <v>7.973</v>
+        <v>7.838</v>
       </c>
       <c r="C65" s="31" t="n">
-        <v>7.964</v>
+        <v>7.75</v>
       </c>
       <c r="D65" s="31" t="n">
-        <v>7.667</v>
+        <v>8.555999999999999</v>
       </c>
       <c r="E65" s="31" t="n">
-        <v>6.692</v>
+        <v>8.692</v>
       </c>
       <c r="F65" s="31" t="n">
-        <v>6.556</v>
+        <v>7.556</v>
       </c>
       <c r="G65" s="31" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H65" s="32" t="inlineStr">
-        <is>
-          <t>8th</t>
+        <v>6.8</v>
+      </c>
+      <c r="H65" s="35" t="inlineStr">
+        <is>
+          <t>19th</t>
         </is>
       </c>
       <c r="I65" s="31" t="inlineStr"/>
-      <c r="J65" s="32" t="inlineStr">
-        <is>
-          <t>10th</t>
+      <c r="J65" s="35" t="inlineStr">
+        <is>
+          <t>11th</t>
         </is>
       </c>
       <c r="K65" s="31" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="L65" s="31" t="n">
-        <v>8.555999999999999</v>
+        <v>7.889</v>
       </c>
       <c r="M65" s="31" t="n">
-        <v>8.643000000000001</v>
+        <v>8.214</v>
       </c>
       <c r="N65" s="31" t="n">
-        <v>8.316000000000001</v>
+        <v>8</v>
       </c>
       <c r="O65" s="31" t="n">
-        <v>8</v>
+        <v>7.586</v>
       </c>
       <c r="P65" s="31" t="n">
-        <v>8.055999999999999</v>
+        <v>8.111000000000001</v>
       </c>
       <c r="Q65" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="30" t="inlineStr">
         <is>
-          <t>1st Inn R/G</t>
+          <t>HR/G</t>
         </is>
       </c>
       <c r="B66" s="31" t="n">
-        <v>0.243</v>
+        <v>0.919</v>
       </c>
       <c r="C66" s="31" t="n">
-        <v>0.321</v>
+        <v>0.929</v>
       </c>
       <c r="D66" s="31" t="n">
-        <v>0.444</v>
+        <v>1.056</v>
       </c>
       <c r="E66" s="31" t="n">
-        <v>0.615</v>
+        <v>1.154</v>
       </c>
       <c r="F66" s="31" t="n">
         <v>0.778</v>
       </c>
       <c r="G66" s="31" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H66" s="33" t="inlineStr">
+        <is>
+          <t>29th</t>
+        </is>
+      </c>
+      <c r="I66" s="31" t="inlineStr"/>
+      <c r="J66" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q66" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B67" s="31" t="n">
+        <v>7.973</v>
+      </c>
+      <c r="C67" s="31" t="n">
+        <v>7.964</v>
+      </c>
+      <c r="D67" s="31" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="E67" s="31" t="n">
+        <v>6.692</v>
+      </c>
+      <c r="F67" s="31" t="n">
+        <v>6.556</v>
+      </c>
+      <c r="G67" s="31" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H67" s="32" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I67" s="31" t="inlineStr"/>
+      <c r="J67" s="32" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
+      <c r="K67" s="31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="L67" s="31" t="n">
+        <v>8.555999999999999</v>
+      </c>
+      <c r="M67" s="31" t="n">
+        <v>8.643000000000001</v>
+      </c>
+      <c r="N67" s="31" t="n">
+        <v>8.316000000000001</v>
+      </c>
+      <c r="O67" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P67" s="31" t="n">
+        <v>8.055999999999999</v>
+      </c>
+      <c r="Q67" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
+          <t>1st Inn R/G</t>
+        </is>
+      </c>
+      <c r="B68" s="31" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="C68" s="31" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="D68" s="31" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="E68" s="31" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="F68" s="31" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="G68" s="31" t="n">
         <v>1</v>
       </c>
-      <c r="H66" s="32" t="inlineStr">
+      <c r="H68" s="32" t="inlineStr">
         <is>
           <t>3rd</t>
         </is>
       </c>
-      <c r="I66" s="31" t="inlineStr">
+      <c r="I68" s="31" t="inlineStr">
         <is>
           <t>★★</t>
         </is>
       </c>
-      <c r="J66" s="32" t="inlineStr">
+      <c r="J68" s="32" t="inlineStr">
         <is>
           <t>10th</t>
         </is>
       </c>
-      <c r="K66" s="31" t="n">
+      <c r="K68" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="L66" s="31" t="n">
+      <c r="L68" s="31" t="n">
         <v>0.222</v>
       </c>
-      <c r="M66" s="31" t="n">
+      <c r="M68" s="31" t="n">
         <v>0.214</v>
       </c>
-      <c r="N66" s="31" t="n">
+      <c r="N68" s="31" t="n">
         <v>0.158</v>
       </c>
-      <c r="O66" s="31" t="n">
+      <c r="O68" s="31" t="n">
         <v>0.241</v>
       </c>
-      <c r="P66" s="31" t="n">
+      <c r="P68" s="31" t="n">
         <v>0.444</v>
       </c>
-      <c r="Q66" s="34" t="inlineStr">
+      <c r="Q68" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="28" t="inlineStr">
         <is>
           <t>Chicago White Sox offense vs Kansas City Royals defense</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="29" t="inlineStr">
         <is>
           <t>Stat</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B71" s="29" t="inlineStr">
         <is>
           <t>A Season</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C71" s="29" t="inlineStr">
         <is>
           <t>A L30</t>
         </is>
       </c>
-      <c r="D69" s="29" t="inlineStr">
+      <c r="D71" s="29" t="inlineStr">
         <is>
           <t>A L20</t>
         </is>
       </c>
-      <c r="E69" s="29" t="inlineStr">
+      <c r="E71" s="29" t="inlineStr">
         <is>
           <t>A L15</t>
         </is>
       </c>
-      <c r="F69" s="29" t="inlineStr">
+      <c r="F71" s="29" t="inlineStr">
         <is>
           <t>A L10</t>
         </is>
       </c>
-      <c r="G69" s="29" t="inlineStr">
+      <c r="G71" s="29" t="inlineStr">
         <is>
           <t>A L5</t>
         </is>
       </c>
-      <c r="H69" s="29" t="inlineStr">
+      <c r="H71" s="29" t="inlineStr">
         <is>
           <t>A Rk</t>
         </is>
       </c>
-      <c r="I69" s="29" t="inlineStr">
+      <c r="I71" s="29" t="inlineStr">
         <is>
           <t>Adv</t>
         </is>
       </c>
-      <c r="J69" s="29" t="inlineStr">
+      <c r="J71" s="29" t="inlineStr">
         <is>
           <t>H Rk</t>
         </is>
       </c>
-      <c r="K69" s="29" t="inlineStr">
+      <c r="K71" s="29" t="inlineStr">
         <is>
           <t>H L5</t>
         </is>
       </c>
-      <c r="L69" s="29" t="inlineStr">
+      <c r="L71" s="29" t="inlineStr">
         <is>
           <t>H L10</t>
         </is>
       </c>
-      <c r="M69" s="29" t="inlineStr">
+      <c r="M71" s="29" t="inlineStr">
         <is>
           <t>H L15</t>
         </is>
       </c>
-      <c r="N69" s="29" t="inlineStr">
+      <c r="N71" s="29" t="inlineStr">
         <is>
           <t>H L20</t>
         </is>
       </c>
-      <c r="O69" s="29" t="inlineStr">
+      <c r="O71" s="29" t="inlineStr">
         <is>
           <t>H L30</t>
         </is>
       </c>
-      <c r="P69" s="29" t="inlineStr">
+      <c r="P71" s="29" t="inlineStr">
         <is>
           <t>H Season</t>
         </is>
       </c>
-      <c r="Q69" s="29" t="inlineStr">
+      <c r="Q71" s="29" t="inlineStr">
         <is>
           <t>Opp stat</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>Runs/G</t>
-        </is>
-      </c>
-      <c r="B70" s="31" t="n">
-        <v>4.605</v>
-      </c>
-      <c r="C70" s="31" t="n">
-        <v>4.667</v>
-      </c>
-      <c r="D70" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="E70" s="31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F70" s="31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G70" s="31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H70" s="32" t="inlineStr">
-        <is>
-          <t>4th</t>
-        </is>
-      </c>
-      <c r="I70" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J70" s="35" t="inlineStr">
-        <is>
-          <t>14th</t>
-        </is>
-      </c>
-      <c r="K70" s="31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L70" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="M70" s="31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N70" s="31" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O70" s="31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="P70" s="31" t="n">
-        <v>4.675</v>
-      </c>
-      <c r="Q70" s="34" t="inlineStr">
-        <is>
-          <t>Opp Runs/G</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="30" t="inlineStr">
-        <is>
-          <t>Hits/G</t>
-        </is>
-      </c>
-      <c r="B71" s="31" t="n">
-        <v>7.444</v>
-      </c>
-      <c r="C71" s="31" t="n">
-        <v>7.586</v>
-      </c>
-      <c r="D71" s="31" t="n">
-        <v>8.683999999999999</v>
-      </c>
-      <c r="E71" s="31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="F71" s="31" t="n">
-        <v>7.667</v>
-      </c>
-      <c r="G71" s="31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H71" s="35" t="inlineStr">
-        <is>
-          <t>17th</t>
-        </is>
-      </c>
-      <c r="I71" s="31" t="inlineStr">
-        <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="J71" s="33" t="inlineStr">
-        <is>
-          <t>27th</t>
-        </is>
-      </c>
-      <c r="K71" s="31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="L71" s="31" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="M71" s="31" t="n">
-        <v>9.308</v>
-      </c>
-      <c r="N71" s="31" t="n">
-        <v>8.778</v>
-      </c>
-      <c r="O71" s="31" t="n">
-        <v>8.179</v>
-      </c>
-      <c r="P71" s="31" t="n">
-        <v>8.162000000000001</v>
-      </c>
-      <c r="Q71" s="34" t="inlineStr">
-        <is>
-          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>HR/G</t>
+          <t>Runs/G</t>
         </is>
       </c>
       <c r="B72" s="31" t="n">
-        <v>1.306</v>
+        <v>4.605</v>
       </c>
       <c r="C72" s="31" t="n">
-        <v>1.345</v>
+        <v>4.667</v>
       </c>
       <c r="D72" s="31" t="n">
-        <v>1.737</v>
+        <v>5.6</v>
       </c>
       <c r="E72" s="31" t="n">
-        <v>1.643</v>
+        <v>5.6</v>
       </c>
       <c r="F72" s="31" t="n">
-        <v>1.556</v>
+        <v>5.4</v>
       </c>
       <c r="G72" s="31" t="n">
-        <v>1.2</v>
+        <v>5.2</v>
       </c>
       <c r="H72" s="32" t="inlineStr">
         <is>
-          <t>8th</t>
-        </is>
-      </c>
-      <c r="I72" s="31" t="inlineStr"/>
-      <c r="J72" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P72" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="I72" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J72" s="35" t="inlineStr">
+        <is>
+          <t>14th</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L72" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="M72" s="31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N72" s="31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O72" s="31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P72" s="31" t="n">
+        <v>4.675</v>
       </c>
       <c r="Q72" s="34" t="inlineStr">
         <is>
-          <t>Opp HR/G</t>
+          <t>Opp Runs/G</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>Batter K/G</t>
+          <t>Hits/G</t>
         </is>
       </c>
       <c r="B73" s="31" t="n">
-        <v>9.388999999999999</v>
+        <v>7.444</v>
       </c>
       <c r="C73" s="31" t="n">
-        <v>8.724</v>
+        <v>7.586</v>
       </c>
       <c r="D73" s="31" t="n">
-        <v>9.053000000000001</v>
+        <v>8.683999999999999</v>
       </c>
       <c r="E73" s="31" t="n">
-        <v>9.286</v>
+        <v>8.5</v>
       </c>
       <c r="F73" s="31" t="n">
-        <v>9.667</v>
+        <v>7.667</v>
       </c>
       <c r="G73" s="31" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="H73" s="33" t="inlineStr">
+        <v>7.6</v>
+      </c>
+      <c r="H73" s="35" t="inlineStr">
+        <is>
+          <t>17th</t>
+        </is>
+      </c>
+      <c r="I73" s="31" t="inlineStr">
+        <is>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="J73" s="33" t="inlineStr">
         <is>
           <t>27th</t>
         </is>
       </c>
-      <c r="I73" s="31" t="inlineStr"/>
-      <c r="J73" s="35" t="inlineStr">
-        <is>
-          <t>18th</t>
-        </is>
-      </c>
       <c r="K73" s="31" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="L73" s="31" t="n">
-        <v>7.778</v>
+        <v>8.667</v>
       </c>
       <c r="M73" s="31" t="n">
-        <v>8.385</v>
+        <v>9.308</v>
       </c>
       <c r="N73" s="31" t="n">
-        <v>8.333</v>
+        <v>8.778</v>
       </c>
       <c r="O73" s="31" t="n">
-        <v>8</v>
+        <v>8.179</v>
       </c>
       <c r="P73" s="31" t="n">
-        <v>8.404999999999999</v>
+        <v>8.162000000000001</v>
       </c>
       <c r="Q73" s="34" t="inlineStr">
         <is>
-          <t>Opp Batter K/G</t>
+          <t>Opp Hits/G</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="30" t="inlineStr">
         <is>
+          <t>HR/G</t>
+        </is>
+      </c>
+      <c r="B74" s="31" t="n">
+        <v>1.306</v>
+      </c>
+      <c r="C74" s="31" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="D74" s="31" t="n">
+        <v>1.737</v>
+      </c>
+      <c r="E74" s="31" t="n">
+        <v>1.643</v>
+      </c>
+      <c r="F74" s="31" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="G74" s="31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H74" s="32" t="inlineStr">
+        <is>
+          <t>8th</t>
+        </is>
+      </c>
+      <c r="I74" s="31" t="inlineStr"/>
+      <c r="J74" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q74" s="34" t="inlineStr">
+        <is>
+          <t>Opp HR/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="30" t="inlineStr">
+        <is>
+          <t>Batter K/G</t>
+        </is>
+      </c>
+      <c r="B75" s="31" t="n">
+        <v>9.388999999999999</v>
+      </c>
+      <c r="C75" s="31" t="n">
+        <v>8.724</v>
+      </c>
+      <c r="D75" s="31" t="n">
+        <v>9.053000000000001</v>
+      </c>
+      <c r="E75" s="31" t="n">
+        <v>9.286</v>
+      </c>
+      <c r="F75" s="31" t="n">
+        <v>9.667</v>
+      </c>
+      <c r="G75" s="31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H75" s="33" t="inlineStr">
+        <is>
+          <t>27th</t>
+        </is>
+      </c>
+      <c r="I75" s="31" t="inlineStr"/>
+      <c r="J75" s="35" t="inlineStr">
+        <is>
+          <t>18th</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="L75" s="31" t="n">
+        <v>7.778</v>
+      </c>
+      <c r="M75" s="31" t="n">
+        <v>8.385</v>
+      </c>
+      <c r="N75" s="31" t="n">
+        <v>8.333</v>
+      </c>
+      <c r="O75" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="P75" s="31" t="n">
+        <v>8.404999999999999</v>
+      </c>
+      <c r="Q75" s="34" t="inlineStr">
+        <is>
+          <t>Opp Batter K/G</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="30" t="inlineStr">
+        <is>
           <t>1st Inn R/G</t>
         </is>
       </c>
-      <c r="B74" s="31" t="n">
+      <c r="B76" s="31" t="n">
         <v>0.611</v>
       </c>
-      <c r="C74" s="31" t="n">
+      <c r="C76" s="31" t="n">
         <v>0.552</v>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D76" s="31" t="n">
         <v>0.737</v>
       </c>
-      <c r="E74" s="31" t="n">
+      <c r="E76" s="31" t="n">
         <v>0.857</v>
       </c>
-      <c r="F74" s="31" t="n">
+      <c r="F76" s="31" t="n">
         <v>0.667</v>
       </c>
-      <c r="G74" s="31" t="n">
+      <c r="G76" s="31" t="n">
         <v>0.6</v>
       </c>
-      <c r="H74" s="35" t="inlineStr">
+      <c r="H76" s="35" t="inlineStr">
         <is>
           <t>14th</t>
         </is>
       </c>
-      <c r="I74" s="31" t="inlineStr"/>
-      <c r="J74" s="32" t="inlineStr">
+      <c r="I76" s="31" t="inlineStr"/>
+      <c r="J76" s="32" t="inlineStr">
         <is>
           <t>9th</t>
         </is>
       </c>
-      <c r="K74" s="31" t="n">
+      <c r="K76" s="31" t="n">
         <v>0.2</v>
       </c>
-      <c r="L74" s="31" t="n">
+      <c r="L76" s="31" t="n">
         <v>0.556</v>
       </c>
-      <c r="M74" s="31" t="n">
+      <c r="M76" s="31" t="n">
         <v>0.6919999999999999</v>
       </c>
-      <c r="N74" s="31" t="n">
+      <c r="N76" s="31" t="n">
         <v>0.667</v>
       </c>
-      <c r="O74" s="31" t="n">
+      <c r="O76" s="31" t="n">
         <v>0.536</v>
       </c>
-      <c r="P74" s="31" t="n">
+      <c r="P76" s="31" t="n">
         <v>0.5679999999999999</v>
       </c>
-      <c r="Q74" s="34" t="inlineStr">
+      <c r="Q76" s="34" t="inlineStr">
         <is>
           <t>Opp 1st Inn R/G</t>
         </is>
@@ -8091,37 +8091,37 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers -1.5</t>
+          <t>Over 169.5</t>
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.4783203125</v>
+        <v>0.6593548387096775</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>109</v>
+        <v>-194</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="I5" s="13">
         <f>IF($H$5="","",IF($H$5&lt;0,-$H$5/(-$H$5+100),100/($H$5+100)))</f>
@@ -8145,7 +8145,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 65.9% (fair -194). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -8157,37 +8157,37 @@
     <row r="6">
       <c r="A6" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Milwaukee Brewers -1.5</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.6412101321585904</v>
+        <v>0.48404</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-179</v>
+        <v>107</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-127</v>
+        <v>150</v>
       </c>
       <c r="I6" s="13">
         <f>IF($H$6="","",IF($H$6&lt;0,-$H$6/(-$H$6+100),100/($H$6+100)))</f>
@@ -8211,7 +8211,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -179). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -8223,17 +8223,17 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Miami Marlins @ Colorado Rockies</t>
+          <t>Cincinnati Reds @ Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>00:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -8243,17 +8243,17 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4806437768240343</v>
+        <v>0.6450704845814978</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>108</v>
+        <v>-182</v>
       </c>
       <c r="H7" s="15" t="n">
-        <v>133</v>
+        <v>-127</v>
       </c>
       <c r="I7" s="13">
         <f>IF($H$7="","",IF($H$7&lt;0,-$H$7/(-$H$7+100),100/($H$7+100)))</f>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 64.5% (fair -182). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -8294,32 +8294,32 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
+          <t>San Francisco Giants @ Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
         <is>
-          <t>Pittsburgh Pirates</t>
+          <t>Under 9</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5478921568627451</v>
+        <v>0.5460576923076923</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-121</v>
+        <v>-120</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I8" s="13">
         <f>IF($H$8="","",IF($H$8&lt;0,-$H$8/(-$H$8+100),100/($H$8+100)))</f>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -8370,22 +8370,22 @@
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Over 165.5</t>
+          <t>Golden State Valkyries</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5241784037558685</v>
+        <v>0.5806038461538462</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-110</v>
+        <v>-138</v>
       </c>
       <c r="H9" s="15" t="n">
-        <v>113</v>
+        <v>-108</v>
       </c>
       <c r="I9" s="13">
         <f>IF($H$9="","",IF($H$9&lt;0,-$H$9/(-$H$9+100),100/($H$9+100)))</f>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 58.1% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -8436,19 +8436,19 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Pittsburgh Pirates</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5410784313725491</v>
+        <v>0.5466666666666666</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-118</v>
+        <v>-121</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>104</v>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -8487,17 +8487,17 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>New York Liberty @ Golden State Valkyries</t>
+          <t>Miami Marlins @ Colorado Rockies</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>00:40</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -8507,17 +8507,17 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.5896023255813955</v>
+        <v>0.4777682403433476</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-144</v>
+        <v>109</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>-115</v>
+        <v>133</v>
       </c>
       <c r="I11" s="13">
         <f>IF($H$11="","",IF($H$11&lt;0,-$H$11/(-$H$11+100),100/($H$11+100)))</f>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -8558,32 +8558,32 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire @ Washington Mystics</t>
+          <t>Las Vegas Aces @ Chicago Sky</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
         <is>
-          <t>Portland Fire +7.5</t>
+          <t>Over 181.5</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.5240865384615385</v>
+        <v>0.5384878048780489</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-110</v>
+        <v>-117</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="I12" s="13">
         <f>IF($H$12="","",IF($H$12&lt;0,-$H$12/(-$H$12+100),100/($H$12+100)))</f>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 53.8% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -8624,32 +8624,32 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Athletics +1.5</t>
+          <t>Milwaukee Brewers</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.6316109243697479</v>
+        <v>0.651323076923077</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-171</v>
+        <v>-187</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>-138</v>
+        <v>-147</v>
       </c>
       <c r="I13" s="13">
         <f>IF($H$13="","",IF($H$13&lt;0,-$H$13/(-$H$13+100),100/($H$13+100)))</f>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 63.2% (fair -171). Your call.</t>
+          <t>Model 65.1% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -8690,32 +8690,32 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Los Angeles Dodgers @ Athletics</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
         <is>
-          <t>Milwaukee Brewers</t>
+          <t>Athletics +1.5</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.6508200000000001</v>
+        <v>0.6323067226890756</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-186</v>
+        <v>-172</v>
       </c>
       <c r="H14" s="15" t="n">
-        <v>-150</v>
+        <v>-138</v>
       </c>
       <c r="I14" s="13">
         <f>IF($H$14="","",IF($H$14&lt;0,-$H$14/(-$H$14+100),100/($H$14+100)))</f>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 65.1% (fair -186). Your call.</t>
+          <t>Model 63.2% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -8751,17 +8751,17 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Portland Fire @ Washington Mystics</t>
+          <t>Pittsburgh Pirates @ Philadelphia Phillies</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Over 169.5</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4981566820276498</v>
+        <v>0.544</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>101</v>
+        <v>-119</v>
       </c>
       <c r="H15" s="15" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="I15" s="13">
         <f>IF($H$15="","",IF($H$15&lt;0,-$H$15/(-$H$15+100),100/($H$15+100)))</f>
@@ -8805,7 +8805,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -8817,37 +8817,37 @@
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies @ Minnesota Twins</t>
+          <t>Los Angeles Dodgers @ Athletics</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
         <is>
-          <t>Colorado Rockies</t>
+          <t>Under 10.5</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.43084</v>
+        <v>0.5396</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>132</v>
+        <v>-117</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I16" s="13">
         <f>IF($H$16="","",IF($H$16&lt;0,-$H$16/(-$H$16+100),100/($H$16+100)))</f>
@@ -8871,7 +8871,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -8883,37 +8883,37 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Los Angeles Dodgers @ Athletics</t>
+          <t>Portland Fire @ Washington Mystics</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Under 10.5</t>
+          <t>Portland Fire +7.5</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.5376</v>
+        <v>0.5182692307692308</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>-116</v>
+        <v>-108</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -8973,10 +8973,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.4841891891891892</v>
+        <v>0.4853603603603603</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>122</v>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -9039,10 +9039,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.4995813953488373</v>
+        <v>0.5005116279069768</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>115</v>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -9081,37 +9081,37 @@
     <row r="20">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>New York Liberty @ Golden State Valkyries</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers</t>
+          <t>Over 165.5</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.4578540772532189</v>
+        <v>0.5241666666666667</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>118</v>
+        <v>-110</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>133</v>
+        <v>104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 52.4% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -9171,10 +9171,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5685279069767442</v>
+        <v>0.5704</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-132</v>
+        <v>-133</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>-115</v>
@@ -9201,7 +9201,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -9213,37 +9213,37 @@
     <row r="22">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Washington Nationals @ Baltimore Orioles</t>
+          <t>Detroit Tigers @ New York Yankees</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>Spread</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>Baltimore Orioles -1.5</t>
+          <t>Detroit Tigers</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.5093749999999999</v>
+        <v>0.455793991416309</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-104</v>
+        <v>119</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>108</v>
+        <v>133</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -9267,7 +9267,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -9284,12 +9284,12 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
+          <t>Texas Rangers @ Toronto Blue Jays</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -9299,17 +9299,17 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Arizona Diamondbacks</t>
+          <t>Texas Rangers</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.3689473684210526</v>
+        <v>0.4854128440366973</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>171</v>
+        <v>106</v>
       </c>
       <c r="H23" s="15" t="n">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="I23" s="13">
         <f>IF($H$23="","",IF($H$23&lt;0,-$H$23/(-$H$23+100),100/($H$23+100)))</f>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 36.9% (fair +171). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -9369,10 +9369,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.5339686274509804</v>
+        <v>0.5375882352941176</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>-104</v>
@@ -9399,7 +9399,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Philadelphia Phillies @ New York Mets</t>
+          <t>Washington Nationals @ Baltimore Orioles</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -9431,17 +9431,17 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>New York Mets +1.5</t>
+          <t>Baltimore Orioles -1.5</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5551854460093897</v>
+        <v>0.506875</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-125</v>
+        <v>-103</v>
       </c>
       <c r="H25" s="15" t="n">
-        <v>-113</v>
+        <v>108</v>
       </c>
       <c r="I25" s="13">
         <f>IF($H$25="","",IF($H$25&lt;0,-$H$25/(-$H$25+100),100/($H$25+100)))</f>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -9477,37 +9477,37 @@
     <row r="26">
       <c r="A26" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Cincinnati Reds @ Milwaukee Brewers</t>
+          <t>Colorado Rockies @ Minnesota Twins</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
-          <t>Over 8.5</t>
+          <t>Colorado Rockies</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.5479047619047619</v>
+        <v>0.42152</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>-121</v>
+        <v>137</v>
       </c>
       <c r="H26" s="15" t="n">
-        <v>-110</v>
+        <v>150</v>
       </c>
       <c r="I26" s="13">
         <f>IF($H$26="","",IF($H$26&lt;0,-$H$26/(-$H$26+100),100/($H$26+100)))</f>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -9548,32 +9548,32 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>New York Mets @ Toronto Blue Jays</t>
+          <t>Cincinnati Reds @ Milwaukee Brewers</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>23:07</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>New York Mets</t>
+          <t>Over 8.5</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4891079812206574</v>
+        <v>0.546075</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>104</v>
+        <v>-120</v>
       </c>
       <c r="H27" s="15" t="n">
-        <v>113</v>
+        <v>-108</v>
       </c>
       <c r="I27" s="13">
         <f>IF($H$27="","",IF($H$27&lt;0,-$H$27/(-$H$27+100),100/($H$27+100)))</f>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -9609,37 +9609,37 @@
     <row r="28">
       <c r="A28" s="20" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Detroit Tigers @ New York Yankees</t>
+          <t>Arizona Diamondbacks @ Tampa Bay Rays</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Moneyline</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
         <is>
-          <t>Under 8</t>
+          <t>Arizona Diamondbacks</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5077560975609756</v>
+        <v>0.3689473684210526</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-103</v>
+        <v>171</v>
       </c>
       <c r="H28" s="15" t="n">
-        <v>105</v>
+        <v>185</v>
       </c>
       <c r="I28" s="13">
         <f>IF($H$28="","",IF($H$28&lt;0,-$H$28/(-$H$28+100),100/($H$28+100)))</f>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 36.9% (fair +171). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -9680,32 +9680,32 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers @ Toronto Blue Jays</t>
+          <t>Philadelphia Phillies @ New York Mets</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Moneyline</t>
+          <t>Spread</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Texas Rangers</t>
+          <t>New York Mets +1.5</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.4773853211009175</v>
+        <v>0.5576788732394365</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>109</v>
+        <v>-126</v>
       </c>
       <c r="H29" s="15" t="n">
-        <v>118</v>
+        <v>-113</v>
       </c>
       <c r="I29" s="13">
         <f>IF($H$29="","",IF($H$29&lt;0,-$H$29/(-$H$29+100),100/($H$29+100)))</f>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +109). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -9906,10 +9906,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.3448951048951049</v>
+        <v>0.3473426573426573</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>186</v>
@@ -9936,7 +9936,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 34.5% (fair +190). Your call.</t>
+          <t>Model 34.7% (fair +188). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -9972,10 +9972,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.655078417266187</v>
+        <v>0.6526453237410073</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-190</v>
+        <v>-188</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-178</v>
@@ -10002,7 +10002,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 65.5% (fair -190). Your call.</t>
+          <t>Model 65.3% (fair -188). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -10038,10 +10038,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.511</v>
+        <v>0.5185</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>-104</v>
+        <v>-108</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>127</v>
@@ -10068,7 +10068,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -10104,10 +10104,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.489</v>
+        <v>0.4815</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>-108</v>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -10170,10 +10170,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.5093749999999999</v>
+        <v>0.506875</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>-104</v>
+        <v>-103</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>108</v>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 50.9% (fair -104). Your call.</t>
+          <t>Model 50.7% (fair -103). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -10236,10 +10236,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.4906523809523809</v>
+        <v>0.4931142857142857</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>-110</v>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 49.1% (fair +104). Your call.</t>
+          <t>Model 49.3% (fair +103). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -10302,10 +10302,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.3588105726872247</v>
+        <v>0.3549339207048458</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>127</v>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 35.9% (fair +179). Your call.</t>
+          <t>Model 35.5% (fair +182). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -10368,10 +10368,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.6412101321585904</v>
+        <v>0.6450704845814978</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>-179</v>
+        <v>-182</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>-127</v>
@@ -10398,7 +10398,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 64.1% (fair -179). Your call.</t>
+          <t>Model 64.5% (fair -182). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -10434,10 +10434,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.5477</v>
+        <v>0.5493</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>-121</v>
+        <v>-122</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>117</v>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.9% (fair -122). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -10500,10 +10500,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.4523</v>
+        <v>0.4507</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>128</v>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.1% (fair +122). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -10566,10 +10566,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.5994</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>-150</v>
+        <v>-154</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>160</v>
@@ -10596,7 +10596,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 59.9% (fair -150). Your call.</t>
+          <t>Model 60.6% (fair -154). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -10632,10 +10632,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.4006</v>
+        <v>0.3935999999999999</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>-117</v>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 40.1% (fair +150). Your call.</t>
+          <t>Model 39.4% (fair +154). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -10698,10 +10698,10 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4773853211009175</v>
+        <v>0.4854128440366973</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>118</v>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +109). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -10764,10 +10764,10 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5226</v>
+        <v>0.5145818181818181</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-109</v>
+        <v>-106</v>
       </c>
       <c r="H18" s="15" t="n">
         <v>-120</v>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -109). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -10830,10 +10830,10 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.441</v>
+        <v>0.439</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H19" s="15" t="n">
         <v>104</v>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="N19" s="19" t="inlineStr">
         <is>
-          <t>Model 44.1% (fair +127). Your call.</t>
+          <t>Model 43.9% (fair +128). Your call.</t>
         </is>
       </c>
       <c r="O19" s="15" t="n"/>
@@ -10896,10 +10896,10 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>0.5589999999999999</v>
+        <v>0.5609999999999999</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-127</v>
+        <v>-128</v>
       </c>
       <c r="H20" s="15" t="n">
         <v>117</v>
@@ -10926,7 +10926,7 @@
       </c>
       <c r="N20" s="19" t="inlineStr">
         <is>
-          <t>Model 55.9% (fair -127). Your call.</t>
+          <t>Model 56.1% (fair -128). Your call.</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -10962,10 +10962,10 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.3698</v>
+        <v>0.3553</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="H21" s="15" t="n">
         <v>174</v>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 37.0% (fair +170). Your call.</t>
+          <t>Model 35.5% (fair +181). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -11028,10 +11028,10 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.6302</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-170</v>
+        <v>-181</v>
       </c>
       <c r="H22" s="15" t="n">
         <v>-125</v>
@@ -11058,7 +11058,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 63.0% (fair -170). Your call.</t>
+          <t>Model 64.5% (fair -181). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -11094,10 +11094,10 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>0.50815</v>
+        <v>0.5042</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>-103</v>
+        <v>-102</v>
       </c>
       <c r="H23" s="15" t="n">
         <v>100</v>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="N23" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -11160,10 +11160,10 @@
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>0.491826923076923</v>
+        <v>0.4958173076923078</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H24" s="15" t="n">
         <v>108</v>
@@ -11190,7 +11190,7 @@
       </c>
       <c r="N24" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -11226,10 +11226,10 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>0.5508</v>
+        <v>0.5583</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>-123</v>
+        <v>-126</v>
       </c>
       <c r="H25" s="15" t="n">
         <v>113</v>
@@ -11256,7 +11256,7 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -11292,10 +11292,10 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>0.4492</v>
+        <v>0.4417</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H26" s="15" t="n">
         <v>107</v>
@@ -11322,7 +11322,7 @@
       </c>
       <c r="N26" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>0.4995813953488373</v>
+        <v>0.5005116279069768</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="H27" s="15" t="n">
         <v>115</v>
@@ -11388,7 +11388,7 @@
       </c>
       <c r="N27" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair +100). Your call.</t>
+          <t>Model 50.1% (fair -100). Your call.</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -11424,10 +11424,10 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>0.5004361502347418</v>
+        <v>0.499481220657277</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-113</v>
@@ -11454,7 +11454,7 @@
       </c>
       <c r="N28" s="19" t="inlineStr">
         <is>
-          <t>Model 50.0% (fair -100). Your call.</t>
+          <t>Model 49.9% (fair +100). Your call.</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>0.443</v>
+        <v>0.4406</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H29" s="15" t="n">
         <v>104</v>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="N29" s="19" t="inlineStr">
         <is>
-          <t>Model 44.3% (fair +126). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -11556,10 +11556,10 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>0.5569999999999999</v>
+        <v>0.5594</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>-126</v>
+        <v>-127</v>
       </c>
       <c r="H30" s="15" t="n">
         <v>121</v>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="N30" s="19" t="inlineStr">
         <is>
-          <t>Model 55.7% (fair -126). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -11622,10 +11622,10 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>0.318</v>
+        <v>0.3137</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H31" s="15" t="n">
         <v>175</v>
@@ -11652,7 +11652,7 @@
       </c>
       <c r="N31" s="19" t="inlineStr">
         <is>
-          <t>Model 31.8% (fair +214). Your call.</t>
+          <t>Model 31.4% (fair +219). Your call.</t>
         </is>
       </c>
       <c r="O31" s="15" t="n"/>
@@ -11688,10 +11688,10 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>0.6819999999999999</v>
+        <v>0.6863</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>-214</v>
+        <v>-219</v>
       </c>
       <c r="H32" s="15" t="n">
         <v>186</v>
@@ -11718,7 +11718,7 @@
       </c>
       <c r="N32" s="19" t="inlineStr">
         <is>
-          <t>Model 68.2% (fair -214). Your call.</t>
+          <t>Model 68.6% (fair -219). Your call.</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -12150,10 +12150,10 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>0.58872</v>
+        <v>0.5835600000000001</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>-143</v>
+        <v>-140</v>
       </c>
       <c r="H39" s="15" t="n">
         <v>-150</v>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="N39" s="19" t="inlineStr">
         <is>
-          <t>Model 58.9% (fair -143). Your call.</t>
+          <t>Model 58.4% (fair -140). Your call.</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -12216,10 +12216,10 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>0.41128</v>
+        <v>0.41644</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="H40" s="15" t="n">
         <v>150</v>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="N40" s="19" t="inlineStr">
         <is>
-          <t>Model 41.1% (fair +143). Your call.</t>
+          <t>Model 41.6% (fair +140). Your call.</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -12282,10 +12282,10 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>0.4309</v>
+        <v>0.4235</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="H41" s="15" t="n">
         <v>108</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="N41" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 42.4% (fair +136). Your call.</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -12348,10 +12348,10 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>0.5690999999999999</v>
+        <v>0.5765</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>-132</v>
+        <v>-136</v>
       </c>
       <c r="H42" s="15" t="n">
         <v>114</v>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="N42" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 57.6% (fair -136). Your call.</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -12414,10 +12414,10 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>0.5551854460093897</v>
+        <v>0.5576788732394365</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>-125</v>
+        <v>-126</v>
       </c>
       <c r="H43" s="15" t="n">
         <v>-113</v>
@@ -12444,7 +12444,7 @@
       </c>
       <c r="N43" s="19" t="inlineStr">
         <is>
-          <t>Model 55.5% (fair -125). Your call.</t>
+          <t>Model 55.8% (fair -126). Your call.</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -12480,10 +12480,10 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>0.4448130841121496</v>
+        <v>0.4423364485981309</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H44" s="15" t="n">
         <v>114</v>
@@ -12510,7 +12510,7 @@
       </c>
       <c r="N44" s="19" t="inlineStr">
         <is>
-          <t>Model 44.5% (fair +125). Your call.</t>
+          <t>Model 44.2% (fair +126). Your call.</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -12546,10 +12546,10 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>0.43084</v>
+        <v>0.42152</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H45" s="15" t="n">
         <v>150</v>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="N45" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 42.2% (fair +137). Your call.</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>0.5691540983606558</v>
+        <v>0.5784786885245902</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>-132</v>
+        <v>-137</v>
       </c>
       <c r="H46" s="15" t="n">
         <v>-144</v>
@@ -12642,7 +12642,7 @@
       </c>
       <c r="N46" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 57.8% (fair -137). Your call.</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -12678,10 +12678,10 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>0.5254</v>
+        <v>0.5138</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>-111</v>
+        <v>-106</v>
       </c>
       <c r="H47" s="15" t="n">
         <v>117</v>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="N47" s="19" t="inlineStr">
         <is>
-          <t>Model 52.5% (fair -111). Your call.</t>
+          <t>Model 51.4% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -12744,10 +12744,10 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>0.4746</v>
+        <v>0.4862</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H48" s="15" t="n">
         <v>110</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="N48" s="19" t="inlineStr">
         <is>
-          <t>Model 47.5% (fair +111). Your call.</t>
+          <t>Model 48.6% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -12810,10 +12810,10 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>0.4147</v>
+        <v>0.4315</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="H49" s="15" t="n">
         <v>133</v>
@@ -12840,7 +12840,7 @@
       </c>
       <c r="N49" s="19" t="inlineStr">
         <is>
-          <t>Model 41.5% (fair +141). Your call.</t>
+          <t>Model 43.1% (fair +132). Your call.</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -12876,10 +12876,10 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>0.5852999999999999</v>
+        <v>0.5685</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>-141</v>
+        <v>-132</v>
       </c>
       <c r="H50" s="15" t="n">
         <v>105</v>
@@ -12906,7 +12906,7 @@
       </c>
       <c r="N50" s="19" t="inlineStr">
         <is>
-          <t>Model 58.5% (fair -141). Your call.</t>
+          <t>Model 56.9% (fair -132). Your call.</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -12942,10 +12942,10 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>0.4230901287553648</v>
+        <v>0.4199570815450644</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H51" s="15" t="n">
         <v>133</v>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="N51" s="19" t="inlineStr">
         <is>
-          <t>Model 42.3% (fair +136). Your call.</t>
+          <t>Model 42.0% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -13008,10 +13008,10 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>0.5768709251101322</v>
+        <v>0.5800599118942731</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>-136</v>
+        <v>-138</v>
       </c>
       <c r="H52" s="15" t="n">
         <v>-127</v>
@@ -13038,7 +13038,7 @@
       </c>
       <c r="N52" s="19" t="inlineStr">
         <is>
-          <t>Model 57.7% (fair -136). Your call.</t>
+          <t>Model 58.0% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -13074,10 +13074,10 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>0.6593</v>
+        <v>0.6669</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>-194</v>
+        <v>-200</v>
       </c>
       <c r="H53" s="15" t="n">
         <v>-104</v>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="N53" s="19" t="inlineStr">
         <is>
-          <t>Model 65.9% (fair -194). Your call.</t>
+          <t>Model 66.7% (fair -200). Your call.</t>
         </is>
       </c>
       <c r="O53" s="15" t="n"/>
@@ -13140,10 +13140,10 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>0.3407</v>
+        <v>0.3331</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="H54" s="15" t="n">
         <v>120</v>
@@ -13170,7 +13170,7 @@
       </c>
       <c r="N54" s="19" t="inlineStr">
         <is>
-          <t>Model 34.1% (fair +194). Your call.</t>
+          <t>Model 33.3% (fair +200). Your call.</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -13206,10 +13206,10 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>0.4649</v>
+        <v>0.4708</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H55" s="15" t="n">
         <v>167</v>
@@ -13236,7 +13236,7 @@
       </c>
       <c r="N55" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 47.1% (fair +112). Your call.</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -13272,10 +13272,10 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>0.5351</v>
+        <v>0.5292</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>-115</v>
+        <v>-112</v>
       </c>
       <c r="H56" s="15" t="n">
         <v>-118</v>
@@ -13302,7 +13302,7 @@
       </c>
       <c r="N56" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 52.9% (fair -112). Your call.</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -13338,10 +13338,10 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>0.41368</v>
+        <v>0.40648</v>
       </c>
       <c r="G57" s="14" t="n">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H57" s="15" t="n">
         <v>150</v>
@@ -13368,7 +13368,7 @@
       </c>
       <c r="N57" s="19" t="inlineStr">
         <is>
-          <t>Model 41.4% (fair +142). Your call.</t>
+          <t>Model 40.6% (fair +146). Your call.</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -13404,10 +13404,10 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>0.5863336032388664</v>
+        <v>0.5935348178137652</v>
       </c>
       <c r="G58" s="14" t="n">
-        <v>-142</v>
+        <v>-146</v>
       </c>
       <c r="H58" s="15" t="n">
         <v>-147</v>
@@ -13434,7 +13434,7 @@
       </c>
       <c r="N58" s="19" t="inlineStr">
         <is>
-          <t>Model 58.6% (fair -142). Your call.</t>
+          <t>Model 59.4% (fair -146). Your call.</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -13470,10 +13470,10 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>0.5913</v>
+        <v>0.5968</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>-145</v>
+        <v>-148</v>
       </c>
       <c r="H59" s="15" t="n">
         <v>108</v>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="N59" s="19" t="inlineStr">
         <is>
-          <t>Model 59.1% (fair -145). Your call.</t>
+          <t>Model 59.7% (fair -148). Your call.</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -13536,10 +13536,10 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>0.4087</v>
+        <v>0.4032</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H60" s="15" t="n">
         <v>127</v>
@@ -13566,7 +13566,7 @@
       </c>
       <c r="N60" s="19" t="inlineStr">
         <is>
-          <t>Model 40.9% (fair +145). Your call.</t>
+          <t>Model 40.3% (fair +148). Your call.</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -13602,10 +13602,10 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>0.447</v>
+        <v>0.4586</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="H61" s="15" t="n">
         <v>141</v>
@@ -13632,7 +13632,7 @@
       </c>
       <c r="N61" s="19" t="inlineStr">
         <is>
-          <t>Model 44.7% (fair +124). Your call.</t>
+          <t>Model 45.9% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -13668,10 +13668,10 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>0.5529999999999999</v>
+        <v>0.5414</v>
       </c>
       <c r="G62" s="14" t="n">
-        <v>-124</v>
+        <v>-118</v>
       </c>
       <c r="H62" s="15" t="n">
         <v>-101</v>
@@ -13698,7 +13698,7 @@
       </c>
       <c r="N62" s="19" t="inlineStr">
         <is>
-          <t>Model 55.3% (fair -124). Your call.</t>
+          <t>Model 54.1% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -13734,10 +13734,10 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>0.4834</v>
+        <v>0.4804</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="N63" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 48.0% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -13798,10 +13798,10 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5196</v>
       </c>
       <c r="G64" s="14" t="n">
-        <v>-107</v>
+        <v>-108</v>
       </c>
       <c r="H64" s="15" t="n"/>
       <c r="I64" s="13">
@@ -13826,7 +13826,7 @@
       </c>
       <c r="N64" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 52.0% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -13862,10 +13862,10 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>0.48</v>
+        <v>0.4657</v>
       </c>
       <c r="G65" s="14" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="H65" s="15" t="n"/>
       <c r="I65" s="13">
@@ -13890,7 +13890,7 @@
       </c>
       <c r="N65" s="19" t="inlineStr">
         <is>
-          <t>Model 48.0% (fair +108). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -13926,10 +13926,10 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>0.52</v>
+        <v>0.5343</v>
       </c>
       <c r="G66" s="14" t="n">
-        <v>-108</v>
+        <v>-115</v>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="N66" s="19" t="inlineStr">
         <is>
-          <t>Model 52.0% (fair -108). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -13990,10 +13990,10 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>0.521</v>
+        <v>0.5234</v>
       </c>
       <c r="G67" s="14" t="n">
-        <v>-109</v>
+        <v>-110</v>
       </c>
       <c r="H67" s="15" t="n"/>
       <c r="I67" s="13">
@@ -14018,7 +14018,7 @@
       </c>
       <c r="N67" s="19" t="inlineStr">
         <is>
-          <t>Model 52.1% (fair -109). Your call.</t>
+          <t>Model 52.3% (fair -110). Your call.</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -14054,10 +14054,10 @@
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>0.479</v>
+        <v>0.4766</v>
       </c>
       <c r="G68" s="14" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="N68" s="19" t="inlineStr">
         <is>
-          <t>Model 47.9% (fair +109). Your call.</t>
+          <t>Model 47.7% (fair +110). Your call.</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -14118,10 +14118,10 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>0.5511</v>
+        <v>0.5484</v>
       </c>
       <c r="G69" s="14" t="n">
-        <v>-123</v>
+        <v>-121</v>
       </c>
       <c r="H69" s="15" t="n"/>
       <c r="I69" s="13">
@@ -14146,7 +14146,7 @@
       </c>
       <c r="N69" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 54.8% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -14182,10 +14182,10 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>0.4489</v>
+        <v>0.4516</v>
       </c>
       <c r="G70" s="14" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13">
@@ -14210,7 +14210,7 @@
       </c>
       <c r="N70" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 45.2% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -14638,10 +14638,10 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>0.4594594594594595</v>
+        <v>0.461981981981982</v>
       </c>
       <c r="G77" s="14" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H77" s="15" t="n">
         <v>122</v>
@@ -14668,7 +14668,7 @@
       </c>
       <c r="N77" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -14704,10 +14704,10 @@
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>0.5405612334801762</v>
+        <v>0.5380436123348018</v>
       </c>
       <c r="G78" s="14" t="n">
-        <v>-118</v>
+        <v>-116</v>
       </c>
       <c r="H78" s="15" t="n">
         <v>-127</v>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="N78" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -14842,7 +14842,7 @@
         <v>-110</v>
       </c>
       <c r="H80" s="15" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I80" s="13">
         <f>IF($H$80="","",IF($H$80&lt;0,-$H$80/(-$H$80+100),100/($H$80+100)))</f>
@@ -14902,10 +14902,10 @@
         </is>
       </c>
       <c r="F81" s="13" t="n">
-        <v>0.3952</v>
+        <v>0.3914</v>
       </c>
       <c r="G81" s="14" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H81" s="15" t="n">
         <v>165</v>
@@ -14932,7 +14932,7 @@
       </c>
       <c r="N81" s="19" t="inlineStr">
         <is>
-          <t>Model 39.5% (fair +153). Your call.</t>
+          <t>Model 39.1% (fair +155). Your call.</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -14968,10 +14968,10 @@
         </is>
       </c>
       <c r="F82" s="13" t="n">
-        <v>0.6048</v>
+        <v>0.6086</v>
       </c>
       <c r="G82" s="14" t="n">
-        <v>-153</v>
+        <v>-155</v>
       </c>
       <c r="H82" s="15" t="n">
         <v>120</v>
@@ -14998,7 +14998,7 @@
       </c>
       <c r="N82" s="19" t="inlineStr">
         <is>
-          <t>Model 60.5% (fair -153). Your call.</t>
+          <t>Model 60.9% (fair -155). Your call.</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -15034,7 +15034,7 @@
         </is>
       </c>
       <c r="F83" s="13" t="n">
-        <v>0.5478921568627451</v>
+        <v>0.5466666666666666</v>
       </c>
       <c r="G83" s="14" t="n">
         <v>-121</v>
@@ -15064,7 +15064,7 @@
       </c>
       <c r="N83" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.7% (fair -121). Your call.</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -15100,7 +15100,7 @@
         </is>
       </c>
       <c r="F84" s="13" t="n">
-        <v>0.452095145631068</v>
+        <v>0.4533300970873786</v>
       </c>
       <c r="G84" s="14" t="n">
         <v>121</v>
@@ -15130,7 +15130,7 @@
       </c>
       <c r="N84" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.3% (fair +121). Your call.</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -15166,13 +15166,13 @@
         </is>
       </c>
       <c r="F85" s="13" t="n">
-        <v>0.5410784313725491</v>
+        <v>0.544</v>
       </c>
       <c r="G85" s="14" t="n">
-        <v>-118</v>
+        <v>-119</v>
       </c>
       <c r="H85" s="15" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I85" s="13">
         <f>IF($H$85="","",IF($H$85&lt;0,-$H$85/(-$H$85+100),100/($H$85+100)))</f>
@@ -15196,7 +15196,7 @@
       </c>
       <c r="N85" s="19" t="inlineStr">
         <is>
-          <t>Model 54.1% (fair -118). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -15232,10 +15232,10 @@
         </is>
       </c>
       <c r="F86" s="13" t="n">
-        <v>0.4589254901960784</v>
+        <v>0.4560196078431372</v>
       </c>
       <c r="G86" s="14" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H86" s="15" t="n">
         <v>-104</v>
@@ -15262,7 +15262,7 @@
       </c>
       <c r="N86" s="19" t="inlineStr">
         <is>
-          <t>Model 45.9% (fair +118). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -15298,10 +15298,10 @@
         </is>
       </c>
       <c r="F87" s="13" t="n">
-        <v>0.2796</v>
+        <v>0.2818</v>
       </c>
       <c r="G87" s="14" t="n">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="H87" s="15" t="n">
         <v>165</v>
@@ -15328,7 +15328,7 @@
       </c>
       <c r="N87" s="19" t="inlineStr">
         <is>
-          <t>Model 28.0% (fair +258). Your call.</t>
+          <t>Model 28.2% (fair +255). Your call.</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -15364,10 +15364,10 @@
         </is>
       </c>
       <c r="F88" s="13" t="n">
-        <v>0.7203999999999999</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="G88" s="14" t="n">
-        <v>-258</v>
+        <v>-255</v>
       </c>
       <c r="H88" s="15" t="n">
         <v>170</v>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="N88" s="19" t="inlineStr">
         <is>
-          <t>Model 72.0% (fair -258). Your call.</t>
+          <t>Model 71.8% (fair -255). Your call.</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -15430,10 +15430,10 @@
         </is>
       </c>
       <c r="F89" s="13" t="n">
-        <v>0.4578540772532189</v>
+        <v>0.455793991416309</v>
       </c>
       <c r="G89" s="14" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H89" s="15" t="n">
         <v>133</v>
@@ -15460,7 +15460,7 @@
       </c>
       <c r="N89" s="19" t="inlineStr">
         <is>
-          <t>Model 45.8% (fair +118). Your call.</t>
+          <t>Model 45.6% (fair +119). Your call.</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -15496,10 +15496,10 @@
         </is>
       </c>
       <c r="F90" s="13" t="n">
-        <v>0.5421255319148937</v>
+        <v>0.5441936170212767</v>
       </c>
       <c r="G90" s="14" t="n">
-        <v>-118</v>
+        <v>-119</v>
       </c>
       <c r="H90" s="15" t="n">
         <v>-135</v>
@@ -15526,7 +15526,7 @@
       </c>
       <c r="N90" s="19" t="inlineStr">
         <is>
-          <t>Model 54.2% (fair -118). Your call.</t>
+          <t>Model 54.4% (fair -119). Your call.</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -15562,10 +15562,10 @@
         </is>
       </c>
       <c r="F91" s="13" t="n">
-        <v>0.49225</v>
+        <v>0.4957</v>
       </c>
       <c r="G91" s="14" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H91" s="15" t="n">
         <v>100</v>
@@ -15592,7 +15592,7 @@
       </c>
       <c r="N91" s="19" t="inlineStr">
         <is>
-          <t>Model 49.2% (fair +103). Your call.</t>
+          <t>Model 49.6% (fair +102). Your call.</t>
         </is>
       </c>
       <c r="O91" s="15" t="n"/>
@@ -15628,13 +15628,13 @@
         </is>
       </c>
       <c r="F92" s="13" t="n">
-        <v>0.5077560975609756</v>
+        <v>0.5043269230769231</v>
       </c>
       <c r="G92" s="14" t="n">
-        <v>-103</v>
+        <v>-102</v>
       </c>
       <c r="H92" s="15" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I92" s="13">
         <f>IF($H$92="","",IF($H$92&lt;0,-$H$92/(-$H$92+100),100/($H$92+100)))</f>
@@ -15658,7 +15658,7 @@
       </c>
       <c r="N92" s="19" t="inlineStr">
         <is>
-          <t>Model 50.8% (fair -103). Your call.</t>
+          <t>Model 50.4% (fair -102). Your call.</t>
         </is>
       </c>
       <c r="O92" s="15" t="n"/>
@@ -15694,10 +15694,10 @@
         </is>
       </c>
       <c r="F93" s="13" t="n">
-        <v>0.3747148288973384</v>
+        <v>0.3770722433460076</v>
       </c>
       <c r="G93" s="14" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H93" s="15" t="n">
         <v>163</v>
@@ -15724,7 +15724,7 @@
       </c>
       <c r="N93" s="19" t="inlineStr">
         <is>
-          <t>Model 37.5% (fair +167). Your call.</t>
+          <t>Model 37.7% (fair +165). Your call.</t>
         </is>
       </c>
       <c r="O93" s="15" t="n"/>
@@ -15760,10 +15760,10 @@
         </is>
       </c>
       <c r="F94" s="13" t="n">
-        <v>0.6252851851851852</v>
+        <v>0.6229555555555555</v>
       </c>
       <c r="G94" s="14" t="n">
-        <v>-167</v>
+        <v>-165</v>
       </c>
       <c r="H94" s="15" t="n">
         <v>-170</v>
@@ -15790,7 +15790,7 @@
       </c>
       <c r="N94" s="19" t="inlineStr">
         <is>
-          <t>Model 62.5% (fair -167). Your call.</t>
+          <t>Model 62.3% (fair -165). Your call.</t>
         </is>
       </c>
       <c r="O94" s="15" t="n"/>
@@ -15826,7 +15826,7 @@
         </is>
       </c>
       <c r="F95" s="13" t="n">
-        <v>0.4891079812206574</v>
+        <v>0.4907511737089202</v>
       </c>
       <c r="G95" s="14" t="n">
         <v>104</v>
@@ -15856,7 +15856,7 @@
       </c>
       <c r="N95" s="19" t="inlineStr">
         <is>
-          <t>Model 48.9% (fair +104). Your call.</t>
+          <t>Model 49.1% (fair +104). Your call.</t>
         </is>
       </c>
       <c r="O95" s="15" t="n"/>
@@ -15892,7 +15892,7 @@
         </is>
       </c>
       <c r="F96" s="13" t="n">
-        <v>0.510887323943662</v>
+        <v>0.5092427230046949</v>
       </c>
       <c r="G96" s="14" t="n">
         <v>-104</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="N96" s="19" t="inlineStr">
         <is>
-          <t>Model 51.1% (fair -104). Your call.</t>
+          <t>Model 50.9% (fair -104). Your call.</t>
         </is>
       </c>
       <c r="O96" s="15" t="n"/>
@@ -15958,13 +15958,13 @@
         </is>
       </c>
       <c r="F97" s="13" t="n">
-        <v>0.4660188118811882</v>
+        <v>0.4624</v>
       </c>
       <c r="G97" s="14" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H97" s="15" t="n">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="I97" s="13">
         <f>IF($H$97="","",IF($H$97&lt;0,-$H$97/(-$H$97+100),100/($H$97+100)))</f>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="N97" s="19" t="inlineStr">
         <is>
-          <t>Model 46.6% (fair +115). Your call.</t>
+          <t>Model 46.2% (fair +116). Your call.</t>
         </is>
       </c>
       <c r="O97" s="15" t="n"/>
@@ -16024,10 +16024,10 @@
         </is>
       </c>
       <c r="F98" s="13" t="n">
-        <v>0.5339686274509804</v>
+        <v>0.5375882352941176</v>
       </c>
       <c r="G98" s="14" t="n">
-        <v>-115</v>
+        <v>-116</v>
       </c>
       <c r="H98" s="15" t="n">
         <v>-104</v>
@@ -16054,7 +16054,7 @@
       </c>
       <c r="N98" s="19" t="inlineStr">
         <is>
-          <t>Model 53.4% (fair -115). Your call.</t>
+          <t>Model 53.8% (fair -116). Your call.</t>
         </is>
       </c>
       <c r="O98" s="15" t="n"/>
@@ -16090,10 +16090,10 @@
         </is>
       </c>
       <c r="F99" s="13" t="n">
-        <v>0.3492</v>
+        <v>0.3483</v>
       </c>
       <c r="G99" s="14" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H99" s="15" t="n">
         <v>178</v>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="N99" s="19" t="inlineStr">
         <is>
-          <t>Model 34.9% (fair +186). Your call.</t>
+          <t>Model 34.8% (fair +187). Your call.</t>
         </is>
       </c>
       <c r="O99" s="15" t="n"/>
@@ -16156,13 +16156,13 @@
         </is>
       </c>
       <c r="F100" s="13" t="n">
-        <v>0.6508</v>
+        <v>0.6516999999999999</v>
       </c>
       <c r="G100" s="14" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="H100" s="15" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="I100" s="13">
         <f>IF($H$100="","",IF($H$100&lt;0,-$H$100/(-$H$100+100),100/($H$100+100)))</f>
@@ -16186,7 +16186,7 @@
       </c>
       <c r="N100" s="19" t="inlineStr">
         <is>
-          <t>Model 65.1% (fair -186). Your call.</t>
+          <t>Model 65.2% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O100" s="15" t="n"/>
@@ -16222,13 +16222,13 @@
         </is>
       </c>
       <c r="F101" s="13" t="n">
-        <v>0.3907</v>
+        <v>0.3892</v>
       </c>
       <c r="G101" s="14" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H101" s="15" t="n">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="I101" s="13">
         <f>IF($H$101="","",IF($H$101&lt;0,-$H$101/(-$H$101+100),100/($H$101+100)))</f>
@@ -16252,7 +16252,7 @@
       </c>
       <c r="N101" s="19" t="inlineStr">
         <is>
-          <t>Model 39.1% (fair +156). Your call.</t>
+          <t>Model 38.9% (fair +157). Your call.</t>
         </is>
       </c>
       <c r="O101" s="15" t="n"/>
@@ -16288,10 +16288,10 @@
         </is>
       </c>
       <c r="F102" s="13" t="n">
-        <v>0.6093</v>
+        <v>0.6108</v>
       </c>
       <c r="G102" s="14" t="n">
-        <v>-156</v>
+        <v>-157</v>
       </c>
       <c r="H102" s="15" t="n">
         <v>122</v>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="N102" s="19" t="inlineStr">
         <is>
-          <t>Model 60.9% (fair -156). Your call.</t>
+          <t>Model 61.1% (fair -157). Your call.</t>
         </is>
       </c>
       <c r="O102" s="15" t="n"/>
@@ -16354,10 +16354,10 @@
         </is>
       </c>
       <c r="F103" s="13" t="n">
-        <v>0.477</v>
+        <v>0.4785</v>
       </c>
       <c r="G103" s="14" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H103" s="15" t="n">
         <v>122</v>
@@ -16384,7 +16384,7 @@
       </c>
       <c r="N103" s="19" t="inlineStr">
         <is>
-          <t>Model 47.7% (fair +110). Your call.</t>
+          <t>Model 47.9% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O103" s="15" t="n"/>
@@ -16420,13 +16420,13 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>0.523</v>
+        <v>0.5215000000000001</v>
       </c>
       <c r="G104" s="14" t="n">
-        <v>-110</v>
+        <v>-109</v>
       </c>
       <c r="H104" s="15" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="I104" s="13">
         <f>IF($H$104="","",IF($H$104&lt;0,-$H$104/(-$H$104+100),100/($H$104+100)))</f>
@@ -16450,7 +16450,7 @@
       </c>
       <c r="N104" s="19" t="inlineStr">
         <is>
-          <t>Model 52.3% (fair -110). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O104" s="15" t="n"/>
@@ -16486,10 +16486,10 @@
         </is>
       </c>
       <c r="F105" s="13" t="n">
-        <v>0.4649545454545454</v>
+        <v>0.4580454545454545</v>
       </c>
       <c r="G105" s="14" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H105" s="15" t="n">
         <v>120</v>
@@ -16516,7 +16516,7 @@
       </c>
       <c r="N105" s="19" t="inlineStr">
         <is>
-          <t>Model 46.5% (fair +115). Your call.</t>
+          <t>Model 45.8% (fair +118). Your call.</t>
         </is>
       </c>
       <c r="O105" s="15" t="n"/>
@@ -16552,13 +16552,13 @@
         </is>
       </c>
       <c r="F106" s="13" t="n">
-        <v>0.5350363636363636</v>
+        <v>0.5419555555555556</v>
       </c>
       <c r="G106" s="14" t="n">
-        <v>-115</v>
+        <v>-118</v>
       </c>
       <c r="H106" s="15" t="n">
-        <v>-120</v>
+        <v>-134</v>
       </c>
       <c r="I106" s="13">
         <f>IF($H$106="","",IF($H$106&lt;0,-$H$106/(-$H$106+100),100/($H$106+100)))</f>
@@ -16582,7 +16582,7 @@
       </c>
       <c r="N106" s="19" t="inlineStr">
         <is>
-          <t>Model 53.5% (fair -115). Your call.</t>
+          <t>Model 54.2% (fair -118). Your call.</t>
         </is>
       </c>
       <c r="O106" s="15" t="n"/>
@@ -16618,10 +16618,10 @@
         </is>
       </c>
       <c r="F107" s="13" t="n">
-        <v>0.4859313725490196</v>
+        <v>0.4841176470588235</v>
       </c>
       <c r="G107" s="14" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H107" s="15" t="n">
         <v>104</v>
@@ -16648,7 +16648,7 @@
       </c>
       <c r="N107" s="19" t="inlineStr">
         <is>
-          <t>Model 48.6% (fair +106). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O107" s="15" t="n"/>
@@ -16684,10 +16684,10 @@
         </is>
       </c>
       <c r="F108" s="13" t="n">
-        <v>0.5140704225352113</v>
+        <v>0.5158741784037559</v>
       </c>
       <c r="G108" s="14" t="n">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="H108" s="15" t="n">
         <v>-113</v>
@@ -16714,7 +16714,7 @@
       </c>
       <c r="N108" s="19" t="inlineStr">
         <is>
-          <t>Model 51.4% (fair -106). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O108" s="15" t="n"/>
@@ -16750,10 +16750,10 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>0.34916</v>
+        <v>0.34868</v>
       </c>
       <c r="G109" s="14" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H109" s="15" t="n">
         <v>150</v>
@@ -16780,7 +16780,7 @@
       </c>
       <c r="N109" s="19" t="inlineStr">
         <is>
-          <t>Model 34.9% (fair +186). Your call.</t>
+          <t>Model 34.9% (fair +187). Your call.</t>
         </is>
       </c>
       <c r="O109" s="15" t="n"/>
@@ -16816,13 +16816,13 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>0.6508200000000001</v>
+        <v>0.651323076923077</v>
       </c>
       <c r="G110" s="14" t="n">
-        <v>-186</v>
+        <v>-187</v>
       </c>
       <c r="H110" s="15" t="n">
-        <v>-150</v>
+        <v>-147</v>
       </c>
       <c r="I110" s="13">
         <f>IF($H$110="","",IF($H$110&lt;0,-$H$110/(-$H$110+100),100/($H$110+100)))</f>
@@ -16846,7 +16846,7 @@
       </c>
       <c r="N110" s="19" t="inlineStr">
         <is>
-          <t>Model 65.1% (fair -186). Your call.</t>
+          <t>Model 65.1% (fair -187). Your call.</t>
         </is>
       </c>
       <c r="O110" s="15" t="n"/>
@@ -16882,13 +16882,13 @@
         </is>
       </c>
       <c r="F111" s="13" t="n">
-        <v>0.5479047619047619</v>
+        <v>0.546075</v>
       </c>
       <c r="G111" s="14" t="n">
-        <v>-121</v>
+        <v>-120</v>
       </c>
       <c r="H111" s="15" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="I111" s="13">
         <f>IF($H$111="","",IF($H$111&lt;0,-$H$111/(-$H$111+100),100/($H$111+100)))</f>
@@ -16912,7 +16912,7 @@
       </c>
       <c r="N111" s="19" t="inlineStr">
         <is>
-          <t>Model 54.8% (fair -121). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O111" s="15" t="n"/>
@@ -16948,13 +16948,13 @@
         </is>
       </c>
       <c r="F112" s="13" t="n">
-        <v>0.4520952380952381</v>
+        <v>0.453921568627451</v>
       </c>
       <c r="G112" s="14" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H112" s="15" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="I112" s="13">
         <f>IF($H$112="","",IF($H$112&lt;0,-$H$112/(-$H$112+100),100/($H$112+100)))</f>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="N112" s="19" t="inlineStr">
         <is>
-          <t>Model 45.2% (fair +121). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O112" s="15" t="n"/>
@@ -17014,13 +17014,13 @@
         </is>
       </c>
       <c r="F113" s="13" t="n">
-        <v>0.4783203125</v>
+        <v>0.48404</v>
       </c>
       <c r="G113" s="14" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H113" s="15" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="I113" s="13">
         <f>IF($H$113="","",IF($H$113&lt;0,-$H$113/(-$H$113+100),100/($H$113+100)))</f>
@@ -17044,7 +17044,7 @@
       </c>
       <c r="N113" s="19" t="inlineStr">
         <is>
-          <t>Model 47.8% (fair +109). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O113" s="15" t="n"/>
@@ -17080,13 +17080,13 @@
         </is>
       </c>
       <c r="F114" s="13" t="n">
-        <v>0.5216619771863118</v>
+        <v>0.5159667984189723</v>
       </c>
       <c r="G114" s="14" t="n">
-        <v>-109</v>
+        <v>-107</v>
       </c>
       <c r="H114" s="15" t="n">
-        <v>-163</v>
+        <v>-153</v>
       </c>
       <c r="I114" s="13">
         <f>IF($H$114="","",IF($H$114&lt;0,-$H$114/(-$H$114+100),100/($H$114+100)))</f>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="N114" s="19" t="inlineStr">
         <is>
-          <t>Model 52.2% (fair -109). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O114" s="15" t="n"/>
@@ -17146,7 +17146,7 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>0.440352422907489</v>
+        <v>0.4406607929515418</v>
       </c>
       <c r="G115" s="14" t="n">
         <v>127</v>
@@ -17176,7 +17176,7 @@
       </c>
       <c r="N115" s="19" t="inlineStr">
         <is>
-          <t>Model 44.0% (fair +127). Your call.</t>
+          <t>Model 44.1% (fair +127). Your call.</t>
         </is>
       </c>
       <c r="O115" s="15" t="n"/>
@@ -17212,13 +17212,13 @@
         </is>
       </c>
       <c r="F116" s="13" t="n">
-        <v>0.559653781512605</v>
+        <v>0.5593420600858369</v>
       </c>
       <c r="G116" s="14" t="n">
         <v>-127</v>
       </c>
       <c r="H116" s="15" t="n">
-        <v>-138</v>
+        <v>-133</v>
       </c>
       <c r="I116" s="13">
         <f>IF($H$116="","",IF($H$116&lt;0,-$H$116/(-$H$116+100),100/($H$116+100)))</f>
@@ -17242,7 +17242,7 @@
       </c>
       <c r="N116" s="19" t="inlineStr">
         <is>
-          <t>Model 56.0% (fair -127). Your call.</t>
+          <t>Model 55.9% (fair -127). Your call.</t>
         </is>
       </c>
       <c r="O116" s="15" t="n"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="F117" s="13" t="n">
-        <v>0.4841891891891892</v>
+        <v>0.4853603603603603</v>
       </c>
       <c r="G117" s="14" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H117" s="15" t="n">
         <v>122</v>
@@ -17308,7 +17308,7 @@
       </c>
       <c r="N117" s="19" t="inlineStr">
         <is>
-          <t>Model 48.4% (fair +107). Your call.</t>
+          <t>Model 48.5% (fair +106). Your call.</t>
         </is>
       </c>
       <c r="O117" s="15" t="n"/>
@@ -17344,13 +17344,13 @@
         </is>
       </c>
       <c r="F118" s="13" t="n">
-        <v>0.5157818181818181</v>
+        <v>0.5145981981981982</v>
       </c>
       <c r="G118" s="14" t="n">
-        <v>-107</v>
+        <v>-106</v>
       </c>
       <c r="H118" s="15" t="n">
-        <v>-120</v>
+        <v>-122</v>
       </c>
       <c r="I118" s="13">
         <f>IF($H$118="","",IF($H$118&lt;0,-$H$118/(-$H$118+100),100/($H$118+100)))</f>
@@ -17374,7 +17374,7 @@
       </c>
       <c r="N118" s="19" t="inlineStr">
         <is>
-          <t>Model 51.6% (fair -107). Your call.</t>
+          <t>Model 51.5% (fair -106). Your call.</t>
         </is>
       </c>
       <c r="O118" s="15" t="n"/>
@@ -17410,7 +17410,7 @@
         </is>
       </c>
       <c r="F119" s="13" t="n">
-        <v>0.4834</v>
+        <v>0.4838</v>
       </c>
       <c r="G119" s="14" t="n">
         <v>107</v>
@@ -17440,7 +17440,7 @@
       </c>
       <c r="N119" s="19" t="inlineStr">
         <is>
-          <t>Model 48.3% (fair +107). Your call.</t>
+          <t>Model 48.4% (fair +107). Your call.</t>
         </is>
       </c>
       <c r="O119" s="15" t="n"/>
@@ -17476,13 +17476,13 @@
         </is>
       </c>
       <c r="F120" s="13" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5162</v>
       </c>
       <c r="G120" s="14" t="n">
         <v>-107</v>
       </c>
       <c r="H120" s="15" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I120" s="13">
         <f>IF($H$120="","",IF($H$120&lt;0,-$H$120/(-$H$120+100),100/($H$120+100)))</f>
@@ -17506,7 +17506,7 @@
       </c>
       <c r="N120" s="19" t="inlineStr">
         <is>
-          <t>Model 51.7% (fair -107). Your call.</t>
+          <t>Model 51.6% (fair -107). Your call.</t>
         </is>
       </c>
       <c r="O120" s="15" t="n"/>
@@ -17542,13 +17542,13 @@
         </is>
       </c>
       <c r="F121" s="13" t="n">
-        <v>0.3638059701492538</v>
+        <v>0.3647547169811321</v>
       </c>
       <c r="G121" s="14" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H121" s="15" t="n">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="I121" s="13">
         <f>IF($H$121="","",IF($H$121&lt;0,-$H$121/(-$H$121+100),100/($H$121+100)))</f>
@@ -17572,7 +17572,7 @@
       </c>
       <c r="N121" s="19" t="inlineStr">
         <is>
-          <t>Model 36.4% (fair +175). Your call.</t>
+          <t>Model 36.5% (fair +174). Your call.</t>
         </is>
       </c>
       <c r="O121" s="15" t="n"/>
@@ -17608,13 +17608,13 @@
         </is>
       </c>
       <c r="F122" s="13" t="n">
-        <v>0.6361899280575539</v>
+        <v>0.6352254681647941</v>
       </c>
       <c r="G122" s="14" t="n">
-        <v>-175</v>
+        <v>-174</v>
       </c>
       <c r="H122" s="15" t="n">
-        <v>-178</v>
+        <v>-167</v>
       </c>
       <c r="I122" s="13">
         <f>IF($H$122="","",IF($H$122&lt;0,-$H$122/(-$H$122+100),100/($H$122+100)))</f>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="N122" s="19" t="inlineStr">
         <is>
-          <t>Model 63.6% (fair -175). Your call.</t>
+          <t>Model 63.5% (fair -174). Your call.</t>
         </is>
       </c>
       <c r="O122" s="15" t="n"/>
@@ -17674,13 +17674,13 @@
         </is>
       </c>
       <c r="F123" s="13" t="n">
-        <v>0.5193554621848738</v>
+        <v>0.5222360655737706</v>
       </c>
       <c r="G123" s="14" t="n">
-        <v>-108</v>
+        <v>-109</v>
       </c>
       <c r="H123" s="15" t="n">
-        <v>-138</v>
+        <v>-144</v>
       </c>
       <c r="I123" s="13">
         <f>IF($H$123="","",IF($H$123&lt;0,-$H$123/(-$H$123+100),100/($H$123+100)))</f>
@@ -17704,7 +17704,7 @@
       </c>
       <c r="N123" s="19" t="inlineStr">
         <is>
-          <t>Model 51.9% (fair -108). Your call.</t>
+          <t>Model 52.2% (fair -109). Your call.</t>
         </is>
       </c>
       <c r="O123" s="15" t="n"/>
@@ -17740,10 +17740,10 @@
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>0.4806437768240343</v>
+        <v>0.4777682403433476</v>
       </c>
       <c r="G124" s="14" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H124" s="15" t="n">
         <v>133</v>
@@ -17770,7 +17770,7 @@
       </c>
       <c r="N124" s="19" t="inlineStr">
         <is>
-          <t>Model 48.1% (fair +108). Your call.</t>
+          <t>Model 47.8% (fair +109). Your call.</t>
         </is>
       </c>
       <c r="O124" s="15" t="n"/>
@@ -17806,10 +17806,10 @@
         </is>
       </c>
       <c r="F125" s="13" t="n">
-        <v>0.4304</v>
+        <v>0.4282</v>
       </c>
       <c r="G125" s="14" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H125" s="15" t="n"/>
       <c r="I125" s="13">
@@ -17834,7 +17834,7 @@
       </c>
       <c r="N125" s="19" t="inlineStr">
         <is>
-          <t>Model 43.0% (fair +132). Your call.</t>
+          <t>Model 42.8% (fair +134). Your call.</t>
         </is>
       </c>
       <c r="O125" s="15" t="n"/>
@@ -17870,10 +17870,10 @@
         </is>
       </c>
       <c r="F126" s="13" t="n">
-        <v>0.5696</v>
+        <v>0.5718</v>
       </c>
       <c r="G126" s="14" t="n">
-        <v>-132</v>
+        <v>-134</v>
       </c>
       <c r="H126" s="15" t="n"/>
       <c r="I126" s="13">
@@ -17898,7 +17898,7 @@
       </c>
       <c r="N126" s="19" t="inlineStr">
         <is>
-          <t>Model 57.0% (fair -132). Your call.</t>
+          <t>Model 57.2% (fair -134). Your call.</t>
         </is>
       </c>
       <c r="O126" s="15" t="n"/>
@@ -17934,10 +17934,10 @@
         </is>
       </c>
       <c r="F127" s="13" t="n">
-        <v>0.4623921568627451</v>
+        <v>0.4604039215686274</v>
       </c>
       <c r="G127" s="14" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H127" s="15" t="n">
         <v>-104</v>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="N127" s="19" t="inlineStr">
         <is>
-          <t>Model 46.2% (fair +116). Your call.</t>
+          <t>Model 46.0% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O127" s="15" t="n"/>
@@ -18000,10 +18000,10 @@
         </is>
       </c>
       <c r="F128" s="13" t="n">
-        <v>0.5376</v>
+        <v>0.5396</v>
       </c>
       <c r="G128" s="14" t="n">
-        <v>-116</v>
+        <v>-117</v>
       </c>
       <c r="H128" s="15" t="n">
         <v>100</v>
@@ -18030,7 +18030,7 @@
       </c>
       <c r="N128" s="19" t="inlineStr">
         <is>
-          <t>Model 53.8% (fair -116). Your call.</t>
+          <t>Model 54.0% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O128" s="15" t="n"/>
@@ -18066,10 +18066,10 @@
         </is>
       </c>
       <c r="F129" s="13" t="n">
-        <v>0.6316109243697479</v>
+        <v>0.6323067226890756</v>
       </c>
       <c r="G129" s="14" t="n">
-        <v>-171</v>
+        <v>-172</v>
       </c>
       <c r="H129" s="15" t="n">
         <v>-138</v>
@@ -18096,7 +18096,7 @@
       </c>
       <c r="N129" s="19" t="inlineStr">
         <is>
-          <t>Model 63.2% (fair -171). Your call.</t>
+          <t>Model 63.2% (fair -172). Your call.</t>
         </is>
       </c>
       <c r="O129" s="15" t="n"/>
@@ -18132,10 +18132,10 @@
         </is>
       </c>
       <c r="F130" s="13" t="n">
-        <v>0.3683690987124464</v>
+        <v>0.3676824034334764</v>
       </c>
       <c r="G130" s="14" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H130" s="15" t="n">
         <v>133</v>
@@ -18162,7 +18162,7 @@
       </c>
       <c r="N130" s="19" t="inlineStr">
         <is>
-          <t>Model 36.8% (fair +171). Your call.</t>
+          <t>Model 36.8% (fair +172). Your call.</t>
         </is>
       </c>
       <c r="O130" s="15" t="n"/>
@@ -18198,10 +18198,10 @@
         </is>
       </c>
       <c r="F131" s="13" t="n">
-        <v>0.467</v>
+        <v>0.4656</v>
       </c>
       <c r="G131" s="14" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H131" s="15" t="n"/>
       <c r="I131" s="13">
@@ -18226,7 +18226,7 @@
       </c>
       <c r="N131" s="19" t="inlineStr">
         <is>
-          <t>Model 46.7% (fair +114). Your call.</t>
+          <t>Model 46.6% (fair +115). Your call.</t>
         </is>
       </c>
       <c r="O131" s="15" t="n"/>
@@ -18262,10 +18262,10 @@
         </is>
       </c>
       <c r="F132" s="13" t="n">
-        <v>0.533</v>
+        <v>0.5344</v>
       </c>
       <c r="G132" s="14" t="n">
-        <v>-114</v>
+        <v>-115</v>
       </c>
       <c r="H132" s="15" t="n"/>
       <c r="I132" s="13">
@@ -18290,7 +18290,7 @@
       </c>
       <c r="N132" s="19" t="inlineStr">
         <is>
-          <t>Model 53.3% (fair -114). Your call.</t>
+          <t>Model 53.4% (fair -115). Your call.</t>
         </is>
       </c>
       <c r="O132" s="15" t="n"/>
@@ -18326,7 +18326,7 @@
         </is>
       </c>
       <c r="F133" s="13" t="n">
-        <v>0.4347</v>
+        <v>0.4351</v>
       </c>
       <c r="G133" s="14" t="n">
         <v>130</v>
@@ -18392,7 +18392,7 @@
         </is>
       </c>
       <c r="F134" s="13" t="n">
-        <v>0.5653</v>
+        <v>0.5649</v>
       </c>
       <c r="G134" s="14" t="n">
         <v>-130</v>
@@ -18458,10 +18458,10 @@
         </is>
       </c>
       <c r="F135" s="13" t="n">
-        <v>0.4314903846153846</v>
+        <v>0.4295673076923077</v>
       </c>
       <c r="G135" s="14" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H135" s="15" t="n">
         <v>108</v>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="N135" s="19" t="inlineStr">
         <is>
-          <t>Model 43.1% (fair +132). Your call.</t>
+          <t>Model 43.0% (fair +133). Your call.</t>
         </is>
       </c>
       <c r="O135" s="15" t="n"/>
@@ -18524,10 +18524,10 @@
         </is>
       </c>
       <c r="F136" s="13" t="n">
-        <v>0.5685279069767442</v>
+        <v>0.5704</v>
       </c>
       <c r="G136" s="14" t="n">
-        <v>-132</v>
+        <v>-133</v>
       </c>
       <c r="H136" s="15" t="n">
         <v>-115</v>
@@ -18554,7 +18554,7 @@
       </c>
       <c r="N136" s="19" t="inlineStr">
         <is>
-          <t>Model 56.9% (fair -132). Your call.</t>
+          <t>Model 57.0% (fair -133). Your call.</t>
         </is>
       </c>
       <c r="O136" s="15" t="n"/>
@@ -18590,10 +18590,10 @@
         </is>
       </c>
       <c r="F137" s="13" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.5538</v>
       </c>
       <c r="G137" s="14" t="n">
-        <v>-123</v>
+        <v>-124</v>
       </c>
       <c r="H137" s="15" t="n"/>
       <c r="I137" s="13">
@@ -18618,7 +18618,7 @@
       </c>
       <c r="N137" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 55.4% (fair -124). Your call.</t>
         </is>
       </c>
       <c r="O137" s="15" t="n"/>
@@ -18654,10 +18654,10 @@
         </is>
       </c>
       <c r="F138" s="13" t="n">
-        <v>0.4491</v>
+        <v>0.4461</v>
       </c>
       <c r="G138" s="14" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H138" s="15" t="n"/>
       <c r="I138" s="13">
@@ -18682,7 +18682,7 @@
       </c>
       <c r="N138" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 44.6% (fair +124). Your call.</t>
         </is>
       </c>
       <c r="O138" s="15" t="n"/>
@@ -18718,13 +18718,13 @@
         </is>
       </c>
       <c r="F139" s="13" t="n">
-        <v>0.3895</v>
+        <v>0.453947572815534</v>
       </c>
       <c r="G139" s="14" t="n">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="H139" s="15" t="n">
-        <v>104</v>
+        <v>-106</v>
       </c>
       <c r="I139" s="13">
         <f>IF($H$139="","",IF($H$139&lt;0,-$H$139/(-$H$139+100),100/($H$139+100)))</f>
@@ -18748,7 +18748,7 @@
       </c>
       <c r="N139" s="19" t="inlineStr">
         <is>
-          <t>Model 39.0% (fair +157). Your call.</t>
+          <t>Model 45.4% (fair +120). Your call.</t>
         </is>
       </c>
       <c r="O139" s="15" t="n"/>
@@ -18784,10 +18784,10 @@
         </is>
       </c>
       <c r="F140" s="13" t="n">
-        <v>0.6105</v>
+        <v>0.5460576923076923</v>
       </c>
       <c r="G140" s="14" t="n">
-        <v>-157</v>
+        <v>-120</v>
       </c>
       <c r="H140" s="15" t="n">
         <v>108</v>
@@ -18814,7 +18814,7 @@
       </c>
       <c r="N140" s="19" t="inlineStr">
         <is>
-          <t>Model 61.1% (fair -157). Your call.</t>
+          <t>Model 54.6% (fair -120). Your call.</t>
         </is>
       </c>
       <c r="O140" s="15" t="n"/>
@@ -18850,10 +18850,10 @@
         </is>
       </c>
       <c r="F141" s="13" t="n">
-        <v>0.345893536121673</v>
+        <v>0.3449049429657795</v>
       </c>
       <c r="G141" s="14" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H141" s="15" t="n">
         <v>163</v>
@@ -18880,7 +18880,7 @@
       </c>
       <c r="N141" s="19" t="inlineStr">
         <is>
-          <t>Model 34.6% (fair +189). Your call.</t>
+          <t>Model 34.5% (fair +190). Your call.</t>
         </is>
       </c>
       <c r="O141" s="15" t="n"/>
@@ -18916,13 +18916,13 @@
         </is>
       </c>
       <c r="F142" s="13" t="n">
-        <v>0.6540875912408759</v>
+        <v>0.655078417266187</v>
       </c>
       <c r="G142" s="14" t="n">
-        <v>-189</v>
+        <v>-190</v>
       </c>
       <c r="H142" s="15" t="n">
-        <v>-174</v>
+        <v>-178</v>
       </c>
       <c r="I142" s="13">
         <f>IF($H$142="","",IF($H$142&lt;0,-$H$142/(-$H$142+100),100/($H$142+100)))</f>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="N142" s="19" t="inlineStr">
         <is>
-          <t>Model 65.4% (fair -189). Your call.</t>
+          <t>Model 65.5% (fair -190). Your call.</t>
         </is>
       </c>
       <c r="O142" s="15" t="n"/>
@@ -19123,10 +19123,10 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>0.2992173913043478</v>
+        <v>0.2939710144927536</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>245</v>
@@ -19153,7 +19153,7 @@
       </c>
       <c r="N5" s="19" t="inlineStr">
         <is>
-          <t>Model 29.9% (fair +234). Your call.</t>
+          <t>Model 29.4% (fair +240). Your call.</t>
         </is>
       </c>
       <c r="O5" s="15" t="n"/>
@@ -19189,10 +19189,10 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>0.7007710144927536</v>
+        <v>0.7060260869565217</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>-234</v>
+        <v>-240</v>
       </c>
       <c r="H6" s="15" t="n">
         <v>-245</v>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="N6" s="19" t="inlineStr">
         <is>
-          <t>Model 70.1% (fair -234). Your call.</t>
+          <t>Model 70.6% (fair -240). Your call.</t>
         </is>
       </c>
       <c r="O6" s="15" t="n"/>
@@ -19255,10 +19255,10 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>0.4981566820276498</v>
+        <v>0.6593548387096775</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>101</v>
+        <v>-194</v>
       </c>
       <c r="H7" s="15" t="n">
         <v>117</v>
@@ -19285,7 +19285,7 @@
       </c>
       <c r="N7" s="19" t="inlineStr">
         <is>
-          <t>Model 49.8% (fair +101). Your call.</t>
+          <t>Model 65.9% (fair -194). Your call.</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -19321,10 +19321,10 @@
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>0.5019</v>
+        <v>0.3407</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>-101</v>
+        <v>194</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>117</v>
@@ -19351,7 +19351,7 @@
       </c>
       <c r="N8" s="19" t="inlineStr">
         <is>
-          <t>Model 50.2% (fair -101). Your call.</t>
+          <t>Model 34.1% (fair +194). Your call.</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -19387,10 +19387,10 @@
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>0.4759158415841584</v>
+        <v>0.4817227722772277</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H9" s="15" t="n">
         <v>-102</v>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="N9" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 48.2% (fair +108). Your call.</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -19453,10 +19453,10 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>0.5240865384615385</v>
+        <v>0.5182692307692308</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>-110</v>
+        <v>-108</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>108</v>
@@ -19483,7 +19483,7 @@
       </c>
       <c r="N10" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 51.8% (fair -108). Your call.</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -19519,10 +19519,10 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>0.7444684931506851</v>
+        <v>0.7503493150684932</v>
       </c>
       <c r="G11" s="14" t="n">
-        <v>-291</v>
+        <v>-301</v>
       </c>
       <c r="H11" s="15" t="n">
         <v>-265</v>
@@ -19549,7 +19549,7 @@
       </c>
       <c r="N11" s="19" t="inlineStr">
         <is>
-          <t>Model 74.4% (fair -291). Your call.</t>
+          <t>Model 75.0% (fair -301). Your call.</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -19585,10 +19585,10 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>0.2555437665782493</v>
+        <v>0.2496551724137931</v>
       </c>
       <c r="G12" s="14" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>277</v>
@@ -19615,7 +19615,7 @@
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>Model 25.6% (fair +291). Your call.</t>
+          <t>Model 25.0% (fair +301). Your call.</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -19651,10 +19651,10 @@
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>0.4731707317073171</v>
+        <v>0.5384878048780489</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>111</v>
+        <v>-117</v>
       </c>
       <c r="H13" s="15" t="n">
         <v>105</v>
@@ -19681,7 +19681,7 @@
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>Model 47.3% (fair +111). Your call.</t>
+          <t>Model 53.8% (fair -117). Your call.</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -19717,10 +19717,10 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>0.5267999999999999</v>
+        <v>0.4615</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>-111</v>
+        <v>117</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>105</v>
@@ -19747,7 +19747,7 @@
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>Model 52.7% (fair -111). Your call.</t>
+          <t>Model 46.2% (fair +117). Your call.</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -19783,10 +19783,10 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>0.4485</v>
+        <v>0.4334</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H15" s="15" t="n">
         <v>117</v>
@@ -19813,7 +19813,7 @@
       </c>
       <c r="N15" s="19" t="inlineStr">
         <is>
-          <t>Model 44.9% (fair +123). Your call.</t>
+          <t>Model 43.3% (fair +131). Your call.</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -19849,10 +19849,10 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>0.5515</v>
+        <v>0.5666</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>-123</v>
+        <v>-131</v>
       </c>
       <c r="H16" s="15" t="n">
         <v>108</v>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="N16" s="19" t="inlineStr">
         <is>
-          <t>Model 55.1% (fair -123). Your call.</t>
+          <t>Model 56.7% (fair -131). Your call.</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -19915,13 +19915,13 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>0.4104147465437789</v>
+        <v>0.4193749999999999</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I17" s="13">
         <f>IF($H$17="","",IF($H$17&lt;0,-$H$17/(-$H$17+100),100/($H$17+100)))</f>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="N17" s="19" t="inlineStr">
         <is>
-          <t>Model 41.0% (fair +144). Your call.</t>
+          <t>Model 41.9% (fair +138). Your call.</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -19981,13 +19981,13 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>0.5896023255813955</v>
+        <v>0.5806038461538462</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>-144</v>
+        <v>-138</v>
       </c>
       <c r="H18" s="15" t="n">
-        <v>-115</v>
+        <v>-108</v>
       </c>
       <c r="I18" s="13">
         <f>IF($H$18="","",IF($H$18&lt;0,-$H$18/(-$H$18+100),100/($H$18+100)))</f>
@@ -20011,7 +20011,7 @@
       </c>
       <c r="N18" s="19" t="inlineStr">
         <is>
-          <t>Model 59.0% (fair -144). Your call.</t>
+          <t>Model 58.1% (fair -138). Your call.</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -20047,13 +20047,13 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>0.5241784037558685</v>
+        <v>0.5241666666666667</v>
       </c>
       <c r="G19" s="14" t="n">
         <v>-110</v>
       </c>
       <c r="H19" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I19" s="13">
         <f>IF($H$19="","",IF($H$19&lt;0,-$H$19/(-$H$19+100),100/($H$19+100)))</f>
@@ -20119,7 +20119,7 @@
         <v>110</v>
       </c>
       <c r="H20" s="15" t="n">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="I20" s="13">
         <f>IF($H$20="","",IF($H$20&lt;0,-$H$20/(-$H$20+100),100/($H$20+100)))</f>
@@ -20175,17 +20175,17 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Golden State Valkyries -3.5</t>
+          <t>Golden State Valkyries -1.5</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>0.5236</v>
+        <v>0.5921</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-110</v>
+        <v>-145</v>
       </c>
       <c r="H21" s="15" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I21" s="13">
         <f>IF($H$21="","",IF($H$21&lt;0,-$H$21/(-$H$21+100),100/($H$21+100)))</f>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="N21" s="19" t="inlineStr">
         <is>
-          <t>Model 52.4% (fair -110). Your call.</t>
+          <t>Model 59.2% (fair -145). Your call.</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -20241,17 +20241,17 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>New York Liberty +3.5</t>
+          <t>New York Liberty +1.5</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>0.4764</v>
+        <v>0.4079</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="H22" s="15" t="n">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="I22" s="13">
         <f>IF($H$22="","",IF($H$22&lt;0,-$H$22/(-$H$22+100),100/($H$22+100)))</f>
@@ -20275,7 +20275,7 @@
       </c>
       <c r="N22" s="19" t="inlineStr">
         <is>
-          <t>Model 47.6% (fair +110). Your call.</t>
+          <t>Model 40.8% (fair +145). Your call.</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -20390,28 +20390,28 @@
         </is>
       </c>
       <c r="B5" s="21" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C5" s="22" t="n">
-        <v>0.252</v>
+        <v>0.2505</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>0.4402</v>
+        <v>0.4492</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>-8.220000000000001</v>
+        <v>-5.62</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>-4.47</v>
+        <v>-3.01</v>
       </c>
       <c r="H5" s="24" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.5031</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="6">
@@ -20421,10 +20421,10 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>0.2526</v>
+        <v>0.2525</v>
       </c>
       <c r="D6" s="21" t="n">
         <v>148</v>
@@ -20452,28 +20452,28 @@
         </is>
       </c>
       <c r="B7" s="21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C7" s="22" t="n">
-        <v>0.2494</v>
+        <v>0.2371</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E7" s="13" t="n">
-        <v>0.3235</v>
+        <v>0.3784</v>
       </c>
       <c r="F7" s="23" t="n">
-        <v>-6.05</v>
+        <v>-3.45</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>-17.8</v>
+        <v>-9.33</v>
       </c>
       <c r="H7" s="24" t="n">
-        <v>-4</v>
+        <v>-2.61</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>0.3846</v>
+        <v>0.3929</v>
       </c>
     </row>
     <row r="8">
@@ -20525,7 +20525,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>When the model said X%, how often it actually happened (n=217, ECE 0.063 — lower is better; a calibrated model's bars sit on the diagonal).</t>
+          <t>When the model said X%, how often it actually happened (n=220, ECE 0.061 — lower is better; a calibrated model's bars sit on the diagonal).</t>
         </is>
       </c>
     </row>
@@ -20582,16 +20582,16 @@
         </is>
       </c>
       <c r="B18" s="21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>0.2646</v>
+        <v>0.2599</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>0.5</v>
+        <v>0.4286</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>0.2354</v>
+        <v>0.1687</v>
       </c>
     </row>
     <row r="19">
@@ -20620,16 +20620,16 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C20" s="13" t="n">
-        <v>0.4557</v>
+        <v>0.456</v>
       </c>
       <c r="D20" s="13" t="n">
-        <v>0.4627</v>
+        <v>0.4638</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>0.007</v>
+        <v>0.0078</v>
       </c>
     </row>
     <row r="21">
